--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="62">
   <si>
     <t>DIVISION</t>
   </si>
@@ -68,82 +68,76 @@
     <t>POSTED</t>
   </si>
   <si>
+    <t>RAFI SEAFOOD</t>
+  </si>
+  <si>
+    <t>Surbled</t>
+  </si>
+  <si>
+    <t>MAMA RADA PRODUCTION</t>
+  </si>
+  <si>
+    <t>KSP</t>
+  </si>
+  <si>
+    <t>Bali Permata Jaya</t>
+  </si>
+  <si>
+    <t>SURYA CIPTA NIAGA</t>
+  </si>
+  <si>
+    <t>BAYU AGNI</t>
+  </si>
+  <si>
+    <t>JOY GREEN</t>
+  </si>
+  <si>
+    <t>N/O</t>
+  </si>
+  <si>
+    <t>CELEBRITY BAKERY</t>
+  </si>
+  <si>
+    <t>KROP</t>
+  </si>
+  <si>
+    <t>BOILER</t>
+  </si>
+  <si>
+    <t>ABDI JAYA</t>
+  </si>
+  <si>
+    <t>DISHY SOAP</t>
+  </si>
+  <si>
+    <t>DAILY BAGUETTE (NICO)</t>
+  </si>
+  <si>
+    <t>BAR</t>
+  </si>
+  <si>
+    <t>WARUNG EKA</t>
+  </si>
+  <si>
+    <t>DEWATA COCONUT</t>
+  </si>
+  <si>
+    <t>PNB</t>
+  </si>
+  <si>
+    <t>DSP</t>
+  </si>
+  <si>
+    <t>DSP (ARYA BIMA)</t>
+  </si>
+  <si>
+    <t>SELERA (STIR UP SYRUP)</t>
+  </si>
+  <si>
+    <t>DW BALI</t>
+  </si>
+  <si>
     <t>DDB</t>
-  </si>
-  <si>
-    <t>RAFI SEAFOOD</t>
-  </si>
-  <si>
-    <t>Surbled</t>
-  </si>
-  <si>
-    <t>MAMA RADA PRODUCTION</t>
-  </si>
-  <si>
-    <t>Blacklist</t>
-  </si>
-  <si>
-    <t>KSP</t>
-  </si>
-  <si>
-    <t>MAKER</t>
-  </si>
-  <si>
-    <t>SURYA CIPTA NIAGA</t>
-  </si>
-  <si>
-    <t>BAYU AGNI</t>
-  </si>
-  <si>
-    <t>JOY GREEN</t>
-  </si>
-  <si>
-    <t>N/O</t>
-  </si>
-  <si>
-    <t>CELEBRITY BAKERY</t>
-  </si>
-  <si>
-    <t>KROP</t>
-  </si>
-  <si>
-    <t>BOILER</t>
-  </si>
-  <si>
-    <t>ABDI JAYA</t>
-  </si>
-  <si>
-    <t>YET</t>
-  </si>
-  <si>
-    <t>DISHY SOAP</t>
-  </si>
-  <si>
-    <t>DAILY BAGUETTE (NICO)</t>
-  </si>
-  <si>
-    <t>BAR</t>
-  </si>
-  <si>
-    <t>WARUNG EKA</t>
-  </si>
-  <si>
-    <t>DEWATA COCONUT</t>
-  </si>
-  <si>
-    <t>PNB</t>
-  </si>
-  <si>
-    <t>DSP</t>
-  </si>
-  <si>
-    <t>DSP (ARYA BIMA)</t>
-  </si>
-  <si>
-    <t>SELERA (STIR UP SYRUP)</t>
-  </si>
-  <si>
-    <t>DW BALI</t>
   </si>
   <si>
     <t>NANO DEWATA</t>
@@ -407,7 +401,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -434,6 +428,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -625,7 +625,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -895,6 +895,43 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1045,7 +1082,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1057,119 +1094,119 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1215,13 +1252,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1233,10 +1273,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1248,13 +1288,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1263,10 +1303,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1284,7 +1324,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1293,17 +1336,65 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
@@ -1851,12 +1942,14 @@
     <col min="5" max="5" width="12.5714285714286" style="3" customWidth="1"/>
     <col min="6" max="7" width="13.6666666666667" customWidth="1"/>
     <col min="8" max="8" width="13.6666666666667" style="4" customWidth="1"/>
-    <col min="9" max="11" width="14.3333333333333"/>
+    <col min="9" max="9" width="14.3333333333333"/>
+    <col min="10" max="10" width="15.4285714285714"/>
+    <col min="11" max="11" width="14.3333333333333"/>
     <col min="12" max="12" width="22.6666666666667" customWidth="1"/>
     <col min="13" max="13" width="11.6666666666667"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1880,6 +1973,10 @@
       </c>
       <c r="H1" s="11" t="s">
         <v>3</v>
+      </c>
+      <c r="J1" s="63">
+        <f>SUM(F2,F3,F4,F8,F13,F14,F17,F24,F25,F34)</f>
+        <v>127592646</v>
       </c>
     </row>
     <row r="2" ht="15" spans="1:10">
@@ -1907,7 +2004,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" ht="15" spans="1:8">
       <c r="A3" s="17"/>
       <c r="B3" s="13" t="s">
         <v>11</v>
@@ -1918,20 +2015,19 @@
       <c r="D3" s="15">
         <v>45478060</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="15"/>
+      <c r="F3" s="15">
+        <v>39027410</v>
+      </c>
       <c r="G3" s="15"/>
       <c r="H3" s="16"/>
-      <c r="J3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+    </row>
+    <row r="4" ht="15" spans="1:10">
       <c r="A4" s="17"/>
       <c r="B4" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>8</v>
@@ -1939,20 +2035,22 @@
       <c r="D4" s="15">
         <v>29900100</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="15"/>
+      <c r="F4" s="15">
+        <v>20617200</v>
+      </c>
       <c r="G4" s="15"/>
       <c r="H4" s="16"/>
       <c r="J4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="1:8">
       <c r="A5" s="17"/>
       <c r="B5" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>8</v>
@@ -1968,14 +2066,11 @@
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="16"/>
-      <c r="J5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" ht="15" spans="1:8">
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="17"/>
       <c r="B6" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>8</v>
@@ -1984,18 +2079,21 @@
         <v>5610900</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F6" s="15">
         <v>3578050</v>
       </c>
       <c r="G6" s="15"/>
       <c r="H6" s="16"/>
-    </row>
-    <row r="7" ht="15" spans="1:8">
+      <c r="J6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="17"/>
       <c r="B7" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>8</v>
@@ -2015,7 +2113,7 @@
     <row r="8" spans="1:8">
       <c r="A8" s="17"/>
       <c r="B8" s="13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>8</v>
@@ -2023,7 +2121,7 @@
       <c r="D8" s="15">
         <v>8775000</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="18" t="s">
         <v>12</v>
       </c>
       <c r="F8" s="15">
@@ -2035,14 +2133,14 @@
     <row r="9" ht="15" spans="1:8">
       <c r="A9" s="17"/>
       <c r="B9" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="D9" s="15"/>
-      <c r="E9" s="14" t="s">
-        <v>23</v>
+      <c r="E9" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
@@ -2051,14 +2149,14 @@
     <row r="10" ht="15" spans="1:8">
       <c r="A10" s="17"/>
       <c r="B10" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="D10" s="15"/>
-      <c r="E10" s="14" t="s">
-        <v>23</v>
+      <c r="E10" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
@@ -2067,10 +2165,10 @@
     <row r="11" spans="1:12">
       <c r="A11" s="17"/>
       <c r="B11" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="14" t="s">
         <v>23</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="14" t="s">
@@ -2081,12 +2179,12 @@
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="16"/>
-      <c r="L11" s="45"/>
+      <c r="L11" s="63"/>
     </row>
     <row r="12" ht="15" spans="1:8">
       <c r="A12" s="17"/>
       <c r="B12" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>8</v>
@@ -2104,7 +2202,7 @@
     <row r="13" ht="15" spans="1:8">
       <c r="A13" s="17"/>
       <c r="B13" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>8</v>
@@ -2112,23 +2210,25 @@
       <c r="D13" s="15">
         <v>4375000</v>
       </c>
-      <c r="E13" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="15"/>
+      <c r="E13" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="15">
+        <v>4715000</v>
+      </c>
       <c r="G13" s="15"/>
       <c r="H13" s="16"/>
     </row>
     <row r="14" ht="15" spans="1:8">
       <c r="A14" s="17"/>
       <c r="B14" s="13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="15"/>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="18" t="s">
         <v>12</v>
       </c>
       <c r="F14" s="15">
@@ -2138,49 +2238,49 @@
       <c r="H14" s="16"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="18"/>
-      <c r="B15" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="21">
+      <c r="A15" s="19"/>
+      <c r="B15" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="22"/>
+      <c r="E15" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="22">
         <v>2320000</v>
       </c>
-      <c r="G15" s="21"/>
-      <c r="H15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="23"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="26">
+      <c r="A16" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="27">
         <v>20669000</v>
       </c>
-      <c r="E16" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="26">
+      <c r="E16" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="27">
         <v>13909500</v>
       </c>
-      <c r="G16" s="26"/>
-      <c r="H16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="28"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="17"/>
       <c r="B17" s="13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>8</v>
@@ -2188,7 +2288,7 @@
       <c r="D17" s="15">
         <v>3230000</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="18" t="s">
         <v>12</v>
       </c>
       <c r="F17" s="15">
@@ -2200,7 +2300,7 @@
     <row r="18" spans="1:8">
       <c r="A18" s="17"/>
       <c r="B18" s="13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>8</v>
@@ -2220,7 +2320,7 @@
     <row r="19" spans="1:8">
       <c r="A19" s="17"/>
       <c r="B19" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>8</v>
@@ -2240,14 +2340,14 @@
     <row r="20" ht="15" spans="1:8">
       <c r="A20" s="17"/>
       <c r="B20" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>23</v>
+        <v>33</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="D20" s="15"/>
-      <c r="E20" s="14" t="s">
-        <v>23</v>
+      <c r="E20" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15"/>
       <c r="G20" s="15"/>
@@ -2256,7 +2356,7 @@
     <row r="21" spans="1:8">
       <c r="A21" s="17"/>
       <c r="B21" s="13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>8</v>
@@ -2273,10 +2373,10 @@
       <c r="G21" s="15"/>
       <c r="H21" s="16"/>
     </row>
-    <row r="22" ht="15" spans="1:8">
+    <row r="22" spans="1:8">
       <c r="A22" s="17"/>
       <c r="B22" s="13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C22" s="14" t="s">
         <v>8</v>
@@ -2284,8 +2384,8 @@
       <c r="D22" s="15">
         <v>2410000</v>
       </c>
-      <c r="E22" s="14" t="s">
-        <v>23</v>
+      <c r="E22" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
@@ -2294,7 +2394,7 @@
     <row r="23" spans="1:8">
       <c r="A23" s="17"/>
       <c r="B23" s="13" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>8</v>
@@ -2314,13 +2414,13 @@
     <row r="24" spans="1:8">
       <c r="A24" s="17"/>
       <c r="B24" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="28" t="s">
-        <v>40</v>
+        <v>37</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>38</v>
       </c>
       <c r="D24" s="15"/>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="18" t="s">
         <v>12</v>
       </c>
       <c r="F24" s="15">
@@ -2332,7 +2432,7 @@
     <row r="25" spans="1:8">
       <c r="A25" s="17"/>
       <c r="B25" s="13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>8</v>
@@ -2340,7 +2440,7 @@
       <c r="D25" s="15">
         <v>4760036</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="18" t="s">
         <v>12</v>
       </c>
       <c r="F25" s="15">
@@ -2352,7 +2452,7 @@
     <row r="26" spans="1:8">
       <c r="A26" s="17"/>
       <c r="B26" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C26" s="14" t="s">
         <v>8</v>
@@ -2372,7 +2472,7 @@
     <row r="27" spans="1:8">
       <c r="A27" s="17"/>
       <c r="B27" s="13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>8</v>
@@ -2392,23 +2492,23 @@
     <row r="28" ht="15" spans="1:8">
       <c r="A28" s="17"/>
       <c r="B28" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="28" t="s">
-        <v>23</v>
+        <v>42</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>21</v>
       </c>
       <c r="D28" s="15"/>
-      <c r="E28" s="14" t="s">
-        <v>23</v>
+      <c r="E28" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15"/>
       <c r="G28" s="15"/>
       <c r="H28" s="16"/>
     </row>
-    <row r="29" ht="15" spans="1:8">
+    <row r="29" spans="1:8">
       <c r="A29" s="17"/>
       <c r="B29" s="13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>8</v>
@@ -2416,8 +2516,8 @@
       <c r="D29" s="15">
         <v>3948000</v>
       </c>
-      <c r="E29" s="14" t="s">
-        <v>23</v>
+      <c r="E29" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
@@ -2426,7 +2526,7 @@
     <row r="30" spans="1:8">
       <c r="A30" s="17"/>
       <c r="B30" s="13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C30" s="14" t="s">
         <v>8</v>
@@ -2434,24 +2534,24 @@
       <c r="D30" s="15">
         <v>250000</v>
       </c>
-      <c r="E30" s="14" t="s">
-        <v>23</v>
+      <c r="E30" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="16"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" ht="15" spans="1:8">
       <c r="A31" s="17"/>
       <c r="B31" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="28" t="s">
-        <v>23</v>
+        <v>45</v>
+      </c>
+      <c r="C31" s="29" t="s">
+        <v>21</v>
       </c>
       <c r="D31" s="15"/>
-      <c r="E31" s="14" t="s">
-        <v>23</v>
+      <c r="E31" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
@@ -2459,48 +2559,48 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="17"/>
-      <c r="B32" s="29" t="s">
+      <c r="B32" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="32"/>
+      <c r="E32" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="32">
+        <v>915750</v>
+      </c>
+      <c r="G32" s="32"/>
+      <c r="H32" s="33"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="31">
-        <v>915750</v>
-      </c>
-      <c r="G32" s="31"/>
-      <c r="H32" s="32"/>
-    </row>
-    <row r="33" ht="15" spans="1:8">
-      <c r="A33" s="33" t="s">
+      <c r="C33" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="27">
+        <v>4897000</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="27">
+        <v>8368100</v>
+      </c>
+      <c r="G33" s="27"/>
+      <c r="H33" s="28"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="35"/>
+      <c r="B34" s="13" t="s">
         <v>49</v>
-      </c>
-      <c r="B33" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="26">
-        <v>4897000</v>
-      </c>
-      <c r="E33" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="26">
-        <v>8368100</v>
-      </c>
-      <c r="G33" s="26"/>
-      <c r="H33" s="27"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="34"/>
-      <c r="B34" s="13" t="s">
-        <v>51</v>
       </c>
       <c r="C34" s="14" t="s">
         <v>8</v>
@@ -2508,7 +2608,7 @@
       <c r="D34" s="15">
         <v>4375000</v>
       </c>
-      <c r="E34" s="28" t="s">
+      <c r="E34" s="29" t="s">
         <v>12</v>
       </c>
       <c r="F34" s="15">
@@ -2518,9 +2618,9 @@
       <c r="H34" s="16"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="34"/>
+      <c r="A35" s="35"/>
       <c r="B35" s="13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>8</v>
@@ -2538,160 +2638,170 @@
       <c r="H35" s="16"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="35"/>
-      <c r="B36" s="19" t="s">
+      <c r="A36" s="36"/>
+      <c r="B36" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="22">
+        <v>1168000</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="22">
+        <v>893000</v>
+      </c>
+      <c r="G36" s="22"/>
+      <c r="H36" s="23"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="C36" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="21">
-        <v>1168000</v>
-      </c>
-      <c r="E36" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="21">
-        <v>893000</v>
-      </c>
-      <c r="G36" s="21"/>
-      <c r="H36" s="22"/>
-    </row>
-    <row r="37" ht="15" spans="1:8">
-      <c r="A37" s="36" t="s">
+      <c r="C37" s="39"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" s="27">
+        <v>1020000</v>
+      </c>
+      <c r="G37" s="40"/>
+      <c r="H37" s="28"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="41"/>
+      <c r="B38" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="B37" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" s="25"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="F37" s="26">
-        <v>1020000</v>
-      </c>
-      <c r="G37" s="38"/>
-      <c r="H37" s="27"/>
-    </row>
-    <row r="38" ht="15" spans="1:8">
-      <c r="A38" s="39"/>
-      <c r="B38" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="41"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="43"/>
       <c r="E38" s="14" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F38" s="15">
         <v>1350000</v>
       </c>
-      <c r="G38" s="41"/>
+      <c r="G38" s="43"/>
       <c r="H38" s="16"/>
     </row>
-    <row r="39" ht="15" spans="1:8">
-      <c r="A39" s="39"/>
-      <c r="B39" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" s="14"/>
-      <c r="D39" s="41"/>
+    <row r="39" spans="1:8">
+      <c r="A39" s="41"/>
+      <c r="B39" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="43"/>
       <c r="E39" s="14" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F39" s="15">
         <v>600000</v>
       </c>
-      <c r="G39" s="41"/>
+      <c r="G39" s="43"/>
       <c r="H39" s="16"/>
     </row>
-    <row r="40" ht="15" spans="1:8">
-      <c r="A40" s="39"/>
-      <c r="B40" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="41"/>
+    <row r="40" spans="1:8">
+      <c r="A40" s="41"/>
+      <c r="B40" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="43"/>
       <c r="E40" s="14" t="s">
         <v>8</v>
       </c>
       <c r="F40" s="15">
         <v>318134</v>
       </c>
-      <c r="G40" s="41"/>
+      <c r="G40" s="43"/>
       <c r="H40" s="16"/>
     </row>
-    <row r="41" ht="15" spans="1:8">
-      <c r="A41" s="39"/>
-      <c r="B41" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="C41" s="14"/>
-      <c r="D41" s="41"/>
+    <row r="41" spans="1:8">
+      <c r="A41" s="41"/>
+      <c r="B41" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="43"/>
       <c r="E41" s="14" t="s">
         <v>8</v>
       </c>
       <c r="F41" s="15">
         <v>248700</v>
       </c>
-      <c r="G41" s="41"/>
+      <c r="G41" s="43"/>
       <c r="H41" s="16"/>
     </row>
-    <row r="42" ht="15" spans="1:8">
-      <c r="A42" s="39"/>
-      <c r="B42" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="14"/>
-      <c r="D42" s="41"/>
+    <row r="42" spans="1:8">
+      <c r="A42" s="41"/>
+      <c r="B42" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="18"/>
+      <c r="D42" s="43"/>
       <c r="E42" s="14" t="s">
         <v>8</v>
       </c>
       <c r="F42" s="15">
         <v>1029180</v>
       </c>
-      <c r="G42" s="41"/>
+      <c r="G42" s="43"/>
       <c r="H42" s="16"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="42"/>
-      <c r="B43" s="43" t="s">
+      <c r="A43" s="41"/>
+      <c r="B43" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" s="45"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="48">
+        <v>270000</v>
+      </c>
+      <c r="G43" s="46"/>
+      <c r="H43" s="49"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="41"/>
+      <c r="B44" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="51"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="54">
+        <v>1000000</v>
+      </c>
+      <c r="G44" s="52"/>
+      <c r="H44" s="55"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="56"/>
+      <c r="B45" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="C43" s="20"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="21">
-        <v>270000</v>
-      </c>
-      <c r="G43" s="44"/>
-      <c r="H43" s="22"/>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="4">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="4">
+      <c r="C45" s="58"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="61">
         <v>3000000</v>
       </c>
+      <c r="G45" s="59"/>
+      <c r="H45" s="62"/>
     </row>
     <row r="46" spans="6:6">
       <c r="F46" s="4"/>
@@ -2722,7 +2832,7 @@
     <mergeCell ref="A2:A15"/>
     <mergeCell ref="A16:A32"/>
     <mergeCell ref="A33:A36"/>
-    <mergeCell ref="A37:A43"/>
+    <mergeCell ref="A37:A45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="69">
   <si>
     <t>DIVISION</t>
   </si>
@@ -68,6 +68,9 @@
     <t>POSTED</t>
   </si>
   <si>
+    <t>Sedana</t>
+  </si>
+  <si>
     <t>RAFI SEAFOOD</t>
   </si>
   <si>
@@ -77,18 +80,27 @@
     <t>MAMA RADA PRODUCTION</t>
   </si>
   <si>
+    <t>Bali Permata Jaya</t>
+  </si>
+  <si>
     <t>KSP</t>
   </si>
   <si>
-    <t>Bali Permata Jaya</t>
+    <t>Bayu agni</t>
   </si>
   <si>
     <t>SURYA CIPTA NIAGA</t>
   </si>
   <si>
+    <t>Abdi Jaya</t>
+  </si>
+  <si>
     <t>BAYU AGNI</t>
   </si>
   <si>
+    <t>Dishy soap</t>
+  </si>
+  <si>
     <t>JOY GREEN</t>
   </si>
   <si>
@@ -98,9 +110,15 @@
     <t>CELEBRITY BAKERY</t>
   </si>
   <si>
+    <t>Dewata coconut</t>
+  </si>
+  <si>
     <t>KROP</t>
   </si>
   <si>
+    <t>Nano Dewata</t>
+  </si>
+  <si>
     <t>BOILER</t>
   </si>
   <si>
@@ -197,13 +215,13 @@
     <t>COFFEE MACHINE MAINTENANCE</t>
   </si>
   <si>
-    <t>TWIN PACK MINI &amp; ANT KILLER</t>
-  </si>
-  <si>
-    <t>GLASS TISSUE BOX</t>
-  </si>
-  <si>
-    <t>BLANKET, FLOOR MOP, TISSUE</t>
+    <t>TWIN PACK MINI &amp; ANT KILLER (TKP)</t>
+  </si>
+  <si>
+    <t>GLASS TISSUE BOX (TKP)</t>
+  </si>
+  <si>
+    <t>BLANKET, FLOOR MOP, TISSUE (TKP)</t>
   </si>
   <si>
     <t>PURCHASE MCB</t>
@@ -213,6 +231,9 @@
   </si>
   <si>
     <t>GALLERY EX HOTEL</t>
+  </si>
+  <si>
+    <t>BAR CHILLER MAINTENANCE</t>
   </si>
 </sst>
 </file>
@@ -401,7 +422,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -440,6 +461,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -625,7 +658,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -792,6 +825,64 @@
         <color auto="1"/>
       </right>
       <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -800,6 +891,19 @@
         <color auto="1"/>
       </left>
       <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top/>
@@ -807,153 +911,14 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -1082,7 +1047,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1094,119 +1059,119 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1264,6 +1229,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="1" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1294,7 +1262,10 @@
     <xf numFmtId="179" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1315,85 +1286,43 @@
     <xf numFmtId="178" fontId="1" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="1" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="179" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -1974,12 +1903,12 @@
       <c r="H1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="63">
-        <f>SUM(F2,F3,F4,F8,F13,F14,F17,F24,F25,F34)</f>
-        <v>127592646</v>
-      </c>
-    </row>
-    <row r="2" ht="15" spans="1:10">
+      <c r="J1" s="51">
+        <f>SUM(F2,F3,F4,F8,F13,F14,F17,F24,F25,F34,F46)</f>
+        <v>129392646</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="12" t="s">
         <v>6</v>
       </c>
@@ -2004,7 +1933,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="15" spans="1:8">
+    <row r="3" ht="15" spans="1:10">
       <c r="A3" s="17"/>
       <c r="B3" s="13" t="s">
         <v>11</v>
@@ -2023,11 +1952,14 @@
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="16"/>
+      <c r="J3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4" ht="15" spans="1:10">
       <c r="A4" s="17"/>
       <c r="B4" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>8</v>
@@ -2044,13 +1976,13 @@
       <c r="G4" s="15"/>
       <c r="H4" s="16"/>
       <c r="J4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" ht="15" spans="1:8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="1:10">
       <c r="A5" s="17"/>
       <c r="B5" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>8</v>
@@ -2066,11 +1998,14 @@
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="16"/>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="1:10">
       <c r="A6" s="17"/>
       <c r="B6" s="13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>8</v>
@@ -2087,13 +2022,13 @@
       <c r="G6" s="15"/>
       <c r="H6" s="16"/>
       <c r="J6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" ht="15" spans="1:10">
       <c r="A7" s="17"/>
       <c r="B7" s="13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>8</v>
@@ -2109,11 +2044,14 @@
       </c>
       <c r="G7" s="15"/>
       <c r="H7" s="16"/>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="J7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="1:10">
       <c r="A8" s="17"/>
       <c r="B8" s="13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>8</v>
@@ -2129,46 +2067,52 @@
       </c>
       <c r="G8" s="15"/>
       <c r="H8" s="16"/>
+      <c r="J8" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="9" ht="15" spans="1:8">
       <c r="A9" s="17"/>
       <c r="B9" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>25</v>
       </c>
       <c r="D9" s="15"/>
-      <c r="E9" s="18" t="s">
-        <v>21</v>
+      <c r="E9" s="19" t="s">
+        <v>25</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" ht="15" spans="1:8">
+    <row r="10" ht="15" spans="1:10">
       <c r="A10" s="17"/>
       <c r="B10" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>21</v>
+        <v>26</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>25</v>
       </c>
       <c r="D10" s="15"/>
-      <c r="E10" s="18" t="s">
-        <v>21</v>
+      <c r="E10" s="19" t="s">
+        <v>25</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
       <c r="H10" s="16"/>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="J10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:12">
       <c r="A11" s="17"/>
       <c r="B11" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>25</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="14" t="s">
@@ -2179,12 +2123,15 @@
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="16"/>
-      <c r="L11" s="63"/>
-    </row>
-    <row r="12" ht="15" spans="1:8">
+      <c r="J11" t="s">
+        <v>29</v>
+      </c>
+      <c r="L11" s="51"/>
+    </row>
+    <row r="12" ht="15" spans="1:10">
       <c r="A12" s="17"/>
       <c r="B12" s="13" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>8</v>
@@ -2198,11 +2145,14 @@
       </c>
       <c r="G12" s="15"/>
       <c r="H12" s="16"/>
-    </row>
-    <row r="13" ht="15" spans="1:8">
+      <c r="J12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" ht="15" spans="1:10">
       <c r="A13" s="17"/>
       <c r="B13" s="13" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>8</v>
@@ -2218,11 +2168,14 @@
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="16"/>
+      <c r="J13" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="14" ht="15" spans="1:8">
       <c r="A14" s="17"/>
       <c r="B14" s="13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>8</v>
@@ -2238,49 +2191,49 @@
       <c r="H14" s="16"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="19"/>
-      <c r="B15" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="22">
+      <c r="A15" s="20"/>
+      <c r="B15" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="23"/>
+      <c r="E15" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="23">
         <v>2320000</v>
       </c>
-      <c r="G15" s="22"/>
-      <c r="H15" s="23"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="27">
+      <c r="G15" s="23"/>
+      <c r="H15" s="24"/>
+    </row>
+    <row r="16" ht="15" spans="1:8">
+      <c r="A16" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="28">
         <v>20669000</v>
       </c>
-      <c r="E16" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="27">
+      <c r="E16" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="28">
         <v>13909500</v>
       </c>
-      <c r="G16" s="27"/>
-      <c r="H16" s="28"/>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="G16" s="28"/>
+      <c r="H16" s="29"/>
+    </row>
+    <row r="17" ht="15" spans="1:8">
       <c r="A17" s="17"/>
       <c r="B17" s="13" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>8</v>
@@ -2297,10 +2250,10 @@
       <c r="G17" s="15"/>
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" ht="15" spans="1:8">
       <c r="A18" s="17"/>
       <c r="B18" s="13" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>8</v>
@@ -2317,10 +2270,10 @@
       <c r="G18" s="15"/>
       <c r="H18" s="16"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" ht="15" spans="1:8">
       <c r="A19" s="17"/>
       <c r="B19" s="13" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>8</v>
@@ -2340,14 +2293,14 @@
     <row r="20" ht="15" spans="1:8">
       <c r="A20" s="17"/>
       <c r="B20" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>21</v>
+        <v>39</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>25</v>
       </c>
       <c r="D20" s="15"/>
-      <c r="E20" s="18" t="s">
-        <v>21</v>
+      <c r="E20" s="19" t="s">
+        <v>25</v>
       </c>
       <c r="F20" s="15"/>
       <c r="G20" s="15"/>
@@ -2356,7 +2309,7 @@
     <row r="21" spans="1:8">
       <c r="A21" s="17"/>
       <c r="B21" s="13" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>8</v>
@@ -2373,10 +2326,10 @@
       <c r="G21" s="15"/>
       <c r="H21" s="16"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" ht="15" spans="1:8">
       <c r="A22" s="17"/>
       <c r="B22" s="13" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C22" s="14" t="s">
         <v>8</v>
@@ -2384,17 +2337,17 @@
       <c r="D22" s="15">
         <v>2410000</v>
       </c>
-      <c r="E22" s="18" t="s">
-        <v>21</v>
+      <c r="E22" s="19" t="s">
+        <v>25</v>
       </c>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
       <c r="H22" s="16"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" ht="15" spans="1:8">
       <c r="A23" s="17"/>
       <c r="B23" s="13" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>8</v>
@@ -2411,13 +2364,13 @@
       <c r="G23" s="15"/>
       <c r="H23" s="16"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" ht="15" spans="1:8">
       <c r="A24" s="17"/>
       <c r="B24" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="29" t="s">
-        <v>38</v>
+        <v>43</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>44</v>
       </c>
       <c r="D24" s="15"/>
       <c r="E24" s="18" t="s">
@@ -2429,10 +2382,10 @@
       <c r="G24" s="15"/>
       <c r="H24" s="16"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" ht="15" spans="1:8">
       <c r="A25" s="17"/>
       <c r="B25" s="13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>8</v>
@@ -2449,10 +2402,10 @@
       <c r="G25" s="15"/>
       <c r="H25" s="16"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" ht="15" spans="1:8">
       <c r="A26" s="17"/>
       <c r="B26" s="13" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C26" s="14" t="s">
         <v>8</v>
@@ -2469,10 +2422,10 @@
       <c r="G26" s="15"/>
       <c r="H26" s="16"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" ht="15" spans="1:8">
       <c r="A27" s="17"/>
       <c r="B27" s="13" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>8</v>
@@ -2492,23 +2445,23 @@
     <row r="28" ht="15" spans="1:8">
       <c r="A28" s="17"/>
       <c r="B28" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" s="29" t="s">
-        <v>21</v>
+        <v>48</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>25</v>
       </c>
       <c r="D28" s="15"/>
-      <c r="E28" s="18" t="s">
-        <v>21</v>
+      <c r="E28" s="19" t="s">
+        <v>25</v>
       </c>
       <c r="F28" s="15"/>
       <c r="G28" s="15"/>
       <c r="H28" s="16"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" ht="15" spans="1:8">
       <c r="A29" s="17"/>
       <c r="B29" s="13" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>8</v>
@@ -2516,17 +2469,17 @@
       <c r="D29" s="15">
         <v>3948000</v>
       </c>
-      <c r="E29" s="18" t="s">
-        <v>21</v>
+      <c r="E29" s="19" t="s">
+        <v>25</v>
       </c>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="16"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" ht="15" spans="1:8">
       <c r="A30" s="17"/>
       <c r="B30" s="13" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C30" s="14" t="s">
         <v>8</v>
@@ -2534,8 +2487,8 @@
       <c r="D30" s="15">
         <v>250000</v>
       </c>
-      <c r="E30" s="18" t="s">
-        <v>21</v>
+      <c r="E30" s="19" t="s">
+        <v>25</v>
       </c>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
@@ -2544,63 +2497,63 @@
     <row r="31" ht="15" spans="1:8">
       <c r="A31" s="17"/>
       <c r="B31" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" s="29" t="s">
-        <v>21</v>
+        <v>51</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>25</v>
       </c>
       <c r="D31" s="15"/>
-      <c r="E31" s="18" t="s">
-        <v>21</v>
+      <c r="E31" s="19" t="s">
+        <v>25</v>
       </c>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
+      <c r="H31" s="16"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="17"/>
-      <c r="B32" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="32"/>
-      <c r="E32" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="32">
+      <c r="A32" s="20"/>
+      <c r="B32" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="34"/>
+      <c r="E32" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="34">
         <v>915750</v>
       </c>
-      <c r="G32" s="32"/>
-      <c r="H32" s="33"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C33" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="27">
+      <c r="G32" s="34"/>
+      <c r="H32" s="35"/>
+    </row>
+    <row r="33" ht="15" spans="1:8">
+      <c r="A33" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="28">
         <v>4897000</v>
       </c>
-      <c r="E33" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="27">
+      <c r="E33" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="28">
         <v>8368100</v>
       </c>
-      <c r="G33" s="27"/>
-      <c r="H33" s="28"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="35"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="29"/>
+    </row>
+    <row r="34" ht="15" spans="1:8">
+      <c r="A34" s="37"/>
       <c r="B34" s="13" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C34" s="14" t="s">
         <v>8</v>
@@ -2608,7 +2561,7 @@
       <c r="D34" s="15">
         <v>4375000</v>
       </c>
-      <c r="E34" s="29" t="s">
+      <c r="E34" s="38" t="s">
         <v>12</v>
       </c>
       <c r="F34" s="15">
@@ -2618,9 +2571,9 @@
       <c r="H34" s="16"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="35"/>
+      <c r="A35" s="37"/>
       <c r="B35" s="13" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>8</v>
@@ -2638,173 +2591,186 @@
       <c r="H35" s="16"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="36"/>
-      <c r="B36" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="22">
+      <c r="A36" s="12"/>
+      <c r="B36" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="41">
         <v>1168000</v>
       </c>
-      <c r="E36" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="22">
+      <c r="E36" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="41">
         <v>893000</v>
       </c>
-      <c r="G36" s="22"/>
-      <c r="H36" s="23"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="42"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="B37" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="39"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="27">
+      <c r="A37" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" s="15">
         <v>1020000</v>
       </c>
-      <c r="G37" s="40"/>
-      <c r="H37" s="28"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="15"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="41"/>
-      <c r="B38" s="42" t="s">
-        <v>54</v>
+      <c r="A38" s="45"/>
+      <c r="B38" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="C38" s="18"/>
-      <c r="D38" s="43"/>
+      <c r="D38" s="44"/>
       <c r="E38" s="14" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="15">
         <v>1350000</v>
       </c>
-      <c r="G38" s="43"/>
-      <c r="H38" s="16"/>
+      <c r="G38" s="44"/>
+      <c r="H38" s="15"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="41"/>
-      <c r="B39" s="42" t="s">
-        <v>55</v>
+      <c r="A39" s="45"/>
+      <c r="B39" s="13" t="s">
+        <v>61</v>
       </c>
       <c r="C39" s="18"/>
-      <c r="D39" s="43"/>
+      <c r="D39" s="44"/>
       <c r="E39" s="14" t="s">
         <v>8</v>
       </c>
       <c r="F39" s="15">
         <v>600000</v>
       </c>
-      <c r="G39" s="43"/>
-      <c r="H39" s="16"/>
+      <c r="G39" s="44"/>
+      <c r="H39" s="15"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="41"/>
-      <c r="B40" s="42" t="s">
-        <v>56</v>
+      <c r="A40" s="45"/>
+      <c r="B40" s="13" t="s">
+        <v>62</v>
       </c>
       <c r="C40" s="18"/>
-      <c r="D40" s="43"/>
+      <c r="D40" s="44"/>
       <c r="E40" s="14" t="s">
         <v>8</v>
       </c>
       <c r="F40" s="15">
         <v>318134</v>
       </c>
-      <c r="G40" s="43"/>
-      <c r="H40" s="16"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="15"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="41"/>
-      <c r="B41" s="42" t="s">
-        <v>57</v>
+      <c r="A41" s="45"/>
+      <c r="B41" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="C41" s="18"/>
-      <c r="D41" s="43"/>
+      <c r="D41" s="44"/>
       <c r="E41" s="14" t="s">
         <v>8</v>
       </c>
       <c r="F41" s="15">
         <v>248700</v>
       </c>
-      <c r="G41" s="43"/>
-      <c r="H41" s="16"/>
+      <c r="G41" s="44"/>
+      <c r="H41" s="15"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="41"/>
-      <c r="B42" s="42" t="s">
-        <v>58</v>
+      <c r="A42" s="45"/>
+      <c r="B42" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="C42" s="18"/>
-      <c r="D42" s="43"/>
+      <c r="D42" s="44"/>
       <c r="E42" s="14" t="s">
         <v>8</v>
       </c>
       <c r="F42" s="15">
         <v>1029180</v>
       </c>
-      <c r="G42" s="43"/>
-      <c r="H42" s="16"/>
+      <c r="G42" s="44"/>
+      <c r="H42" s="15"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="41"/>
-      <c r="B43" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="C43" s="45"/>
-      <c r="D43" s="46"/>
-      <c r="E43" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="48">
+      <c r="A43" s="45"/>
+      <c r="B43" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C43" s="18"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="15">
         <v>270000</v>
       </c>
-      <c r="G43" s="46"/>
-      <c r="H43" s="49"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="15"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="41"/>
-      <c r="B44" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="C44" s="51"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="54">
+      <c r="A44" s="45"/>
+      <c r="B44" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" s="18"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="15">
         <v>1000000</v>
       </c>
-      <c r="G44" s="52"/>
-      <c r="H44" s="55"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="15"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="56"/>
-      <c r="B45" s="57" t="s">
-        <v>61</v>
-      </c>
-      <c r="C45" s="58"/>
-      <c r="D45" s="59"/>
-      <c r="E45" s="60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="61">
+      <c r="A45" s="45"/>
+      <c r="B45" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C45" s="18"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="15">
         <v>3000000</v>
       </c>
-      <c r="G45" s="59"/>
-      <c r="H45" s="62"/>
-    </row>
-    <row r="46" spans="6:6">
-      <c r="F46" s="4"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="15"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="46"/>
+      <c r="B46" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="48"/>
+      <c r="D46" s="49"/>
+      <c r="E46" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="50">
+        <v>1800000</v>
+      </c>
+      <c r="G46" s="49"/>
+      <c r="H46" s="50"/>
     </row>
     <row r="47" spans="6:6">
       <c r="F47" s="4"/>
@@ -2832,7 +2798,7 @@
     <mergeCell ref="A2:A15"/>
     <mergeCell ref="A16:A32"/>
     <mergeCell ref="A33:A36"/>
-    <mergeCell ref="A37:A45"/>
+    <mergeCell ref="A37:A46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7500"/>
+    <workbookView windowHeight="16040"/>
   </bookViews>
   <sheets>
     <sheet name="SUPPLIER PAYMENT STATUS" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="71">
   <si>
     <t>DIVISION</t>
   </si>
@@ -234,6 +234,12 @@
   </si>
   <si>
     <t>BAR CHILLER MAINTENANCE</t>
+  </si>
+  <si>
+    <t>LEGEND:</t>
+  </si>
+  <si>
+    <t>NO ORDER</t>
   </si>
 </sst>
 </file>
@@ -241,12 +247,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="6">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    <numFmt numFmtId="181" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -706,21 +712,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -738,21 +729,6 @@
         <color auto="1"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="thin">
@@ -806,13 +782,41 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -822,75 +826,6 @@
         <color auto="1"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="thin">
@@ -921,6 +856,77 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1029,16 +1035,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1171,11 +1177,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1184,10 +1190,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1196,58 +1202,40 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1256,16 +1244,28 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1274,58 +1274,52 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1862,20 +1856,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultColWidth="9.16190476190476" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="18.8571428571429" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.3333333333333" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.3333333333333" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.3333333333333" customWidth="1"/>
-    <col min="5" max="5" width="12.5714285714286" style="3" customWidth="1"/>
-    <col min="6" max="7" width="13.6666666666667" customWidth="1"/>
-    <col min="8" max="8" width="13.6666666666667" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.3333333333333"/>
-    <col min="10" max="10" width="15.4285714285714"/>
-    <col min="11" max="11" width="14.3333333333333"/>
-    <col min="12" max="12" width="22.6666666666667" customWidth="1"/>
-    <col min="13" max="13" width="11.6666666666667"/>
+    <col min="1" max="1" width="18.859375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.3359375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.3359375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.3359375" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" style="3" customWidth="1"/>
+    <col min="6" max="7" width="13.6640625" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="14.3359375"/>
+    <col min="10" max="10" width="15.4296875"/>
+    <col min="11" max="11" width="14.3359375"/>
+    <col min="12" max="12" width="22.6640625" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1891,886 +1885,886 @@
       <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="38" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="51">
+      <c r="J1" s="47">
         <f>SUM(F2,F3,F4,F8,F13,F14,F17,F24,F25,F34,F46)</f>
         <v>129392646</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="12" t="s">
+    <row r="2" ht="16.8" spans="1:10">
+      <c r="A2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="15">
+      <c r="C2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="12">
         <v>66835000</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="12">
         <v>39738000</v>
       </c>
-      <c r="G2" s="15"/>
-      <c r="H2" s="16"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="41"/>
       <c r="J2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="15" spans="1:10">
-      <c r="A3" s="17"/>
-      <c r="B3" s="13" t="s">
+    <row r="3" ht="16.8" spans="1:10">
+      <c r="A3" s="13"/>
+      <c r="B3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="15">
+      <c r="C3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="12">
         <v>45478060</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="12">
         <v>39027410</v>
       </c>
-      <c r="G3" s="15"/>
-      <c r="H3" s="16"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="41"/>
       <c r="J3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="1:10">
-      <c r="A4" s="17"/>
-      <c r="B4" s="13" t="s">
+    <row r="4" ht="16.8" spans="1:10">
+      <c r="A4" s="13"/>
+      <c r="B4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="15">
+      <c r="C4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="12">
         <v>29900100</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="12">
         <v>20617200</v>
       </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="16"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="41"/>
       <c r="J4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="1:10">
-      <c r="A5" s="17"/>
-      <c r="B5" s="13" t="s">
+    <row r="5" ht="16.8" spans="1:10">
+      <c r="A5" s="13"/>
+      <c r="B5" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="15">
+      <c r="C5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="12">
         <v>4400000</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="15">
+      <c r="E5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="12">
         <v>5560000</v>
       </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="16"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="41"/>
       <c r="J5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="1:10">
-      <c r="A6" s="17"/>
-      <c r="B6" s="13" t="s">
+    <row r="6" ht="16.8" spans="1:10">
+      <c r="A6" s="13"/>
+      <c r="B6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="15">
+      <c r="C6" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="12">
         <v>5610900</v>
       </c>
-      <c r="E6" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="15">
+      <c r="E6" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="12">
         <v>3578050</v>
       </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="16"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="41"/>
       <c r="J6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" ht="15" spans="1:10">
-      <c r="A7" s="17"/>
-      <c r="B7" s="13" t="s">
+    <row r="7" ht="16.8" spans="1:10">
+      <c r="A7" s="13"/>
+      <c r="B7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="15">
+      <c r="C7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="12">
         <v>3663300</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="15">
+      <c r="E7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="12">
         <v>1983600</v>
       </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="41"/>
       <c r="J7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="15" spans="1:10">
-      <c r="A8" s="17"/>
-      <c r="B8" s="13" t="s">
+    <row r="8" ht="16.8" spans="1:10">
+      <c r="A8" s="13"/>
+      <c r="B8" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="15">
+      <c r="C8" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="12">
         <v>8775000</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="12">
         <v>7800000</v>
       </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="16"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="41"/>
       <c r="J8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="1:8">
-      <c r="A9" s="17"/>
-      <c r="B9" s="13" t="s">
+    <row r="9" ht="16.8" spans="1:8">
+      <c r="A9" s="13"/>
+      <c r="B9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="19" t="s">
+      <c r="D9" s="12"/>
+      <c r="E9" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="16"/>
-    </row>
-    <row r="10" ht="15" spans="1:10">
-      <c r="A10" s="17"/>
-      <c r="B10" s="13" t="s">
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="41"/>
+    </row>
+    <row r="10" ht="16.8" spans="1:10">
+      <c r="A10" s="13"/>
+      <c r="B10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="19" t="s">
+      <c r="D10" s="12"/>
+      <c r="E10" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="16"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="41"/>
       <c r="J10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="1:12">
-      <c r="A11" s="17"/>
-      <c r="B11" s="13" t="s">
+    <row r="11" ht="16.8" spans="1:12">
+      <c r="A11" s="13"/>
+      <c r="B11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="15">
+      <c r="D11" s="12"/>
+      <c r="E11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="12">
         <v>326000</v>
       </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="16"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="41"/>
       <c r="J11" t="s">
         <v>29</v>
       </c>
-      <c r="L11" s="51"/>
-    </row>
-    <row r="12" ht="15" spans="1:10">
-      <c r="A12" s="17"/>
-      <c r="B12" s="13" t="s">
+      <c r="L11" s="47"/>
+    </row>
+    <row r="12" ht="16.8" spans="1:10">
+      <c r="A12" s="13"/>
+      <c r="B12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="15">
+      <c r="C12" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="12">
         <v>924000</v>
       </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="16"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="41"/>
       <c r="J12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" ht="15" spans="1:10">
-      <c r="A13" s="17"/>
-      <c r="B13" s="13" t="s">
+    <row r="13" ht="16.8" spans="1:10">
+      <c r="A13" s="13"/>
+      <c r="B13" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="15">
+      <c r="C13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="12">
         <v>4375000</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="12">
         <v>4715000</v>
       </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="16"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="41"/>
       <c r="J13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" ht="15" spans="1:8">
-      <c r="A14" s="17"/>
-      <c r="B14" s="13" t="s">
+    <row r="14" ht="16.8" spans="1:8">
+      <c r="A14" s="13"/>
+      <c r="B14" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="18" t="s">
+      <c r="C14" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="12"/>
+      <c r="E14" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="12">
         <v>1525000</v>
       </c>
-      <c r="G14" s="15"/>
-      <c r="H14" s="16"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="20"/>
-      <c r="B15" s="21" t="s">
+      <c r="G14" s="12"/>
+      <c r="H14" s="41"/>
+    </row>
+    <row r="15" ht="17.55" spans="1:8">
+      <c r="A15" s="15"/>
+      <c r="B15" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="23"/>
-      <c r="E15" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="23">
+      <c r="C15" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="18"/>
+      <c r="E15" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="18">
         <v>2320000</v>
       </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="24"/>
-    </row>
-    <row r="16" ht="15" spans="1:8">
-      <c r="A16" s="25" t="s">
+      <c r="G15" s="18"/>
+      <c r="H15" s="42"/>
+    </row>
+    <row r="16" ht="16.8" spans="1:8">
+      <c r="A16" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="28">
+      <c r="C16" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="22">
         <v>20669000</v>
       </c>
-      <c r="E16" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="28">
+      <c r="E16" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="22">
         <v>13909500</v>
       </c>
-      <c r="G16" s="28"/>
-      <c r="H16" s="29"/>
-    </row>
-    <row r="17" ht="15" spans="1:8">
-      <c r="A17" s="17"/>
-      <c r="B17" s="13" t="s">
+      <c r="G16" s="22"/>
+      <c r="H16" s="43"/>
+    </row>
+    <row r="17" ht="16.8" spans="1:8">
+      <c r="A17" s="13"/>
+      <c r="B17" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="15">
+      <c r="C17" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="12">
         <v>3230000</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="12">
         <v>2415000</v>
       </c>
-      <c r="G17" s="15"/>
-      <c r="H17" s="16"/>
-    </row>
-    <row r="18" ht="15" spans="1:8">
-      <c r="A18" s="17"/>
-      <c r="B18" s="13" t="s">
+      <c r="G17" s="12"/>
+      <c r="H17" s="41"/>
+    </row>
+    <row r="18" ht="16.8" spans="1:8">
+      <c r="A18" s="13"/>
+      <c r="B18" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="15">
+      <c r="C18" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="12">
         <v>10775000</v>
       </c>
-      <c r="E18" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="15">
+      <c r="E18" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="12">
         <v>10000000</v>
       </c>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16"/>
-    </row>
-    <row r="19" ht="15" spans="1:8">
-      <c r="A19" s="17"/>
-      <c r="B19" s="13" t="s">
+      <c r="G18" s="12"/>
+      <c r="H18" s="41"/>
+    </row>
+    <row r="19" ht="16.8" spans="1:8">
+      <c r="A19" s="13"/>
+      <c r="B19" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="15">
+      <c r="C19" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="12">
         <v>10023000</v>
       </c>
-      <c r="E19" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="15">
+      <c r="E19" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="12">
         <v>6637500</v>
       </c>
-      <c r="G19" s="15"/>
-      <c r="H19" s="16"/>
-    </row>
-    <row r="20" ht="15" spans="1:8">
-      <c r="A20" s="17"/>
-      <c r="B20" s="13" t="s">
+      <c r="G19" s="12"/>
+      <c r="H19" s="41"/>
+    </row>
+    <row r="20" ht="16.8" spans="1:8">
+      <c r="A20" s="13"/>
+      <c r="B20" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="19" t="s">
+      <c r="D20" s="12"/>
+      <c r="E20" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="16"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="17"/>
-      <c r="B21" s="13" t="s">
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="41"/>
+    </row>
+    <row r="21" ht="16.8" spans="1:8">
+      <c r="A21" s="13"/>
+      <c r="B21" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="15">
+      <c r="C21" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="12">
         <v>3663000</v>
       </c>
-      <c r="E21" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="15">
+      <c r="E21" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="12">
         <v>1998000</v>
       </c>
-      <c r="G21" s="15"/>
-      <c r="H21" s="16"/>
-    </row>
-    <row r="22" ht="15" spans="1:8">
-      <c r="A22" s="17"/>
-      <c r="B22" s="13" t="s">
+      <c r="G21" s="12"/>
+      <c r="H21" s="41"/>
+    </row>
+    <row r="22" ht="16.8" spans="1:8">
+      <c r="A22" s="13"/>
+      <c r="B22" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="15">
+      <c r="C22" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="12">
         <v>2410000</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="16"/>
-    </row>
-    <row r="23" ht="15" spans="1:8">
-      <c r="A23" s="17"/>
-      <c r="B23" s="13" t="s">
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="41"/>
+    </row>
+    <row r="23" ht="16.8" spans="1:8">
+      <c r="A23" s="13"/>
+      <c r="B23" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="15">
+      <c r="C23" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="12">
         <v>2447502</v>
       </c>
-      <c r="E23" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="15">
+      <c r="E23" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="12">
         <v>1312502</v>
       </c>
-      <c r="G23" s="15"/>
-      <c r="H23" s="16"/>
-    </row>
-    <row r="24" ht="15" spans="1:8">
-      <c r="A24" s="17"/>
-      <c r="B24" s="13" t="s">
+      <c r="G23" s="12"/>
+      <c r="H23" s="41"/>
+    </row>
+    <row r="24" ht="16.8" spans="1:8">
+      <c r="A24" s="13"/>
+      <c r="B24" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="18" t="s">
+      <c r="D24" s="12"/>
+      <c r="E24" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="12">
         <v>2280000</v>
       </c>
-      <c r="G24" s="15"/>
-      <c r="H24" s="16"/>
-    </row>
-    <row r="25" ht="15" spans="1:8">
-      <c r="A25" s="17"/>
-      <c r="B25" s="13" t="s">
+      <c r="G24" s="12"/>
+      <c r="H24" s="41"/>
+    </row>
+    <row r="25" ht="16.8" spans="1:8">
+      <c r="A25" s="13"/>
+      <c r="B25" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C25" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="15">
+      <c r="C25" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="12">
         <v>4760036</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="12">
         <v>4760036</v>
       </c>
-      <c r="G25" s="15"/>
-      <c r="H25" s="16"/>
-    </row>
-    <row r="26" ht="15" spans="1:8">
-      <c r="A26" s="17"/>
-      <c r="B26" s="13" t="s">
+      <c r="G25" s="12"/>
+      <c r="H25" s="41"/>
+    </row>
+    <row r="26" ht="16.8" spans="1:8">
+      <c r="A26" s="13"/>
+      <c r="B26" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="15">
+      <c r="C26" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="12">
         <v>5600000</v>
       </c>
-      <c r="E26" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="15">
+      <c r="E26" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="12">
         <v>5600000</v>
       </c>
-      <c r="G26" s="15"/>
-      <c r="H26" s="16"/>
-    </row>
-    <row r="27" ht="15" spans="1:8">
-      <c r="A27" s="17"/>
-      <c r="B27" s="13" t="s">
+      <c r="G26" s="12"/>
+      <c r="H26" s="41"/>
+    </row>
+    <row r="27" ht="16.8" spans="1:8">
+      <c r="A27" s="13"/>
+      <c r="B27" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="15">
+      <c r="C27" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="12">
         <v>1225000</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="15">
+      <c r="E27" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="12">
         <v>915750</v>
       </c>
-      <c r="G27" s="15"/>
-      <c r="H27" s="16"/>
-    </row>
-    <row r="28" ht="15" spans="1:8">
-      <c r="A28" s="17"/>
-      <c r="B28" s="13" t="s">
+      <c r="G27" s="12"/>
+      <c r="H27" s="41"/>
+    </row>
+    <row r="28" ht="16.8" spans="1:8">
+      <c r="A28" s="13"/>
+      <c r="B28" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="31" t="s">
+      <c r="C28" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="19" t="s">
+      <c r="D28" s="12"/>
+      <c r="E28" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="16"/>
-    </row>
-    <row r="29" ht="15" spans="1:8">
-      <c r="A29" s="17"/>
-      <c r="B29" s="13" t="s">
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="41"/>
+    </row>
+    <row r="29" ht="16.8" spans="1:8">
+      <c r="A29" s="13"/>
+      <c r="B29" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="15">
+      <c r="C29" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="12">
         <v>3948000</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="16"/>
-    </row>
-    <row r="30" ht="15" spans="1:8">
-      <c r="A30" s="17"/>
-      <c r="B30" s="13" t="s">
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="41"/>
+    </row>
+    <row r="30" ht="16.8" spans="1:8">
+      <c r="A30" s="13"/>
+      <c r="B30" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="15">
+      <c r="C30" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="12">
         <v>250000</v>
       </c>
-      <c r="E30" s="19" t="s">
+      <c r="E30" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="16"/>
-    </row>
-    <row r="31" ht="15" spans="1:8">
-      <c r="A31" s="17"/>
-      <c r="B31" s="13" t="s">
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="41"/>
+    </row>
+    <row r="31" ht="16.8" spans="1:8">
+      <c r="A31" s="13"/>
+      <c r="B31" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="31" t="s">
+      <c r="C31" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="19" t="s">
+      <c r="D31" s="12"/>
+      <c r="E31" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="16"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="20"/>
-      <c r="B32" s="32" t="s">
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="41"/>
+    </row>
+    <row r="32" ht="17.55" spans="1:8">
+      <c r="A32" s="15"/>
+      <c r="B32" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="C32" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="34"/>
-      <c r="E32" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="34">
+      <c r="C32" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="27"/>
+      <c r="E32" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="27">
         <v>915750</v>
       </c>
-      <c r="G32" s="34"/>
-      <c r="H32" s="35"/>
-    </row>
-    <row r="33" ht="15" spans="1:8">
-      <c r="A33" s="36" t="s">
+      <c r="G32" s="27"/>
+      <c r="H32" s="44"/>
+    </row>
+    <row r="33" ht="16.8" spans="1:8">
+      <c r="A33" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B33" s="26" t="s">
+      <c r="B33" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="28">
+      <c r="C33" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="22">
         <v>4897000</v>
       </c>
-      <c r="E33" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="28">
+      <c r="E33" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="22">
         <v>8368100</v>
       </c>
-      <c r="G33" s="28"/>
-      <c r="H33" s="29"/>
-    </row>
-    <row r="34" ht="15" spans="1:8">
-      <c r="A34" s="37"/>
-      <c r="B34" s="13" t="s">
+      <c r="G33" s="22"/>
+      <c r="H33" s="43"/>
+    </row>
+    <row r="34" ht="16.8" spans="1:8">
+      <c r="A34" s="29"/>
+      <c r="B34" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="15">
+      <c r="C34" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="12">
         <v>4375000</v>
       </c>
-      <c r="E34" s="38" t="s">
+      <c r="E34" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="12">
         <v>4715000</v>
       </c>
-      <c r="G34" s="15"/>
-      <c r="H34" s="16"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="37"/>
-      <c r="B35" s="13" t="s">
+      <c r="G34" s="12"/>
+      <c r="H34" s="41"/>
+    </row>
+    <row r="35" ht="16.8" spans="1:8">
+      <c r="A35" s="29"/>
+      <c r="B35" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="15">
+      <c r="C35" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="12">
         <v>1007480.64</v>
       </c>
-      <c r="E35" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="15">
+      <c r="E35" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="12">
         <v>638483</v>
       </c>
-      <c r="G35" s="15"/>
-      <c r="H35" s="16"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="12"/>
-      <c r="B36" s="39" t="s">
+      <c r="G35" s="12"/>
+      <c r="H35" s="41"/>
+    </row>
+    <row r="36" ht="16.8" spans="1:8">
+      <c r="A36" s="9"/>
+      <c r="B36" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="41">
+      <c r="C36" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="32">
         <v>1168000</v>
       </c>
-      <c r="E36" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="41">
+      <c r="E36" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="32">
         <v>893000</v>
       </c>
-      <c r="G36" s="41"/>
-      <c r="H36" s="42"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="43" t="s">
+      <c r="G36" s="32"/>
+      <c r="H36" s="46"/>
+    </row>
+    <row r="37" ht="16.8" spans="1:8">
+      <c r="A37" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="44"/>
-      <c r="E37" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="15">
+      <c r="C37" s="34"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" s="12">
         <v>1020000</v>
       </c>
-      <c r="G37" s="44"/>
-      <c r="H37" s="15"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="45"/>
-      <c r="B38" s="13" t="s">
+      <c r="G37" s="35"/>
+      <c r="H37" s="12"/>
+    </row>
+    <row r="38" ht="16.8" spans="1:8">
+      <c r="A38" s="36"/>
+      <c r="B38" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="44"/>
-      <c r="E38" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="15">
+      <c r="C38" s="34"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="12">
         <v>1350000</v>
       </c>
-      <c r="G38" s="44"/>
-      <c r="H38" s="15"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="45"/>
-      <c r="B39" s="13" t="s">
+      <c r="G38" s="35"/>
+      <c r="H38" s="12"/>
+    </row>
+    <row r="39" ht="16.8" spans="1:8">
+      <c r="A39" s="36"/>
+      <c r="B39" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="15">
+      <c r="C39" s="34"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" s="12">
         <v>600000</v>
       </c>
-      <c r="G39" s="44"/>
-      <c r="H39" s="15"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="45"/>
-      <c r="B40" s="13" t="s">
+      <c r="G39" s="35"/>
+      <c r="H39" s="12"/>
+    </row>
+    <row r="40" ht="16.8" spans="1:8">
+      <c r="A40" s="36"/>
+      <c r="B40" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="44"/>
-      <c r="E40" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="15">
+      <c r="C40" s="34"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" s="12">
         <v>318134</v>
       </c>
-      <c r="G40" s="44"/>
-      <c r="H40" s="15"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="45"/>
-      <c r="B41" s="13" t="s">
+      <c r="G40" s="35"/>
+      <c r="H40" s="12"/>
+    </row>
+    <row r="41" ht="16.8" spans="1:8">
+      <c r="A41" s="36"/>
+      <c r="B41" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C41" s="18"/>
-      <c r="D41" s="44"/>
-      <c r="E41" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="15">
+      <c r="C41" s="34"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="12">
         <v>248700</v>
       </c>
-      <c r="G41" s="44"/>
-      <c r="H41" s="15"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="45"/>
-      <c r="B42" s="13" t="s">
+      <c r="G41" s="35"/>
+      <c r="H41" s="12"/>
+    </row>
+    <row r="42" ht="16.8" spans="1:8">
+      <c r="A42" s="36"/>
+      <c r="B42" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C42" s="18"/>
-      <c r="D42" s="44"/>
-      <c r="E42" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="15">
+      <c r="C42" s="34"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="12">
         <v>1029180</v>
       </c>
-      <c r="G42" s="44"/>
-      <c r="H42" s="15"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="45"/>
-      <c r="B43" s="13" t="s">
+      <c r="G42" s="35"/>
+      <c r="H42" s="12"/>
+    </row>
+    <row r="43" ht="16.8" spans="1:8">
+      <c r="A43" s="36"/>
+      <c r="B43" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C43" s="18"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="15">
+      <c r="C43" s="34"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="12">
         <v>270000</v>
       </c>
-      <c r="G43" s="44"/>
-      <c r="H43" s="15"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="45"/>
-      <c r="B44" s="13" t="s">
+      <c r="G43" s="35"/>
+      <c r="H43" s="12"/>
+    </row>
+    <row r="44" ht="16.8" spans="1:8">
+      <c r="A44" s="36"/>
+      <c r="B44" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="44"/>
-      <c r="E44" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="15">
+      <c r="C44" s="34"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="12">
         <v>1000000</v>
       </c>
-      <c r="G44" s="44"/>
-      <c r="H44" s="15"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="45"/>
-      <c r="B45" s="13" t="s">
+      <c r="G44" s="35"/>
+      <c r="H44" s="12"/>
+    </row>
+    <row r="45" ht="16.8" spans="1:8">
+      <c r="A45" s="36"/>
+      <c r="B45" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C45" s="18"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="15">
+      <c r="C45" s="34"/>
+      <c r="D45" s="35"/>
+      <c r="E45" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="12">
         <v>3000000</v>
       </c>
-      <c r="G45" s="44"/>
-      <c r="H45" s="15"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="46"/>
-      <c r="B46" s="47" t="s">
+      <c r="G45" s="35"/>
+      <c r="H45" s="12"/>
+    </row>
+    <row r="46" ht="16.8" spans="1:8">
+      <c r="A46" s="37"/>
+      <c r="B46" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C46" s="48"/>
-      <c r="D46" s="49"/>
-      <c r="E46" s="48" t="s">
+      <c r="C46" s="34"/>
+      <c r="D46" s="35"/>
+      <c r="E46" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="F46" s="50">
+      <c r="F46" s="12">
         <v>1800000</v>
       </c>
-      <c r="G46" s="49"/>
-      <c r="H46" s="50"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="12"/>
     </row>
     <row r="47" spans="6:6">
       <c r="F47" s="4"/>
@@ -2787,10 +2781,19 @@
     <row r="51" spans="6:6">
       <c r="F51" s="4"/>
     </row>
-    <row r="52" spans="6:6">
+    <row r="52" spans="1:6">
+      <c r="A52" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="F52" s="4"/>
     </row>
-    <row r="53" spans="6:6">
+    <row r="53" spans="1:6">
+      <c r="A53" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="F53" s="4"/>
     </row>
   </sheetData>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16040"/>
+    <workbookView windowWidth="19635" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="SUPPLIER PAYMENT STATUS" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="70">
   <si>
     <t>DIVISION</t>
   </si>
@@ -65,15 +65,15 @@
     <t>SEDANA JAYA</t>
   </si>
   <si>
+    <t>Sedana</t>
+  </si>
+  <si>
+    <t>RAFI SEAFOOD</t>
+  </si>
+  <si>
     <t>POSTED</t>
   </si>
   <si>
-    <t>Sedana</t>
-  </si>
-  <si>
-    <t>RAFI SEAFOOD</t>
-  </si>
-  <si>
     <t>Surbled</t>
   </si>
   <si>
@@ -159,9 +159,6 @@
   </si>
   <si>
     <t>NANO DEWATA</t>
-  </si>
-  <si>
-    <t>UNCHECKED</t>
   </si>
   <si>
     <t>BALI PERMATA JAYA</t>
@@ -247,12 +244,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="6">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-    <numFmt numFmtId="181" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -428,7 +425,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -473,12 +470,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -664,7 +655,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -712,6 +703,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -729,6 +735,21 @@
         <color auto="1"/>
       </left>
       <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="thin">
@@ -782,7 +803,35 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top/>
@@ -822,7 +871,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color auto="1"/>
       </left>
       <right style="thin">
@@ -831,7 +880,9 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -856,77 +907,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1035,16 +1015,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1053,7 +1033,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1065,115 +1045,115 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1181,7 +1161,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1190,10 +1170,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1202,40 +1182,58 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1244,28 +1242,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1274,52 +1257,49 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1856,20 +1836,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9.16190476190476" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="18.859375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.3359375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.3359375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.3359375" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="3" customWidth="1"/>
-    <col min="6" max="7" width="13.6640625" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.3359375"/>
-    <col min="10" max="10" width="15.4296875"/>
-    <col min="11" max="11" width="14.3359375"/>
-    <col min="12" max="12" width="22.6640625" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625"/>
+    <col min="1" max="1" width="18.8571428571429" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.3333333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.3333333333333" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="12.5714285714286" style="3" customWidth="1"/>
+    <col min="6" max="7" width="13.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="13.6666666666667" style="4" customWidth="1"/>
+    <col min="9" max="9" width="14.3333333333333"/>
+    <col min="10" max="10" width="15.4285714285714"/>
+    <col min="11" max="11" width="14.3333333333333"/>
+    <col min="12" max="12" width="22.6666666666667" customWidth="1"/>
+    <col min="13" max="13" width="11.6666666666667"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1885,886 +1865,886 @@
       <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="11" t="s">
         <v>3</v>
       </c>
       <c r="J1" s="47">
-        <f>SUM(F2,F3,F4,F8,F13,F14,F17,F24,F25,F34,F46)</f>
-        <v>129392646</v>
-      </c>
-    </row>
-    <row r="2" ht="16.8" spans="1:10">
-      <c r="A2" s="9" t="s">
+        <f>SUM(F2,F4,F8,F13,F14,F17,F24,F25,F34)</f>
+        <v>88565236</v>
+      </c>
+    </row>
+    <row r="2" ht="15" spans="1:10">
+      <c r="A2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="12">
+      <c r="C2" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="15">
         <v>66835000</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="15">
         <v>39738000</v>
       </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="41"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="16"/>
       <c r="J2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="16.8" spans="1:10">
-      <c r="A3" s="13"/>
-      <c r="B3" s="10" t="s">
+    <row r="3" ht="15" spans="1:10">
+      <c r="A3" s="17"/>
+      <c r="B3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="12">
+      <c r="C3" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="15">
         <v>45478060</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="15">
+        <v>39027410</v>
+      </c>
+      <c r="G3" s="15"/>
+      <c r="H3" s="16"/>
+      <c r="J3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="12">
-        <v>39027410</v>
-      </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="41"/>
-      <c r="J3" t="s">
+    </row>
+    <row r="4" ht="15" spans="1:10">
+      <c r="A4" s="17"/>
+      <c r="B4" s="13" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" ht="16.8" spans="1:10">
-      <c r="A4" s="13"/>
-      <c r="B4" s="10" t="s">
+      <c r="C4" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="15">
+        <v>29900100</v>
+      </c>
+      <c r="E4" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="12">
-        <v>29900100</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="12">
+      <c r="F4" s="15">
         <v>20617200</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="41"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="16"/>
       <c r="J4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="16.8" spans="1:10">
-      <c r="A5" s="13"/>
-      <c r="B5" s="10" t="s">
+    <row r="5" ht="15" spans="1:10">
+      <c r="A5" s="17"/>
+      <c r="B5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="12">
+      <c r="C5" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="15">
         <v>4400000</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="12">
+      <c r="E5" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="15">
         <v>5560000</v>
       </c>
-      <c r="G5" s="12"/>
-      <c r="H5" s="41"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="16"/>
       <c r="J5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="16.8" spans="1:10">
-      <c r="A6" s="13"/>
-      <c r="B6" s="10" t="s">
+    <row r="6" ht="15" spans="1:10">
+      <c r="A6" s="17"/>
+      <c r="B6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="12">
+      <c r="C6" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="15">
         <v>5610900</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="12">
+      <c r="E6" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="15">
         <v>3578050</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="41"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="16"/>
       <c r="J6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" ht="16.8" spans="1:10">
-      <c r="A7" s="13"/>
-      <c r="B7" s="10" t="s">
+    <row r="7" ht="15" spans="1:10">
+      <c r="A7" s="17"/>
+      <c r="B7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="12">
+      <c r="C7" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="15">
         <v>3663300</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="12">
+      <c r="E7" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="15">
         <v>1983600</v>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="41"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="16"/>
       <c r="J7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="16.8" spans="1:10">
-      <c r="A8" s="13"/>
-      <c r="B8" s="10" t="s">
+    <row r="8" ht="15" spans="1:10">
+      <c r="A8" s="17"/>
+      <c r="B8" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="12">
+      <c r="C8" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="15">
         <v>8775000</v>
       </c>
-      <c r="E8" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="12">
+      <c r="E8" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="15">
         <v>7800000</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="41"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="16"/>
       <c r="J8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" ht="16.8" spans="1:8">
-      <c r="A9" s="13"/>
-      <c r="B9" s="10" t="s">
+    <row r="9" ht="15" spans="1:8">
+      <c r="A9" s="17"/>
+      <c r="B9" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="14" t="s">
+      <c r="D9" s="15"/>
+      <c r="E9" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="41"/>
-    </row>
-    <row r="10" ht="16.8" spans="1:10">
-      <c r="A10" s="13"/>
-      <c r="B10" s="10" t="s">
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="16"/>
+    </row>
+    <row r="10" ht="15" spans="1:10">
+      <c r="A10" s="17"/>
+      <c r="B10" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="14" t="s">
+      <c r="D10" s="15"/>
+      <c r="E10" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="41"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="16"/>
       <c r="J10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" ht="16.8" spans="1:12">
-      <c r="A11" s="13"/>
-      <c r="B11" s="10" t="s">
+    <row r="11" ht="15" spans="1:12">
+      <c r="A11" s="17"/>
+      <c r="B11" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="12">
+      <c r="D11" s="15"/>
+      <c r="E11" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="15">
         <v>326000</v>
       </c>
-      <c r="G11" s="12"/>
-      <c r="H11" s="41"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="16"/>
       <c r="J11" t="s">
         <v>29</v>
       </c>
       <c r="L11" s="47"/>
     </row>
-    <row r="12" ht="16.8" spans="1:10">
-      <c r="A12" s="13"/>
-      <c r="B12" s="10" t="s">
+    <row r="12" ht="15" spans="1:10">
+      <c r="A12" s="17"/>
+      <c r="B12" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="12">
+      <c r="C12" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="15"/>
+      <c r="E12" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="15">
         <v>924000</v>
       </c>
-      <c r="G12" s="12"/>
-      <c r="H12" s="41"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="16"/>
       <c r="J12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" ht="16.8" spans="1:10">
-      <c r="A13" s="13"/>
-      <c r="B13" s="10" t="s">
+    <row r="13" ht="15" spans="1:10">
+      <c r="A13" s="17"/>
+      <c r="B13" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="12">
+      <c r="C13" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="15">
         <v>4375000</v>
       </c>
-      <c r="E13" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="12">
+      <c r="E13" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="15">
         <v>4715000</v>
       </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="41"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="16"/>
       <c r="J13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" ht="16.8" spans="1:8">
-      <c r="A14" s="13"/>
-      <c r="B14" s="10" t="s">
+    <row r="14" ht="15" spans="1:8">
+      <c r="A14" s="17"/>
+      <c r="B14" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="12">
+      <c r="C14" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="15">
         <v>1525000</v>
       </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="41"/>
-    </row>
-    <row r="15" ht="17.55" spans="1:8">
-      <c r="A15" s="15"/>
-      <c r="B15" s="16" t="s">
+      <c r="G14" s="15"/>
+      <c r="H14" s="16"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="20"/>
+      <c r="B15" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="18"/>
-      <c r="E15" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="18">
+      <c r="C15" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="23"/>
+      <c r="E15" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="23">
         <v>2320000</v>
       </c>
-      <c r="G15" s="18"/>
-      <c r="H15" s="42"/>
-    </row>
-    <row r="16" ht="16.8" spans="1:8">
-      <c r="A16" s="19" t="s">
+      <c r="G15" s="23"/>
+      <c r="H15" s="24"/>
+    </row>
+    <row r="16" ht="15" spans="1:8">
+      <c r="A16" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="22">
+      <c r="C16" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="28">
         <v>20669000</v>
       </c>
-      <c r="E16" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="22">
+      <c r="E16" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="28">
         <v>13909500</v>
       </c>
-      <c r="G16" s="22"/>
-      <c r="H16" s="43"/>
-    </row>
-    <row r="17" ht="16.8" spans="1:8">
-      <c r="A17" s="13"/>
-      <c r="B17" s="10" t="s">
+      <c r="G16" s="28"/>
+      <c r="H16" s="29"/>
+    </row>
+    <row r="17" ht="15" spans="1:8">
+      <c r="A17" s="17"/>
+      <c r="B17" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="12">
+      <c r="C17" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="15">
         <v>3230000</v>
       </c>
-      <c r="E17" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="12">
+      <c r="E17" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="15">
         <v>2415000</v>
       </c>
-      <c r="G17" s="12"/>
-      <c r="H17" s="41"/>
-    </row>
-    <row r="18" ht="16.8" spans="1:8">
-      <c r="A18" s="13"/>
-      <c r="B18" s="10" t="s">
+      <c r="G17" s="15"/>
+      <c r="H17" s="16"/>
+    </row>
+    <row r="18" ht="15" spans="1:8">
+      <c r="A18" s="17"/>
+      <c r="B18" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="12">
+      <c r="C18" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="15">
         <v>10775000</v>
       </c>
-      <c r="E18" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="12">
+      <c r="E18" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="15">
         <v>10000000</v>
       </c>
-      <c r="G18" s="12"/>
-      <c r="H18" s="41"/>
-    </row>
-    <row r="19" ht="16.8" spans="1:8">
-      <c r="A19" s="13"/>
-      <c r="B19" s="10" t="s">
+      <c r="G18" s="15"/>
+      <c r="H18" s="16"/>
+    </row>
+    <row r="19" ht="15" spans="1:8">
+      <c r="A19" s="17"/>
+      <c r="B19" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="12">
+      <c r="C19" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="15">
         <v>10023000</v>
       </c>
-      <c r="E19" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="12">
+      <c r="E19" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="15">
         <v>6637500</v>
       </c>
-      <c r="G19" s="12"/>
-      <c r="H19" s="41"/>
-    </row>
-    <row r="20" ht="16.8" spans="1:8">
-      <c r="A20" s="13"/>
-      <c r="B20" s="10" t="s">
+      <c r="G19" s="15"/>
+      <c r="H19" s="16"/>
+    </row>
+    <row r="20" ht="15" spans="1:8">
+      <c r="A20" s="17"/>
+      <c r="B20" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="14" t="s">
+      <c r="D20" s="15"/>
+      <c r="E20" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="41"/>
-    </row>
-    <row r="21" ht="16.8" spans="1:8">
-      <c r="A21" s="13"/>
-      <c r="B21" s="10" t="s">
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="16"/>
+    </row>
+    <row r="21" ht="15" spans="1:8">
+      <c r="A21" s="17"/>
+      <c r="B21" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="12">
+      <c r="C21" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="15">
         <v>3663000</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="12">
+      <c r="E21" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="15">
         <v>1998000</v>
       </c>
-      <c r="G21" s="12"/>
-      <c r="H21" s="41"/>
-    </row>
-    <row r="22" ht="16.8" spans="1:8">
-      <c r="A22" s="13"/>
-      <c r="B22" s="10" t="s">
+      <c r="G21" s="15"/>
+      <c r="H21" s="16"/>
+    </row>
+    <row r="22" ht="15" spans="1:8">
+      <c r="A22" s="17"/>
+      <c r="B22" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="12">
+      <c r="C22" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="15">
         <v>2410000</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="41"/>
-    </row>
-    <row r="23" ht="16.8" spans="1:8">
-      <c r="A23" s="13"/>
-      <c r="B23" s="10" t="s">
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="16"/>
+    </row>
+    <row r="23" ht="15" spans="1:8">
+      <c r="A23" s="17"/>
+      <c r="B23" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="12">
+      <c r="C23" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="15">
         <v>2447502</v>
       </c>
-      <c r="E23" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="12">
+      <c r="E23" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="15">
         <v>1312502</v>
       </c>
-      <c r="G23" s="12"/>
-      <c r="H23" s="41"/>
-    </row>
-    <row r="24" ht="16.8" spans="1:8">
-      <c r="A24" s="13"/>
-      <c r="B24" s="10" t="s">
+      <c r="G23" s="15"/>
+      <c r="H23" s="16"/>
+    </row>
+    <row r="24" ht="15" spans="1:8">
+      <c r="A24" s="17"/>
+      <c r="B24" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="15"/>
+      <c r="E24" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="15">
+        <v>2280000</v>
+      </c>
+      <c r="G24" s="15"/>
+      <c r="H24" s="16"/>
+    </row>
+    <row r="25" ht="15" spans="1:8">
+      <c r="A25" s="17"/>
+      <c r="B25" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="12">
-        <v>2280000</v>
-      </c>
-      <c r="G24" s="12"/>
-      <c r="H24" s="41"/>
-    </row>
-    <row r="25" ht="16.8" spans="1:8">
-      <c r="A25" s="13"/>
-      <c r="B25" s="10" t="s">
+      <c r="C25" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="15">
+        <v>4760036</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="15">
+        <v>4760036</v>
+      </c>
+      <c r="G25" s="15"/>
+      <c r="H25" s="16"/>
+    </row>
+    <row r="26" ht="15" spans="1:8">
+      <c r="A26" s="17"/>
+      <c r="B26" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="12">
-        <v>4760036</v>
-      </c>
-      <c r="E25" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="12">
-        <v>4760036</v>
-      </c>
-      <c r="G25" s="12"/>
-      <c r="H25" s="41"/>
-    </row>
-    <row r="26" ht="16.8" spans="1:8">
-      <c r="A26" s="13"/>
-      <c r="B26" s="10" t="s">
+      <c r="C26" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="15">
+        <v>5600000</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="15">
+        <v>5600000</v>
+      </c>
+      <c r="G26" s="15"/>
+      <c r="H26" s="16"/>
+    </row>
+    <row r="27" ht="15" spans="1:8">
+      <c r="A27" s="17"/>
+      <c r="B27" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="12">
-        <v>5600000</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="12">
-        <v>5600000</v>
-      </c>
-      <c r="G26" s="12"/>
-      <c r="H26" s="41"/>
-    </row>
-    <row r="27" ht="16.8" spans="1:8">
-      <c r="A27" s="13"/>
-      <c r="B27" s="10" t="s">
+      <c r="C27" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1225000</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="15">
+        <v>915750</v>
+      </c>
+      <c r="G27" s="15"/>
+      <c r="H27" s="16"/>
+    </row>
+    <row r="28" ht="15" spans="1:8">
+      <c r="A28" s="17"/>
+      <c r="B28" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="12">
-        <v>1225000</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="12">
+      <c r="C28" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="15"/>
+      <c r="E28" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="16"/>
+    </row>
+    <row r="29" ht="15" spans="1:8">
+      <c r="A29" s="17"/>
+      <c r="B29" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="15">
+        <v>3948000</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="16"/>
+    </row>
+    <row r="30" ht="15" spans="1:8">
+      <c r="A30" s="17"/>
+      <c r="B30" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="15">
+        <v>250000</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="16"/>
+    </row>
+    <row r="31" ht="15" spans="1:8">
+      <c r="A31" s="17"/>
+      <c r="B31" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="15"/>
+      <c r="E31" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="16"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="20"/>
+      <c r="B32" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="33"/>
+      <c r="E32" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="33">
         <v>915750</v>
       </c>
-      <c r="G27" s="12"/>
-      <c r="H27" s="41"/>
-    </row>
-    <row r="28" ht="16.8" spans="1:8">
-      <c r="A28" s="13"/>
-      <c r="B28" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="12"/>
-      <c r="E28" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="41"/>
-    </row>
-    <row r="29" ht="16.8" spans="1:8">
-      <c r="A29" s="13"/>
-      <c r="B29" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="12">
-        <v>3948000</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="41"/>
-    </row>
-    <row r="30" ht="16.8" spans="1:8">
-      <c r="A30" s="13"/>
-      <c r="B30" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="12">
-        <v>250000</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="41"/>
-    </row>
-    <row r="31" ht="16.8" spans="1:8">
-      <c r="A31" s="13"/>
-      <c r="B31" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31" s="12"/>
-      <c r="E31" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="41"/>
-    </row>
-    <row r="32" ht="17.55" spans="1:8">
-      <c r="A32" s="15"/>
-      <c r="B32" s="25" t="s">
+      <c r="G32" s="33"/>
+      <c r="H32" s="34"/>
+    </row>
+    <row r="33" ht="15" spans="1:8">
+      <c r="A33" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="C32" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="27">
-        <v>915750</v>
-      </c>
-      <c r="G32" s="27"/>
-      <c r="H32" s="44"/>
-    </row>
-    <row r="33" ht="16.8" spans="1:8">
-      <c r="A33" s="28" t="s">
+      <c r="B33" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="B33" s="20" t="s">
+      <c r="C33" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="28">
+        <v>4897000</v>
+      </c>
+      <c r="E33" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="28">
+        <v>8368100</v>
+      </c>
+      <c r="G33" s="28"/>
+      <c r="H33" s="29"/>
+    </row>
+    <row r="34" ht="15" spans="1:8">
+      <c r="A34" s="36"/>
+      <c r="B34" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="22">
-        <v>4897000</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="22">
-        <v>8368100</v>
-      </c>
-      <c r="G33" s="22"/>
-      <c r="H33" s="43"/>
-    </row>
-    <row r="34" ht="16.8" spans="1:8">
-      <c r="A34" s="29"/>
-      <c r="B34" s="10" t="s">
+      <c r="C34" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="15">
+        <v>4375000</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" s="15">
+        <v>4715000</v>
+      </c>
+      <c r="G34" s="15"/>
+      <c r="H34" s="16"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="36"/>
+      <c r="B35" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="12">
-        <v>4375000</v>
-      </c>
-      <c r="E34" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="12">
-        <v>4715000</v>
-      </c>
-      <c r="G34" s="12"/>
-      <c r="H34" s="41"/>
-    </row>
-    <row r="35" ht="16.8" spans="1:8">
-      <c r="A35" s="29"/>
-      <c r="B35" s="10" t="s">
+      <c r="C35" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="15">
+        <v>1007480.64</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="15">
+        <v>638483</v>
+      </c>
+      <c r="G35" s="15"/>
+      <c r="H35" s="16"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="38"/>
+      <c r="B36" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="12">
-        <v>1007480.64</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="12">
-        <v>638483</v>
-      </c>
-      <c r="G35" s="12"/>
-      <c r="H35" s="41"/>
-    </row>
-    <row r="36" ht="16.8" spans="1:8">
-      <c r="A36" s="9"/>
-      <c r="B36" s="30" t="s">
+      <c r="C36" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="23">
+        <v>1168000</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="23">
+        <v>893000</v>
+      </c>
+      <c r="G36" s="23"/>
+      <c r="H36" s="24"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="32">
-        <v>1168000</v>
-      </c>
-      <c r="E36" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="32">
-        <v>893000</v>
-      </c>
-      <c r="G36" s="32"/>
-      <c r="H36" s="46"/>
-    </row>
-    <row r="37" ht="16.8" spans="1:8">
-      <c r="A37" s="33" t="s">
+      <c r="B37" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="C37" s="41"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" s="44">
+        <v>1020000</v>
+      </c>
+      <c r="G37" s="42"/>
+      <c r="H37" s="44"/>
+    </row>
+    <row r="38" ht="15" spans="1:8">
+      <c r="A38" s="39"/>
+      <c r="B38" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C37" s="34"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="12">
-        <v>1020000</v>
-      </c>
-      <c r="G37" s="35"/>
-      <c r="H37" s="12"/>
-    </row>
-    <row r="38" ht="16.8" spans="1:8">
-      <c r="A38" s="36"/>
-      <c r="B38" s="10" t="s">
+      <c r="C38" s="18"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="15">
+        <v>1350000</v>
+      </c>
+      <c r="G38" s="45"/>
+      <c r="H38" s="15"/>
+    </row>
+    <row r="39" ht="15" spans="1:8">
+      <c r="A39" s="39"/>
+      <c r="B39" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="34"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="12">
-        <v>1350000</v>
-      </c>
-      <c r="G38" s="35"/>
-      <c r="H38" s="12"/>
-    </row>
-    <row r="39" ht="16.8" spans="1:8">
-      <c r="A39" s="36"/>
-      <c r="B39" s="10" t="s">
+      <c r="C39" s="18"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" s="15">
+        <v>600000</v>
+      </c>
+      <c r="G39" s="45"/>
+      <c r="H39" s="15"/>
+    </row>
+    <row r="40" ht="15" spans="1:8">
+      <c r="A40" s="39"/>
+      <c r="B40" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="34"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="12">
-        <v>600000</v>
-      </c>
-      <c r="G39" s="35"/>
-      <c r="H39" s="12"/>
-    </row>
-    <row r="40" ht="16.8" spans="1:8">
-      <c r="A40" s="36"/>
-      <c r="B40" s="10" t="s">
+      <c r="C40" s="18"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" s="15">
+        <v>318134</v>
+      </c>
+      <c r="G40" s="45"/>
+      <c r="H40" s="15"/>
+    </row>
+    <row r="41" ht="15" spans="1:8">
+      <c r="A41" s="39"/>
+      <c r="B41" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="34"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="12">
-        <v>318134</v>
-      </c>
-      <c r="G40" s="35"/>
-      <c r="H40" s="12"/>
-    </row>
-    <row r="41" ht="16.8" spans="1:8">
-      <c r="A41" s="36"/>
-      <c r="B41" s="10" t="s">
+      <c r="C41" s="18"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="15">
+        <v>248700</v>
+      </c>
+      <c r="G41" s="45"/>
+      <c r="H41" s="15"/>
+    </row>
+    <row r="42" ht="15" spans="1:8">
+      <c r="A42" s="39"/>
+      <c r="B42" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C41" s="34"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="12">
-        <v>248700</v>
-      </c>
-      <c r="G41" s="35"/>
-      <c r="H41" s="12"/>
-    </row>
-    <row r="42" ht="16.8" spans="1:8">
-      <c r="A42" s="36"/>
-      <c r="B42" s="10" t="s">
+      <c r="C42" s="18"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="15">
+        <v>1029180</v>
+      </c>
+      <c r="G42" s="45"/>
+      <c r="H42" s="15"/>
+    </row>
+    <row r="43" ht="15" spans="1:8">
+      <c r="A43" s="39"/>
+      <c r="B43" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="12">
-        <v>1029180</v>
-      </c>
-      <c r="G42" s="35"/>
-      <c r="H42" s="12"/>
-    </row>
-    <row r="43" ht="16.8" spans="1:8">
-      <c r="A43" s="36"/>
-      <c r="B43" s="10" t="s">
+      <c r="C43" s="18"/>
+      <c r="D43" s="45"/>
+      <c r="E43" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="15">
+        <v>270000</v>
+      </c>
+      <c r="G43" s="45"/>
+      <c r="H43" s="15"/>
+    </row>
+    <row r="44" ht="15" spans="1:8">
+      <c r="A44" s="39"/>
+      <c r="B44" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C43" s="34"/>
-      <c r="D43" s="35"/>
-      <c r="E43" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="12">
-        <v>270000</v>
-      </c>
-      <c r="G43" s="35"/>
-      <c r="H43" s="12"/>
-    </row>
-    <row r="44" ht="16.8" spans="1:8">
-      <c r="A44" s="36"/>
-      <c r="B44" s="10" t="s">
+      <c r="C44" s="18"/>
+      <c r="D44" s="45"/>
+      <c r="E44" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="15">
+        <v>1000000</v>
+      </c>
+      <c r="G44" s="45"/>
+      <c r="H44" s="15"/>
+    </row>
+    <row r="45" ht="15" spans="1:8">
+      <c r="A45" s="39"/>
+      <c r="B45" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C44" s="34"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="12">
-        <v>1000000</v>
-      </c>
-      <c r="G44" s="35"/>
-      <c r="H44" s="12"/>
-    </row>
-    <row r="45" ht="16.8" spans="1:8">
-      <c r="A45" s="36"/>
-      <c r="B45" s="10" t="s">
+      <c r="C45" s="18"/>
+      <c r="D45" s="45"/>
+      <c r="E45" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="15">
+        <v>3000000</v>
+      </c>
+      <c r="G45" s="45"/>
+      <c r="H45" s="15"/>
+    </row>
+    <row r="46" ht="15" spans="1:8">
+      <c r="A46" s="46"/>
+      <c r="B46" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C45" s="34"/>
-      <c r="D45" s="35"/>
-      <c r="E45" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="12">
-        <v>3000000</v>
-      </c>
-      <c r="G45" s="35"/>
-      <c r="H45" s="12"/>
-    </row>
-    <row r="46" ht="16.8" spans="1:8">
-      <c r="A46" s="37"/>
-      <c r="B46" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C46" s="34"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="12">
+      <c r="C46" s="18"/>
+      <c r="D46" s="45"/>
+      <c r="E46" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F46" s="15">
         <v>1800000</v>
       </c>
-      <c r="G46" s="35"/>
-      <c r="H46" s="12"/>
+      <c r="G46" s="45"/>
+      <c r="H46" s="15"/>
     </row>
     <row r="47" spans="6:6">
       <c r="F47" s="4"/>
@@ -2783,7 +2763,7 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F52" s="4"/>
     </row>
@@ -2792,7 +2772,7 @@
         <v>25</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F53" s="4"/>
     </row>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -1846,7 +1846,7 @@
     <col min="6" max="7" width="13.6666666666667" customWidth="1"/>
     <col min="8" max="8" width="13.6666666666667" style="4" customWidth="1"/>
     <col min="9" max="9" width="14.3333333333333"/>
-    <col min="10" max="10" width="15.4285714285714"/>
+    <col min="10" max="10" width="17.7142857142857" customWidth="1"/>
     <col min="11" max="11" width="14.3333333333333"/>
     <col min="12" max="12" width="22.6666666666667" customWidth="1"/>
     <col min="13" max="13" width="11.6666666666667"/>
@@ -2544,7 +2544,7 @@
       <c r="G34" s="15"/>
       <c r="H34" s="16"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" ht="15" spans="1:8">
       <c r="A35" s="36"/>
       <c r="B35" s="13" t="s">
         <v>55</v>
@@ -2584,7 +2584,7 @@
       <c r="G36" s="23"/>
       <c r="H36" s="24"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" ht="15" spans="1:8">
       <c r="A37" s="39" t="s">
         <v>57</v>
       </c>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7500"/>
+    <workbookView windowWidth="28200" windowHeight="12640"/>
   </bookViews>
   <sheets>
     <sheet name="SUPPLIER PAYMENT STATUS" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="73">
   <si>
     <t>DIVISION</t>
   </si>
@@ -122,15 +122,21 @@
     <t>BOILER</t>
   </si>
   <si>
-    <t>ABDI JAYA</t>
-  </si>
-  <si>
     <t>DISHY SOAP</t>
   </si>
   <si>
     <t>DAILY BAGUETTE (NICO)</t>
   </si>
   <si>
+    <t>SURBLED</t>
+  </si>
+  <si>
+    <t>PAID 1ST</t>
+  </si>
+  <si>
+    <t>PAID 2ND</t>
+  </si>
+  <si>
     <t>BAR</t>
   </si>
   <si>
@@ -177,6 +183,9 @@
   </si>
   <si>
     <t>MULIA JAYA</t>
+  </si>
+  <si>
+    <t>BY CASH</t>
   </si>
   <si>
     <t>DEWATA KENCANA DISTRIBUSI</t>
@@ -244,12 +253,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="6">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    <numFmt numFmtId="181" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -655,7 +664,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -697,6 +706,19 @@
       <top style="medium">
         <color auto="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -706,7 +728,7 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top style="medium">
@@ -727,19 +749,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -749,7 +758,7 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top style="thin">
@@ -767,18 +776,9 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
@@ -800,93 +800,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
@@ -905,6 +819,127 @@
       </right>
       <top/>
       <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -1015,16 +1050,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1033,7 +1068,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1045,34 +1080,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1157,11 +1192,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1170,10 +1205,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1182,124 +1217,130 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="181" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1836,23 +1877,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultColWidth="9.16190476190476" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="18.8571428571429" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.3333333333333" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.3333333333333" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.3333333333333" customWidth="1"/>
-    <col min="5" max="5" width="12.5714285714286" style="3" customWidth="1"/>
-    <col min="6" max="7" width="13.6666666666667" customWidth="1"/>
-    <col min="8" max="8" width="13.6666666666667" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.3333333333333"/>
-    <col min="10" max="10" width="17.7142857142857" customWidth="1"/>
-    <col min="11" max="11" width="14.3333333333333"/>
-    <col min="12" max="12" width="22.6666666666667" customWidth="1"/>
-    <col min="13" max="13" width="11.6666666666667"/>
+    <col min="1" max="1" width="18.859375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.3359375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.3359375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.3359375" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" style="3" customWidth="1"/>
+    <col min="6" max="7" width="13.6640625" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="14.3359375"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.3359375"/>
+    <col min="12" max="12" width="22.6640625" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" ht="18.35" spans="1:10">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1865,886 +1906,951 @@
       <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="40" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="47">
-        <f>SUM(F2,F4,F8,F13,F14,F17,F24,F25,F34)</f>
-        <v>88565236</v>
-      </c>
-    </row>
-    <row r="2" ht="15" spans="1:10">
-      <c r="A2" s="12" t="s">
+      <c r="J1" s="49" t="e">
+        <f>SUM(F2,F4,F8,#REF!,F13,F17,F24,F25,F34)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="15">
+      <c r="C2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="12">
         <v>66835000</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="12">
         <v>39738000</v>
       </c>
-      <c r="G2" s="15"/>
-      <c r="H2" s="16"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="43">
+        <v>34233500</v>
+      </c>
       <c r="J2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="15" spans="1:10">
-      <c r="A3" s="17"/>
-      <c r="B3" s="13" t="s">
+    <row r="3" spans="1:10">
+      <c r="A3" s="13"/>
+      <c r="B3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="15">
+      <c r="C3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="16">
         <v>45478060</v>
       </c>
-      <c r="E3" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="15">
+      <c r="E3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="16">
         <v>39027410</v>
       </c>
-      <c r="G3" s="15"/>
-      <c r="H3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="44">
+        <v>45303890</v>
+      </c>
       <c r="J3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="1:10">
-      <c r="A4" s="17"/>
-      <c r="B4" s="13" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="13"/>
+      <c r="B4" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="15">
+      <c r="C4" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="16">
         <v>29900100</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="16">
         <v>20617200</v>
       </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="44">
+        <v>20728100</v>
+      </c>
       <c r="J4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="1:10">
-      <c r="A5" s="17"/>
-      <c r="B5" s="13" t="s">
+    <row r="5" spans="1:10">
+      <c r="A5" s="13"/>
+      <c r="B5" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="15">
+      <c r="C5" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="16">
         <v>4400000</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="15">
+      <c r="E5" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="16">
         <v>5560000</v>
       </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="44">
+        <v>320000</v>
+      </c>
       <c r="J5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="1:10">
-      <c r="A6" s="17"/>
-      <c r="B6" s="13" t="s">
+    <row r="6" spans="1:10">
+      <c r="A6" s="13"/>
+      <c r="B6" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="15">
+      <c r="C6" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="16">
         <v>5610900</v>
       </c>
-      <c r="E6" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="15">
+      <c r="E6" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="16">
         <v>3578050</v>
       </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="44">
+        <v>5069850</v>
+      </c>
       <c r="J6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" ht="15" spans="1:10">
-      <c r="A7" s="17"/>
-      <c r="B7" s="13" t="s">
+    <row r="7" spans="1:10">
+      <c r="A7" s="13"/>
+      <c r="B7" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="15">
+      <c r="C7" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="16">
         <v>3663300</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="15">
+      <c r="E7" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="16">
         <v>1983600</v>
       </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="44">
+        <v>13417600</v>
+      </c>
       <c r="J7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="15" spans="1:10">
-      <c r="A8" s="17"/>
-      <c r="B8" s="13" t="s">
+    <row r="8" ht="16.8" spans="1:10">
+      <c r="A8" s="13"/>
+      <c r="B8" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="15">
+      <c r="C8" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="16">
         <v>8775000</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="16">
         <v>7800000</v>
       </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="44">
+        <v>3900000</v>
+      </c>
       <c r="J8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="1:8">
-      <c r="A9" s="17"/>
-      <c r="B9" s="13" t="s">
+    <row r="9" ht="16.8" spans="1:8">
+      <c r="A9" s="13"/>
+      <c r="B9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="19" t="s">
+      <c r="D9" s="16"/>
+      <c r="E9" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="16"/>
-    </row>
-    <row r="10" ht="15" spans="1:10">
-      <c r="A10" s="17"/>
-      <c r="B10" s="13" t="s">
+      <c r="F9" s="16"/>
+      <c r="G9" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="44"/>
+    </row>
+    <row r="10" ht="16.8" spans="1:10">
+      <c r="A10" s="13"/>
+      <c r="B10" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="19" t="s">
+      <c r="D10" s="16"/>
+      <c r="E10" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="44"/>
       <c r="J10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="1:12">
-      <c r="A11" s="17"/>
-      <c r="B11" s="13" t="s">
+    <row r="11" ht="16.8" spans="1:12">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="15">
+      <c r="D11" s="16"/>
+      <c r="E11" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="16">
         <v>326000</v>
       </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="44">
+        <v>152000</v>
+      </c>
       <c r="J11" t="s">
         <v>29</v>
       </c>
-      <c r="L11" s="47"/>
-    </row>
-    <row r="12" ht="15" spans="1:10">
-      <c r="A12" s="17"/>
-      <c r="B12" s="13" t="s">
+      <c r="L11" s="49"/>
+    </row>
+    <row r="12" ht="16.8" spans="1:10">
+      <c r="A12" s="13"/>
+      <c r="B12" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="15">
+      <c r="C12" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="16"/>
+      <c r="E12" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="16">
         <v>924000</v>
       </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="16"/>
+      <c r="G12" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="44">
+        <v>594000</v>
+      </c>
       <c r="J12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" ht="15" spans="1:10">
-      <c r="A13" s="17"/>
-      <c r="B13" s="13" t="s">
+    <row r="13" spans="1:8">
+      <c r="A13" s="13"/>
+      <c r="B13" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="15">
+      <c r="C13" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="16"/>
+      <c r="E13" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="16">
+        <v>1525000</v>
+      </c>
+      <c r="G13" s="16"/>
+      <c r="H13" s="44">
+        <v>995000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="13"/>
+      <c r="B14" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="16">
+        <v>2320000</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="44">
+        <v>2996000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="18"/>
+      <c r="B15" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="21"/>
+      <c r="E15" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="45">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="25">
+        <v>20669000</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="25">
+        <v>13909500</v>
+      </c>
+      <c r="G16" s="25"/>
+      <c r="H16" s="46">
+        <v>12478500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="22"/>
+      <c r="B17" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="16">
+        <v>3230000</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="16">
+        <v>2415000</v>
+      </c>
+      <c r="G17" s="16"/>
+      <c r="H17" s="44">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="22"/>
+      <c r="B18" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="16">
+        <v>10775000</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="16">
+        <v>10000000</v>
+      </c>
+      <c r="G18" s="16"/>
+      <c r="H18" s="44">
+        <v>7025000</v>
+      </c>
+    </row>
+    <row r="19" ht="16.8" spans="1:8">
+      <c r="A19" s="22"/>
+      <c r="B19" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="16">
+        <v>10023000</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="16">
+        <v>6637500</v>
+      </c>
+      <c r="G19" s="16"/>
+      <c r="H19" s="44">
+        <v>12023500</v>
+      </c>
+    </row>
+    <row r="20" ht="16.8" spans="1:8">
+      <c r="A20" s="22"/>
+      <c r="B20" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="16"/>
+      <c r="E20" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="16"/>
+      <c r="G20" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="44"/>
+    </row>
+    <row r="21" ht="16.8" spans="1:8">
+      <c r="A21" s="22"/>
+      <c r="B21" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="16">
+        <v>3663000</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="16">
+        <v>1998000</v>
+      </c>
+      <c r="G21" s="16"/>
+      <c r="H21" s="44">
+        <v>1665000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="22"/>
+      <c r="B22" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="16">
+        <v>2410000</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="44">
+        <v>2110000</v>
+      </c>
+    </row>
+    <row r="23" ht="16.8" spans="1:8">
+      <c r="A23" s="22"/>
+      <c r="B23" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="16">
+        <v>2447502</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="16">
+        <v>1312502</v>
+      </c>
+      <c r="G23" s="16"/>
+      <c r="H23" s="44">
+        <v>1750003</v>
+      </c>
+    </row>
+    <row r="24" ht="16.8" spans="1:8">
+      <c r="A24" s="22"/>
+      <c r="B24" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="16"/>
+      <c r="E24" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="16">
+        <v>2280000</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="44"/>
+    </row>
+    <row r="25" ht="16.8" spans="1:8">
+      <c r="A25" s="22"/>
+      <c r="B25" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="16">
+        <v>4760036</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="16">
+        <v>4760036</v>
+      </c>
+      <c r="G25" s="16"/>
+      <c r="H25" s="44">
+        <v>1190009</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="22"/>
+      <c r="B26" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="16">
+        <v>5600000</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="16">
+        <v>5600000</v>
+      </c>
+      <c r="G26" s="16"/>
+      <c r="H26" s="44">
+        <v>5600000</v>
+      </c>
+    </row>
+    <row r="27" ht="16.8" spans="1:8">
+      <c r="A27" s="22"/>
+      <c r="B27" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="16">
+        <v>1225000</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="16">
+        <v>915750</v>
+      </c>
+      <c r="G27" s="16"/>
+      <c r="H27" s="44">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="28" ht="16.8" spans="1:8">
+      <c r="A28" s="22"/>
+      <c r="B28" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="16"/>
+      <c r="E28" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" s="44"/>
+    </row>
+    <row r="29" ht="16.8" spans="1:8">
+      <c r="A29" s="22"/>
+      <c r="B29" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="16">
+        <v>3948000</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H29" s="44"/>
+    </row>
+    <row r="30" ht="16.8" spans="1:8">
+      <c r="A30" s="22"/>
+      <c r="B30" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="16">
+        <v>250000</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="16"/>
+      <c r="G30" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="H30" s="44"/>
+    </row>
+    <row r="31" ht="16.8" spans="1:8">
+      <c r="A31" s="22"/>
+      <c r="B31" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="16"/>
+      <c r="E31" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="16"/>
+      <c r="G31" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H31" s="44"/>
+    </row>
+    <row r="32" ht="17.55" spans="1:8">
+      <c r="A32" s="27"/>
+      <c r="B32" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="30"/>
+      <c r="E32" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="30">
+        <v>915750</v>
+      </c>
+      <c r="G32" s="30"/>
+      <c r="H32" s="47"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="12">
+        <v>4897000</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="12">
+        <v>8368100</v>
+      </c>
+      <c r="G33" s="12"/>
+      <c r="H33" s="43">
+        <v>4047600</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="32"/>
+      <c r="B34" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="16">
         <v>4375000</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E34" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F34" s="16">
         <v>4715000</v>
       </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="16"/>
-      <c r="J13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" ht="15" spans="1:8">
-      <c r="A14" s="17"/>
-      <c r="B14" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="18" t="s">
+      <c r="G34" s="16"/>
+      <c r="H34" s="44">
+        <v>2585000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="32"/>
+      <c r="B35" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="16">
+        <v>1007480.64</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="16">
+        <v>638483</v>
+      </c>
+      <c r="G35" s="16"/>
+      <c r="H35" s="44">
+        <v>269482</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="33"/>
+      <c r="B36" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="21">
+        <v>1168000</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="21">
+        <v>893000</v>
+      </c>
+      <c r="G36" s="21"/>
+      <c r="H36" s="45">
+        <v>847000</v>
+      </c>
+    </row>
+    <row r="37" ht="16.8" spans="1:8">
+      <c r="A37" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="35"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" s="25">
+        <v>1020000</v>
+      </c>
+      <c r="G37" s="36"/>
+      <c r="H37" s="25"/>
+    </row>
+    <row r="38" ht="16.8" spans="1:8">
+      <c r="A38" s="34"/>
+      <c r="B38" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" s="37"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="16">
+        <v>1350000</v>
+      </c>
+      <c r="G38" s="38"/>
+      <c r="H38" s="16"/>
+    </row>
+    <row r="39" ht="16.8" spans="1:8">
+      <c r="A39" s="34"/>
+      <c r="B39" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" s="37"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" s="16">
+        <v>600000</v>
+      </c>
+      <c r="G39" s="38"/>
+      <c r="H39" s="16"/>
+    </row>
+    <row r="40" ht="16.8" spans="1:8">
+      <c r="A40" s="34"/>
+      <c r="B40" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="37"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" s="16">
+        <v>318134</v>
+      </c>
+      <c r="G40" s="38"/>
+      <c r="H40" s="16"/>
+    </row>
+    <row r="41" ht="16.8" spans="1:8">
+      <c r="A41" s="34"/>
+      <c r="B41" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="37"/>
+      <c r="D41" s="38"/>
+      <c r="E41" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="16">
+        <v>248700</v>
+      </c>
+      <c r="G41" s="38"/>
+      <c r="H41" s="16"/>
+    </row>
+    <row r="42" ht="16.8" spans="1:8">
+      <c r="A42" s="34"/>
+      <c r="B42" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="37"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="16">
+        <v>1029180</v>
+      </c>
+      <c r="G42" s="38"/>
+      <c r="H42" s="16"/>
+    </row>
+    <row r="43" ht="16.8" spans="1:8">
+      <c r="A43" s="34"/>
+      <c r="B43" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" s="37"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="16">
+        <v>270000</v>
+      </c>
+      <c r="G43" s="38"/>
+      <c r="H43" s="16"/>
+    </row>
+    <row r="44" ht="16.8" spans="1:8">
+      <c r="A44" s="34"/>
+      <c r="B44" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="37"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="16">
+        <v>1000000</v>
+      </c>
+      <c r="G44" s="38"/>
+      <c r="H44" s="16"/>
+    </row>
+    <row r="45" ht="16.8" spans="1:8">
+      <c r="A45" s="34"/>
+      <c r="B45" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="37"/>
+      <c r="D45" s="38"/>
+      <c r="E45" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="16">
+        <v>3000000</v>
+      </c>
+      <c r="G45" s="38"/>
+      <c r="H45" s="16"/>
+    </row>
+    <row r="46" ht="16.8" spans="1:8">
+      <c r="A46" s="39"/>
+      <c r="B46" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="37"/>
+      <c r="D46" s="38"/>
+      <c r="E46" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="15">
-        <v>1525000</v>
-      </c>
-      <c r="G14" s="15"/>
-      <c r="H14" s="16"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="20"/>
-      <c r="B15" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="23"/>
-      <c r="E15" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="23">
-        <v>2320000</v>
-      </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="24"/>
-    </row>
-    <row r="16" ht="15" spans="1:8">
-      <c r="A16" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="28">
-        <v>20669000</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="28">
-        <v>13909500</v>
-      </c>
-      <c r="G16" s="28"/>
-      <c r="H16" s="29"/>
-    </row>
-    <row r="17" ht="15" spans="1:8">
-      <c r="A17" s="17"/>
-      <c r="B17" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="15">
-        <v>3230000</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="15">
-        <v>2415000</v>
-      </c>
-      <c r="G17" s="15"/>
-      <c r="H17" s="16"/>
-    </row>
-    <row r="18" ht="15" spans="1:8">
-      <c r="A18" s="17"/>
-      <c r="B18" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="15">
-        <v>10775000</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="15">
-        <v>10000000</v>
-      </c>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16"/>
-    </row>
-    <row r="19" ht="15" spans="1:8">
-      <c r="A19" s="17"/>
-      <c r="B19" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="15">
-        <v>10023000</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="15">
-        <v>6637500</v>
-      </c>
-      <c r="G19" s="15"/>
-      <c r="H19" s="16"/>
-    </row>
-    <row r="20" ht="15" spans="1:8">
-      <c r="A20" s="17"/>
-      <c r="B20" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="16"/>
-    </row>
-    <row r="21" ht="15" spans="1:8">
-      <c r="A21" s="17"/>
-      <c r="B21" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="15">
-        <v>3663000</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="15">
-        <v>1998000</v>
-      </c>
-      <c r="G21" s="15"/>
-      <c r="H21" s="16"/>
-    </row>
-    <row r="22" ht="15" spans="1:8">
-      <c r="A22" s="17"/>
-      <c r="B22" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="15">
-        <v>2410000</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="16"/>
-    </row>
-    <row r="23" ht="15" spans="1:8">
-      <c r="A23" s="17"/>
-      <c r="B23" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="15">
-        <v>2447502</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="15">
-        <v>1312502</v>
-      </c>
-      <c r="G23" s="15"/>
-      <c r="H23" s="16"/>
-    </row>
-    <row r="24" ht="15" spans="1:8">
-      <c r="A24" s="17"/>
-      <c r="B24" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="15">
-        <v>2280000</v>
-      </c>
-      <c r="G24" s="15"/>
-      <c r="H24" s="16"/>
-    </row>
-    <row r="25" ht="15" spans="1:8">
-      <c r="A25" s="17"/>
-      <c r="B25" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="15">
-        <v>4760036</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="15">
-        <v>4760036</v>
-      </c>
-      <c r="G25" s="15"/>
-      <c r="H25" s="16"/>
-    </row>
-    <row r="26" ht="15" spans="1:8">
-      <c r="A26" s="17"/>
-      <c r="B26" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="15">
-        <v>5600000</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="15">
-        <v>5600000</v>
-      </c>
-      <c r="G26" s="15"/>
-      <c r="H26" s="16"/>
-    </row>
-    <row r="27" ht="15" spans="1:8">
-      <c r="A27" s="17"/>
-      <c r="B27" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1225000</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="15">
-        <v>915750</v>
-      </c>
-      <c r="G27" s="15"/>
-      <c r="H27" s="16"/>
-    </row>
-    <row r="28" ht="15" spans="1:8">
-      <c r="A28" s="17"/>
-      <c r="B28" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="16"/>
-    </row>
-    <row r="29" ht="15" spans="1:8">
-      <c r="A29" s="17"/>
-      <c r="B29" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="15">
-        <v>3948000</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="16"/>
-    </row>
-    <row r="30" ht="15" spans="1:8">
-      <c r="A30" s="17"/>
-      <c r="B30" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="15">
-        <v>250000</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="16"/>
-    </row>
-    <row r="31" ht="15" spans="1:8">
-      <c r="A31" s="17"/>
-      <c r="B31" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="16"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="20"/>
-      <c r="B32" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="33"/>
-      <c r="E32" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="33">
-        <v>915750</v>
-      </c>
-      <c r="G32" s="33"/>
-      <c r="H32" s="34"/>
-    </row>
-    <row r="33" ht="15" spans="1:8">
-      <c r="A33" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="28">
-        <v>4897000</v>
-      </c>
-      <c r="E33" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="28">
-        <v>8368100</v>
-      </c>
-      <c r="G33" s="28"/>
-      <c r="H33" s="29"/>
-    </row>
-    <row r="34" ht="15" spans="1:8">
-      <c r="A34" s="36"/>
-      <c r="B34" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="15">
-        <v>4375000</v>
-      </c>
-      <c r="E34" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" s="15">
-        <v>4715000</v>
-      </c>
-      <c r="G34" s="15"/>
-      <c r="H34" s="16"/>
-    </row>
-    <row r="35" ht="15" spans="1:8">
-      <c r="A35" s="36"/>
-      <c r="B35" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="15">
-        <v>1007480.64</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="15">
-        <v>638483</v>
-      </c>
-      <c r="G35" s="15"/>
-      <c r="H35" s="16"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="38"/>
-      <c r="B36" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="23">
-        <v>1168000</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="23">
-        <v>893000</v>
-      </c>
-      <c r="G36" s="23"/>
-      <c r="H36" s="24"/>
-    </row>
-    <row r="37" ht="15" spans="1:8">
-      <c r="A37" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="B37" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="C37" s="41"/>
-      <c r="D37" s="42"/>
-      <c r="E37" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="44">
-        <v>1020000</v>
-      </c>
-      <c r="G37" s="42"/>
-      <c r="H37" s="44"/>
-    </row>
-    <row r="38" ht="15" spans="1:8">
-      <c r="A38" s="39"/>
-      <c r="B38" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="15">
-        <v>1350000</v>
-      </c>
-      <c r="G38" s="45"/>
-      <c r="H38" s="15"/>
-    </row>
-    <row r="39" ht="15" spans="1:8">
-      <c r="A39" s="39"/>
-      <c r="B39" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="15">
-        <v>600000</v>
-      </c>
-      <c r="G39" s="45"/>
-      <c r="H39" s="15"/>
-    </row>
-    <row r="40" ht="15" spans="1:8">
-      <c r="A40" s="39"/>
-      <c r="B40" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="15">
-        <v>318134</v>
-      </c>
-      <c r="G40" s="45"/>
-      <c r="H40" s="15"/>
-    </row>
-    <row r="41" ht="15" spans="1:8">
-      <c r="A41" s="39"/>
-      <c r="B41" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C41" s="18"/>
-      <c r="D41" s="45"/>
-      <c r="E41" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="15">
-        <v>248700</v>
-      </c>
-      <c r="G41" s="45"/>
-      <c r="H41" s="15"/>
-    </row>
-    <row r="42" ht="15" spans="1:8">
-      <c r="A42" s="39"/>
-      <c r="B42" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C42" s="18"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="15">
-        <v>1029180</v>
-      </c>
-      <c r="G42" s="45"/>
-      <c r="H42" s="15"/>
-    </row>
-    <row r="43" ht="15" spans="1:8">
-      <c r="A43" s="39"/>
-      <c r="B43" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C43" s="18"/>
-      <c r="D43" s="45"/>
-      <c r="E43" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="15">
-        <v>270000</v>
-      </c>
-      <c r="G43" s="45"/>
-      <c r="H43" s="15"/>
-    </row>
-    <row r="44" ht="15" spans="1:8">
-      <c r="A44" s="39"/>
-      <c r="B44" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="45"/>
-      <c r="E44" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="15">
-        <v>1000000</v>
-      </c>
-      <c r="G44" s="45"/>
-      <c r="H44" s="15"/>
-    </row>
-    <row r="45" ht="15" spans="1:8">
-      <c r="A45" s="39"/>
-      <c r="B45" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C45" s="18"/>
-      <c r="D45" s="45"/>
-      <c r="E45" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="15">
-        <v>3000000</v>
-      </c>
-      <c r="G45" s="45"/>
-      <c r="H45" s="15"/>
-    </row>
-    <row r="46" ht="15" spans="1:8">
-      <c r="A46" s="46"/>
-      <c r="B46" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C46" s="18"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F46" s="15">
+      <c r="F46" s="16">
         <v>1800000</v>
       </c>
-      <c r="G46" s="45"/>
-      <c r="H46" s="15"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="16"/>
     </row>
     <row r="47" spans="6:6">
       <c r="F47" s="4"/>
@@ -2763,7 +2869,7 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F52" s="4"/>
     </row>
@@ -2772,7 +2878,7 @@
         <v>25</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F53" s="4"/>
     </row>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28200" windowHeight="12640"/>
+    <workbookView windowWidth="19635" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="SUPPLIER PAYMENT STATUS" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="73">
   <si>
     <t>DIVISION</t>
   </si>
@@ -56,7 +56,10 @@
     <t>PAID</t>
   </si>
   <si>
-    <t>PAID 50%</t>
+    <t>PAID 100%</t>
+  </si>
+  <si>
+    <t>POSTED</t>
   </si>
   <si>
     <t>Bu bunga</t>
@@ -69,9 +72,6 @@
   </si>
   <si>
     <t>RAFI SEAFOOD</t>
-  </si>
-  <si>
-    <t>POSTED</t>
   </si>
   <si>
     <t>Surbled</t>
@@ -253,12 +253,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="6">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-    <numFmt numFmtId="181" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -664,7 +664,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -710,6 +710,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -740,6 +753,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -770,6 +798,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -789,6 +832,21 @@
         <color auto="1"/>
       </left>
       <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="thin">
@@ -824,6 +882,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -853,21 +924,23 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom/>
@@ -877,71 +950,11 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1050,16 +1063,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1068,7 +1081,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="22" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1080,34 +1093,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1192,11 +1205,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1205,10 +1218,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1217,37 +1230,34 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1256,91 +1266,91 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1877,23 +1887,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9.16190476190476" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="18.859375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.3359375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.3359375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.3359375" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="3" customWidth="1"/>
-    <col min="6" max="7" width="13.6640625" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.3359375"/>
-    <col min="10" max="10" width="17.7109375" customWidth="1"/>
-    <col min="11" max="11" width="14.3359375"/>
-    <col min="12" max="12" width="22.6640625" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625"/>
+    <col min="1" max="1" width="18.8571428571429" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.3333333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.3333333333333" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="12.5714285714286" style="3" customWidth="1"/>
+    <col min="6" max="7" width="13.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="13.6666666666667" style="4" customWidth="1"/>
+    <col min="9" max="9" width="14.3333333333333"/>
+    <col min="10" max="10" width="17.7142857142857" customWidth="1"/>
+    <col min="11" max="11" width="14.3333333333333"/>
+    <col min="12" max="12" width="22.6666666666667" customWidth="1"/>
+    <col min="13" max="13" width="11.6666666666667"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.35" spans="1:10">
+    <row r="1" ht="16.5" spans="1:10">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1906,94 +1916,100 @@
       <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="41" t="s">
+      <c r="G1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="49" t="e">
+      <c r="J1" s="48" t="e">
         <f>SUM(F2,F4,F8,#REF!,F13,F17,F24,F25,F34)</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="12">
+      <c r="C2" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="15">
         <v>66835000</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="15">
         <v>39738000</v>
       </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="43">
+      <c r="G2" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="16">
         <v>34233500</v>
       </c>
       <c r="J2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="17"/>
+      <c r="B3" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="20">
+        <v>45478060</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="20">
+        <v>39027410</v>
+      </c>
+      <c r="G3" s="20" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="13"/>
-      <c r="B3" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="16">
-        <v>45478060</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="16">
-        <v>39027410</v>
-      </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="44">
+      <c r="H3" s="21">
         <v>45303890</v>
       </c>
       <c r="J3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="13"/>
-      <c r="B4" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="16">
+      <c r="A4" s="17"/>
+      <c r="B4" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="20">
         <v>29900100</v>
       </c>
-      <c r="E4" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="16">
+      <c r="E4" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="20">
         <v>20617200</v>
       </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="44">
+      <c r="G4" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="21">
         <v>20728100</v>
       </c>
       <c r="J4" t="s">
@@ -2001,24 +2017,26 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="16">
+      <c r="C5" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="20">
         <v>4400000</v>
       </c>
-      <c r="E5" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="16">
+      <c r="E5" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="20">
         <v>5560000</v>
       </c>
-      <c r="G5" s="16"/>
-      <c r="H5" s="44">
+      <c r="G5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="21">
         <v>320000</v>
       </c>
       <c r="J5" t="s">
@@ -2026,24 +2044,26 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="13"/>
-      <c r="B6" s="14" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="16">
+      <c r="C6" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="20">
         <v>5610900</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="16">
+      <c r="E6" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="20">
         <v>3578050</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="44">
+      <c r="G6" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="21">
         <v>5069850</v>
       </c>
       <c r="J6" t="s">
@@ -2051,137 +2071,141 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14" t="s">
+      <c r="A7" s="17"/>
+      <c r="B7" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="16">
+      <c r="C7" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="20">
         <v>3663300</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="16">
+      <c r="E7" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="20">
         <v>1983600</v>
       </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="44">
+      <c r="G7" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="21">
         <v>13417600</v>
       </c>
       <c r="J7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="16.8" spans="1:10">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14" t="s">
+    <row r="8" spans="1:10">
+      <c r="A8" s="17"/>
+      <c r="B8" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="16">
+      <c r="C8" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="20">
         <v>8775000</v>
       </c>
-      <c r="E8" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="16">
+      <c r="E8" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="20">
         <v>7800000</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="44">
+      <c r="G8" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="21">
         <v>3900000</v>
       </c>
       <c r="J8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" ht="16.8" spans="1:8">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14" t="s">
+    <row r="9" ht="15" spans="1:8">
+      <c r="A9" s="17"/>
+      <c r="B9" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="17" t="s">
+      <c r="D9" s="20"/>
+      <c r="E9" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="17" t="s">
+      <c r="F9" s="20"/>
+      <c r="G9" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="44"/>
-    </row>
-    <row r="10" ht="16.8" spans="1:10">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14" t="s">
+      <c r="H9" s="21"/>
+    </row>
+    <row r="10" ht="15" spans="1:10">
+      <c r="A10" s="17"/>
+      <c r="B10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="17" t="s">
+      <c r="D10" s="20"/>
+      <c r="E10" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="17" t="s">
+      <c r="F10" s="20"/>
+      <c r="G10" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="44"/>
+      <c r="H10" s="21"/>
       <c r="J10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" ht="16.8" spans="1:12">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14" t="s">
+    <row r="11" ht="15" spans="1:12">
+      <c r="A11" s="17"/>
+      <c r="B11" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="16">
+      <c r="D11" s="20"/>
+      <c r="E11" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="20">
         <v>326000</v>
       </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="44">
+      <c r="G11" s="20"/>
+      <c r="H11" s="21">
         <v>152000</v>
       </c>
       <c r="J11" t="s">
         <v>29</v>
       </c>
-      <c r="L11" s="49"/>
-    </row>
-    <row r="12" ht="16.8" spans="1:10">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14" t="s">
+      <c r="L11" s="48"/>
+    </row>
+    <row r="12" ht="15" spans="1:10">
+      <c r="A12" s="17"/>
+      <c r="B12" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="16">
+      <c r="C12" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="E12" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="20">
         <v>924000</v>
       </c>
-      <c r="G12" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="44">
+      <c r="G12" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="21">
         <v>594000</v>
       </c>
       <c r="J12" t="s">
@@ -2189,668 +2213,700 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14" t="s">
+      <c r="A13" s="17"/>
+      <c r="B13" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="16">
+      <c r="C13" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="20"/>
+      <c r="E13" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="20">
         <v>1525000</v>
       </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="44">
+      <c r="G13" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="21">
         <v>995000</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14" t="s">
+    <row r="14" ht="15" spans="1:8">
+      <c r="A14" s="17"/>
+      <c r="B14" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="16">
+      <c r="C14" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="20"/>
+      <c r="E14" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="20">
         <v>2320000</v>
       </c>
-      <c r="G14" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="44">
+      <c r="G14" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="21">
         <v>2996000</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="18"/>
-      <c r="B15" s="19" t="s">
+      <c r="A15" s="24"/>
+      <c r="B15" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="20" t="s">
+      <c r="D15" s="27"/>
+      <c r="E15" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="45">
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="28">
         <v>10000000</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="25">
+      <c r="C16" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="32">
         <v>20669000</v>
       </c>
-      <c r="E16" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="25">
+      <c r="E16" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="32">
         <v>13909500</v>
       </c>
-      <c r="G16" s="25"/>
-      <c r="H16" s="46">
+      <c r="G16" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="33">
         <v>12478500</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="22"/>
-      <c r="B17" s="14" t="s">
+      <c r="A17" s="29"/>
+      <c r="B17" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="16">
+      <c r="C17" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="20">
         <v>3230000</v>
       </c>
-      <c r="E17" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="16">
+      <c r="E17" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="20">
         <v>2415000</v>
       </c>
-      <c r="G17" s="16"/>
-      <c r="H17" s="44">
+      <c r="G17" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="21">
         <v>1800000</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="22"/>
-      <c r="B18" s="14" t="s">
+      <c r="A18" s="29"/>
+      <c r="B18" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="16">
+      <c r="C18" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="20">
         <v>10775000</v>
       </c>
-      <c r="E18" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="16">
+      <c r="E18" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="20">
         <v>10000000</v>
       </c>
-      <c r="G18" s="16"/>
-      <c r="H18" s="44">
+      <c r="G18" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="21">
         <v>7025000</v>
       </c>
     </row>
-    <row r="19" ht="16.8" spans="1:8">
-      <c r="A19" s="22"/>
-      <c r="B19" s="14" t="s">
+    <row r="19" spans="1:8">
+      <c r="A19" s="29"/>
+      <c r="B19" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="16">
+      <c r="C19" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="20">
         <v>10023000</v>
       </c>
-      <c r="E19" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="16">
+      <c r="E19" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="20">
         <v>6637500</v>
       </c>
-      <c r="G19" s="16"/>
-      <c r="H19" s="44">
+      <c r="G19" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="21">
         <v>12023500</v>
       </c>
     </row>
-    <row r="20" ht="16.8" spans="1:8">
-      <c r="A20" s="22"/>
-      <c r="B20" s="14" t="s">
+    <row r="20" ht="15" spans="1:8">
+      <c r="A20" s="29"/>
+      <c r="B20" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="17" t="s">
+      <c r="D20" s="20"/>
+      <c r="E20" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="17" t="s">
+      <c r="F20" s="20"/>
+      <c r="G20" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="H20" s="44"/>
-    </row>
-    <row r="21" ht="16.8" spans="1:8">
-      <c r="A21" s="22"/>
-      <c r="B21" s="14" t="s">
+      <c r="H20" s="21"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="29"/>
+      <c r="B21" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="16">
+      <c r="C21" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="20">
         <v>3663000</v>
       </c>
-      <c r="E21" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="16">
+      <c r="E21" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="20">
         <v>1998000</v>
       </c>
-      <c r="G21" s="16"/>
-      <c r="H21" s="44">
+      <c r="G21" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="21">
         <v>1665000</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="22"/>
-      <c r="B22" s="14" t="s">
+      <c r="A22" s="29"/>
+      <c r="B22" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="16">
+      <c r="C22" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="20">
         <v>2410000</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="44">
+      <c r="F22" s="20"/>
+      <c r="G22" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="21">
         <v>2110000</v>
       </c>
     </row>
-    <row r="23" ht="16.8" spans="1:8">
-      <c r="A23" s="22"/>
-      <c r="B23" s="14" t="s">
+    <row r="23" spans="1:8">
+      <c r="A23" s="29"/>
+      <c r="B23" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="16">
+      <c r="C23" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="20">
         <v>2447502</v>
       </c>
-      <c r="E23" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="16">
+      <c r="E23" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="20">
         <v>1312502</v>
       </c>
-      <c r="G23" s="16"/>
-      <c r="H23" s="44">
+      <c r="G23" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="21">
         <v>1750003</v>
       </c>
     </row>
-    <row r="24" ht="16.8" spans="1:8">
-      <c r="A24" s="22"/>
-      <c r="B24" s="14" t="s">
+    <row r="24" ht="15" spans="1:8">
+      <c r="A24" s="29"/>
+      <c r="B24" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="16">
+      <c r="D24" s="20"/>
+      <c r="E24" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="20">
         <v>2280000</v>
       </c>
-      <c r="G24" s="17" t="s">
+      <c r="G24" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="H24" s="44"/>
-    </row>
-    <row r="25" ht="16.8" spans="1:8">
-      <c r="A25" s="22"/>
-      <c r="B25" s="14" t="s">
+      <c r="H24" s="21"/>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="29"/>
+      <c r="B25" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="16">
+      <c r="C25" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="20">
         <v>4760036</v>
       </c>
-      <c r="E25" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="16">
+      <c r="E25" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="20">
         <v>4760036</v>
       </c>
-      <c r="G25" s="16"/>
-      <c r="H25" s="44">
+      <c r="G25" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" s="21">
         <v>1190009</v>
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="22"/>
-      <c r="B26" s="14" t="s">
+      <c r="A26" s="29"/>
+      <c r="B26" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="16">
+      <c r="C26" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="20">
         <v>5600000</v>
       </c>
-      <c r="E26" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="16">
+      <c r="E26" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="20">
         <v>5600000</v>
       </c>
-      <c r="G26" s="16"/>
-      <c r="H26" s="44">
+      <c r="G26" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="21">
         <v>5600000</v>
       </c>
     </row>
-    <row r="27" ht="16.8" spans="1:8">
-      <c r="A27" s="22"/>
-      <c r="B27" s="14" t="s">
+    <row r="27" spans="1:8">
+      <c r="A27" s="29"/>
+      <c r="B27" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="16">
+      <c r="C27" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="20">
         <v>1225000</v>
       </c>
-      <c r="E27" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="16">
+      <c r="E27" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="20">
         <v>915750</v>
       </c>
-      <c r="G27" s="16"/>
-      <c r="H27" s="44">
+      <c r="G27" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="21">
         <v>600000</v>
       </c>
     </row>
-    <row r="28" ht="16.8" spans="1:8">
-      <c r="A28" s="22"/>
-      <c r="B28" s="14" t="s">
+    <row r="28" ht="15" spans="1:8">
+      <c r="A28" s="29"/>
+      <c r="B28" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="17" t="s">
+      <c r="D28" s="20"/>
+      <c r="E28" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="F28" s="16"/>
-      <c r="G28" s="17" t="s">
+      <c r="F28" s="20"/>
+      <c r="G28" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="H28" s="44"/>
-    </row>
-    <row r="29" ht="16.8" spans="1:8">
-      <c r="A29" s="22"/>
-      <c r="B29" s="14" t="s">
+      <c r="H28" s="21"/>
+    </row>
+    <row r="29" ht="15" spans="1:8">
+      <c r="A29" s="29"/>
+      <c r="B29" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="16">
+      <c r="C29" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="20">
         <v>3948000</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="17" t="s">
+      <c r="F29" s="20"/>
+      <c r="G29" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="H29" s="44"/>
-    </row>
-    <row r="30" ht="16.8" spans="1:8">
-      <c r="A30" s="22"/>
-      <c r="B30" s="14" t="s">
+      <c r="H29" s="21"/>
+    </row>
+    <row r="30" ht="15" spans="1:8">
+      <c r="A30" s="29"/>
+      <c r="B30" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="16">
+      <c r="C30" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="20">
         <v>250000</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="F30" s="16"/>
-      <c r="G30" s="17" t="s">
+      <c r="F30" s="20"/>
+      <c r="G30" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="H30" s="44"/>
-    </row>
-    <row r="31" ht="16.8" spans="1:8">
-      <c r="A31" s="22"/>
-      <c r="B31" s="14" t="s">
+      <c r="H30" s="21"/>
+    </row>
+    <row r="31" ht="15" spans="1:8">
+      <c r="A31" s="29"/>
+      <c r="B31" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="C31" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="17" t="s">
+      <c r="D31" s="20"/>
+      <c r="E31" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="F31" s="16"/>
-      <c r="G31" s="17" t="s">
+      <c r="F31" s="20"/>
+      <c r="G31" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="H31" s="44"/>
-    </row>
-    <row r="32" ht="17.55" spans="1:8">
-      <c r="A32" s="27"/>
-      <c r="B32" s="28" t="s">
+      <c r="H31" s="21"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="35"/>
+      <c r="B32" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="30"/>
-      <c r="E32" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="30">
+      <c r="C32" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="38"/>
+      <c r="E32" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="38">
         <v>915750</v>
       </c>
-      <c r="G32" s="30"/>
-      <c r="H32" s="47"/>
+      <c r="G32" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="H32" s="39"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C33" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="12">
+      <c r="C33" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="15">
         <v>4897000</v>
       </c>
-      <c r="E33" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="12">
+      <c r="E33" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="15">
         <v>8368100</v>
       </c>
-      <c r="G33" s="12"/>
-      <c r="H33" s="43">
+      <c r="G33" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="16">
         <v>4047600</v>
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="32"/>
-      <c r="B34" s="14" t="s">
+      <c r="A34" s="17"/>
+      <c r="B34" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="16">
+      <c r="C34" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="20">
         <v>4375000</v>
       </c>
-      <c r="E34" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" s="16">
+      <c r="E34" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" s="20">
         <v>4715000</v>
       </c>
-      <c r="G34" s="16"/>
-      <c r="H34" s="44">
+      <c r="G34" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H34" s="21">
         <v>2585000</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="32"/>
-      <c r="B35" s="14" t="s">
+    <row r="35" ht="15" spans="1:8">
+      <c r="A35" s="17"/>
+      <c r="B35" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C35" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="16">
+      <c r="C35" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="20">
         <v>1007480.64</v>
       </c>
-      <c r="E35" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="16">
+      <c r="E35" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="20">
         <v>638483</v>
       </c>
-      <c r="G35" s="16"/>
-      <c r="H35" s="44">
+      <c r="G35" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="20">
         <v>269482</v>
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="33"/>
-      <c r="B36" s="19" t="s">
+      <c r="A36" s="24"/>
+      <c r="B36" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="21">
+      <c r="C36" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="20">
         <v>1168000</v>
       </c>
-      <c r="E36" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="21">
+      <c r="E36" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="42">
         <v>893000</v>
       </c>
-      <c r="G36" s="21"/>
-      <c r="H36" s="45">
+      <c r="G36" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="H36" s="20">
         <v>847000</v>
       </c>
     </row>
-    <row r="37" ht="16.8" spans="1:8">
-      <c r="A37" s="34" t="s">
+    <row r="37" ht="15" spans="1:8">
+      <c r="A37" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="B37" s="23" t="s">
+      <c r="B37" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C37" s="35"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="25">
+      <c r="C37" s="44"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" s="20">
         <v>1020000</v>
       </c>
-      <c r="G37" s="36"/>
-      <c r="H37" s="25"/>
-    </row>
-    <row r="38" ht="16.8" spans="1:8">
-      <c r="A38" s="34"/>
-      <c r="B38" s="14" t="s">
+      <c r="G37" s="45"/>
+      <c r="H37" s="46"/>
+    </row>
+    <row r="38" ht="15" spans="1:8">
+      <c r="A38" s="43"/>
+      <c r="B38" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C38" s="37"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="16">
+      <c r="C38" s="44"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="20">
         <v>1350000</v>
       </c>
-      <c r="G38" s="38"/>
-      <c r="H38" s="16"/>
-    </row>
-    <row r="39" ht="16.8" spans="1:8">
-      <c r="A39" s="34"/>
-      <c r="B39" s="14" t="s">
+      <c r="G38" s="45"/>
+      <c r="H38" s="46"/>
+    </row>
+    <row r="39" ht="15" spans="1:8">
+      <c r="A39" s="43"/>
+      <c r="B39" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C39" s="37"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="16">
+      <c r="C39" s="44"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" s="20">
         <v>600000</v>
       </c>
-      <c r="G39" s="38"/>
-      <c r="H39" s="16"/>
-    </row>
-    <row r="40" ht="16.8" spans="1:8">
-      <c r="A40" s="34"/>
-      <c r="B40" s="14" t="s">
+      <c r="G39" s="45"/>
+      <c r="H39" s="46"/>
+    </row>
+    <row r="40" ht="15" spans="1:8">
+      <c r="A40" s="43"/>
+      <c r="B40" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="37"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="16">
+      <c r="C40" s="44"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" s="20">
         <v>318134</v>
       </c>
-      <c r="G40" s="38"/>
-      <c r="H40" s="16"/>
-    </row>
-    <row r="41" ht="16.8" spans="1:8">
-      <c r="A41" s="34"/>
-      <c r="B41" s="14" t="s">
+      <c r="G40" s="45"/>
+      <c r="H40" s="46"/>
+    </row>
+    <row r="41" ht="15" spans="1:8">
+      <c r="A41" s="43"/>
+      <c r="B41" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="37"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="16">
+      <c r="C41" s="44"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="20">
         <v>248700</v>
       </c>
-      <c r="G41" s="38"/>
-      <c r="H41" s="16"/>
-    </row>
-    <row r="42" ht="16.8" spans="1:8">
-      <c r="A42" s="34"/>
-      <c r="B42" s="14" t="s">
+      <c r="G41" s="45"/>
+      <c r="H41" s="46"/>
+    </row>
+    <row r="42" ht="15" spans="1:8">
+      <c r="A42" s="43"/>
+      <c r="B42" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="37"/>
-      <c r="D42" s="38"/>
-      <c r="E42" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="16">
+      <c r="C42" s="44"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="20">
         <v>1029180</v>
       </c>
-      <c r="G42" s="38"/>
-      <c r="H42" s="16"/>
-    </row>
-    <row r="43" ht="16.8" spans="1:8">
-      <c r="A43" s="34"/>
-      <c r="B43" s="14" t="s">
+      <c r="G42" s="45"/>
+      <c r="H42" s="46"/>
+    </row>
+    <row r="43" ht="15" spans="1:8">
+      <c r="A43" s="43"/>
+      <c r="B43" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C43" s="37"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="16">
+      <c r="C43" s="44"/>
+      <c r="D43" s="45"/>
+      <c r="E43" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="20">
         <v>270000</v>
       </c>
-      <c r="G43" s="38"/>
-      <c r="H43" s="16"/>
-    </row>
-    <row r="44" ht="16.8" spans="1:8">
-      <c r="A44" s="34"/>
-      <c r="B44" s="14" t="s">
+      <c r="G43" s="45"/>
+      <c r="H43" s="46"/>
+    </row>
+    <row r="44" ht="15" spans="1:8">
+      <c r="A44" s="43"/>
+      <c r="B44" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="37"/>
-      <c r="D44" s="38"/>
-      <c r="E44" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="16">
+      <c r="C44" s="44"/>
+      <c r="D44" s="45"/>
+      <c r="E44" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="20">
         <v>1000000</v>
       </c>
-      <c r="G44" s="38"/>
-      <c r="H44" s="16"/>
-    </row>
-    <row r="45" ht="16.8" spans="1:8">
-      <c r="A45" s="34"/>
-      <c r="B45" s="14" t="s">
+      <c r="G44" s="45"/>
+      <c r="H44" s="46"/>
+    </row>
+    <row r="45" ht="15" spans="1:8">
+      <c r="A45" s="43"/>
+      <c r="B45" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="37"/>
-      <c r="D45" s="38"/>
-      <c r="E45" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="16">
+      <c r="C45" s="44"/>
+      <c r="D45" s="45"/>
+      <c r="E45" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="20">
         <v>3000000</v>
       </c>
-      <c r="G45" s="38"/>
-      <c r="H45" s="16"/>
-    </row>
-    <row r="46" ht="16.8" spans="1:8">
-      <c r="A46" s="39"/>
-      <c r="B46" s="14" t="s">
+      <c r="G45" s="45"/>
+      <c r="H45" s="46"/>
+    </row>
+    <row r="46" ht="15" spans="1:8">
+      <c r="A46" s="47"/>
+      <c r="B46" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C46" s="37"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="F46" s="16">
+      <c r="C46" s="44"/>
+      <c r="D46" s="45"/>
+      <c r="E46" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="20">
         <v>1800000</v>
       </c>
-      <c r="G46" s="38"/>
-      <c r="H46" s="16"/>
+      <c r="G46" s="45"/>
+      <c r="H46" s="46"/>
     </row>
     <row r="47" spans="6:6">
       <c r="F47" s="4"/>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="77">
   <si>
     <t>DIVISION</t>
   </si>
@@ -128,6 +128,12 @@
     <t>DAILY BAGUETTE (NICO)</t>
   </si>
   <si>
+    <t>abdi</t>
+  </si>
+  <si>
+    <t>anugrah</t>
+  </si>
+  <si>
     <t>SURBLED</t>
   </si>
   <si>
@@ -137,10 +143,16 @@
     <t>PAID 2ND</t>
   </si>
   <si>
+    <t>16x25</t>
+  </si>
+  <si>
     <t>BAR</t>
   </si>
   <si>
     <t>WARUNG EKA</t>
+  </si>
+  <si>
+    <t>20x30</t>
   </si>
   <si>
     <t>DEWATA COCONUT</t>
@@ -1933,7 +1945,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" ht="15" spans="1:10">
       <c r="A2" s="12" t="s">
         <v>6</v>
       </c>
@@ -1962,7 +1974,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" ht="15" spans="1:10">
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="s">
         <v>12</v>
@@ -1989,7 +2001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" ht="15" spans="1:10">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
         <v>14</v>
@@ -2016,7 +2028,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" ht="15" spans="1:10">
       <c r="A5" s="17"/>
       <c r="B5" s="18" t="s">
         <v>16</v>
@@ -2043,7 +2055,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" ht="15" spans="1:10">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
         <v>18</v>
@@ -2070,7 +2082,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" ht="15" spans="1:10">
       <c r="A7" s="17"/>
       <c r="B7" s="18" t="s">
         <v>20</v>
@@ -2097,7 +2109,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" ht="15" spans="1:10">
       <c r="A8" s="17"/>
       <c r="B8" s="18" t="s">
         <v>22</v>
@@ -2212,7 +2224,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" ht="15" spans="1:8">
       <c r="A13" s="17"/>
       <c r="B13" s="18" t="s">
         <v>31</v>
@@ -2234,7 +2246,7 @@
         <v>995000</v>
       </c>
     </row>
-    <row r="14" ht="15" spans="1:8">
+    <row r="14" ht="15" spans="1:12">
       <c r="A14" s="17"/>
       <c r="B14" s="18" t="s">
         <v>32</v>
@@ -2255,31 +2267,46 @@
       <c r="H14" s="21">
         <v>2996000</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="K14" t="s">
+        <v>33</v>
+      </c>
+      <c r="L14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="24"/>
       <c r="B15" s="25" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D15" s="27"/>
       <c r="E15" s="26" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F15" s="27"/>
       <c r="G15" s="27"/>
       <c r="H15" s="28">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="J15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K15" s="21">
+        <v>65000</v>
+      </c>
+      <c r="L15" s="21">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="1:12">
       <c r="A16" s="29" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C16" s="31" t="s">
         <v>8</v>
@@ -2299,11 +2326,20 @@
       <c r="H16" s="33">
         <v>12478500</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="J16" t="s">
+        <v>41</v>
+      </c>
+      <c r="K16" s="21">
+        <v>85000</v>
+      </c>
+      <c r="L16" s="21">
+        <v>115000</v>
+      </c>
+    </row>
+    <row r="17" ht="15" spans="1:8">
       <c r="A17" s="29"/>
       <c r="B17" s="18" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C17" s="19" t="s">
         <v>8</v>
@@ -2324,10 +2360,10 @@
         <v>1800000</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" ht="15" spans="1:8">
       <c r="A18" s="29"/>
       <c r="B18" s="18" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C18" s="19" t="s">
         <v>8</v>
@@ -2348,10 +2384,10 @@
         <v>7025000</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" ht="15" spans="1:8">
       <c r="A19" s="29"/>
       <c r="B19" s="18" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C19" s="19" t="s">
         <v>8</v>
@@ -2375,7 +2411,7 @@
     <row r="20" ht="15" spans="1:8">
       <c r="A20" s="29"/>
       <c r="B20" s="18" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C20" s="23" t="s">
         <v>25</v>
@@ -2390,10 +2426,10 @@
       </c>
       <c r="H20" s="21"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" ht="15" spans="1:8">
       <c r="A21" s="29"/>
       <c r="B21" s="18" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>8</v>
@@ -2414,10 +2450,10 @@
         <v>1665000</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" ht="15" spans="1:8">
       <c r="A22" s="29"/>
       <c r="B22" s="18" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>8</v>
@@ -2436,10 +2472,10 @@
         <v>2110000</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" ht="15" spans="1:8">
       <c r="A23" s="29"/>
       <c r="B23" s="18" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C23" s="19" t="s">
         <v>8</v>
@@ -2463,7 +2499,7 @@
     <row r="24" ht="15" spans="1:8">
       <c r="A24" s="29"/>
       <c r="B24" s="18" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C24" s="23" t="s">
         <v>25</v>
@@ -2480,10 +2516,10 @@
       </c>
       <c r="H24" s="21"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" ht="15" spans="1:8">
       <c r="A25" s="29"/>
       <c r="B25" s="18" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C25" s="19" t="s">
         <v>8</v>
@@ -2504,10 +2540,10 @@
         <v>1190009</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" ht="15" spans="1:8">
       <c r="A26" s="29"/>
       <c r="B26" s="18" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>8</v>
@@ -2528,10 +2564,10 @@
         <v>5600000</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" ht="15" spans="1:8">
       <c r="A27" s="29"/>
       <c r="B27" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C27" s="19" t="s">
         <v>8</v>
@@ -2555,7 +2591,7 @@
     <row r="28" ht="15" spans="1:8">
       <c r="A28" s="29"/>
       <c r="B28" s="18" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C28" s="34" t="s">
         <v>25</v>
@@ -2573,7 +2609,7 @@
     <row r="29" ht="15" spans="1:8">
       <c r="A29" s="29"/>
       <c r="B29" s="18" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C29" s="19" t="s">
         <v>8</v>
@@ -2593,7 +2629,7 @@
     <row r="30" ht="15" spans="1:8">
       <c r="A30" s="29"/>
       <c r="B30" s="18" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C30" s="19" t="s">
         <v>8</v>
@@ -2602,18 +2638,18 @@
         <v>250000</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F30" s="20"/>
       <c r="G30" s="23" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H30" s="21"/>
     </row>
     <row r="31" ht="15" spans="1:8">
       <c r="A31" s="29"/>
       <c r="B31" s="18" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C31" s="34" t="s">
         <v>25</v>
@@ -2631,7 +2667,7 @@
     <row r="32" spans="1:8">
       <c r="A32" s="35"/>
       <c r="B32" s="36" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C32" s="37" t="s">
         <v>8</v>
@@ -2650,10 +2686,10 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>8</v>
@@ -2674,10 +2710,10 @@
         <v>4047600</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" ht="15" spans="1:8">
       <c r="A34" s="17"/>
       <c r="B34" s="18" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C34" s="19" t="s">
         <v>8</v>
@@ -2701,7 +2737,7 @@
     <row r="35" ht="15" spans="1:8">
       <c r="A35" s="17"/>
       <c r="B35" s="18" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C35" s="19" t="s">
         <v>8</v>
@@ -2725,7 +2761,7 @@
     <row r="36" spans="1:8">
       <c r="A36" s="24"/>
       <c r="B36" s="40" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C36" s="19" t="s">
         <v>8</v>
@@ -2748,10 +2784,10 @@
     </row>
     <row r="37" ht="15" spans="1:8">
       <c r="A37" s="43" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C37" s="44"/>
       <c r="D37" s="45"/>
@@ -2767,7 +2803,7 @@
     <row r="38" ht="15" spans="1:8">
       <c r="A38" s="43"/>
       <c r="B38" s="18" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C38" s="44"/>
       <c r="D38" s="45"/>
@@ -2783,7 +2819,7 @@
     <row r="39" ht="15" spans="1:8">
       <c r="A39" s="43"/>
       <c r="B39" s="18" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C39" s="44"/>
       <c r="D39" s="45"/>
@@ -2799,7 +2835,7 @@
     <row r="40" ht="15" spans="1:8">
       <c r="A40" s="43"/>
       <c r="B40" s="18" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C40" s="44"/>
       <c r="D40" s="45"/>
@@ -2815,7 +2851,7 @@
     <row r="41" ht="15" spans="1:8">
       <c r="A41" s="43"/>
       <c r="B41" s="18" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C41" s="44"/>
       <c r="D41" s="45"/>
@@ -2831,7 +2867,7 @@
     <row r="42" ht="15" spans="1:8">
       <c r="A42" s="43"/>
       <c r="B42" s="18" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C42" s="44"/>
       <c r="D42" s="45"/>
@@ -2847,7 +2883,7 @@
     <row r="43" ht="15" spans="1:8">
       <c r="A43" s="43"/>
       <c r="B43" s="18" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C43" s="44"/>
       <c r="D43" s="45"/>
@@ -2863,7 +2899,7 @@
     <row r="44" ht="15" spans="1:8">
       <c r="A44" s="43"/>
       <c r="B44" s="18" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C44" s="44"/>
       <c r="D44" s="45"/>
@@ -2879,7 +2915,7 @@
     <row r="45" ht="15" spans="1:8">
       <c r="A45" s="43"/>
       <c r="B45" s="18" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C45" s="44"/>
       <c r="D45" s="45"/>
@@ -2895,7 +2931,7 @@
     <row r="46" ht="15" spans="1:8">
       <c r="A46" s="47"/>
       <c r="B46" s="18" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C46" s="44"/>
       <c r="D46" s="45"/>
@@ -2925,7 +2961,7 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F52" s="4"/>
     </row>
@@ -2934,7 +2970,7 @@
         <v>25</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F53" s="4"/>
     </row>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -125,7 +125,7 @@
     <t>DISHY SOAP</t>
   </si>
   <si>
-    <t>DAILY BAGUETTE (NICO)</t>
+    <t>DAILY BAGUETTE</t>
   </si>
   <si>
     <t>abdi</t>
@@ -1910,7 +1910,7 @@
     <col min="8" max="8" width="13.6666666666667" style="4" customWidth="1"/>
     <col min="9" max="9" width="14.3333333333333"/>
     <col min="10" max="10" width="17.7142857142857" customWidth="1"/>
-    <col min="11" max="11" width="14.3333333333333"/>
+    <col min="11" max="11" width="15.4285714285714"/>
     <col min="12" max="12" width="22.6666666666667" customWidth="1"/>
     <col min="13" max="13" width="11.6666666666667"/>
   </cols>
@@ -1940,10 +1940,7 @@
       <c r="H1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="48" t="e">
-        <f>SUM(F2,F4,F8,#REF!,F13,F17,F24,F25,F34)</f>
-        <v>#REF!</v>
-      </c>
+      <c r="J1" s="48"/>
     </row>
     <row r="2" ht="15" spans="1:10">
       <c r="A2" s="12" t="s">
@@ -2246,7 +2243,7 @@
         <v>995000</v>
       </c>
     </row>
-    <row r="14" ht="15" spans="1:12">
+    <row r="14" spans="1:12">
       <c r="A14" s="17"/>
       <c r="B14" s="18" t="s">
         <v>32</v>
@@ -2282,11 +2279,15 @@
       <c r="C15" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="27"/>
+      <c r="D15" s="27">
+        <v>0</v>
+      </c>
       <c r="E15" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="27"/>
+      <c r="F15" s="27">
+        <v>10000000</v>
+      </c>
       <c r="G15" s="27"/>
       <c r="H15" s="28">
         <v>10000000</v>
@@ -2360,7 +2361,7 @@
         <v>1800000</v>
       </c>
     </row>
-    <row r="18" ht="15" spans="1:8">
+    <row r="18" spans="1:8">
       <c r="A18" s="29"/>
       <c r="B18" s="18" t="s">
         <v>43</v>
@@ -2384,7 +2385,7 @@
         <v>7025000</v>
       </c>
     </row>
-    <row r="19" ht="15" spans="1:8">
+    <row r="19" spans="1:11">
       <c r="A19" s="29"/>
       <c r="B19" s="18" t="s">
         <v>44</v>
@@ -2407,8 +2408,16 @@
       <c r="H19" s="21">
         <v>12023500</v>
       </c>
-    </row>
-    <row r="20" ht="15" spans="1:8">
+      <c r="J19" s="48">
+        <f>SUM(F8,F13,F17,F24,F25,F46)</f>
+        <v>20580036</v>
+      </c>
+      <c r="K19" s="48">
+        <f>SUM(H2:H35)</f>
+        <v>190854034</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="29"/>
       <c r="B20" s="18" t="s">
         <v>45</v>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7500"/>
+    <workbookView windowWidth="19635" windowHeight="6780"/>
   </bookViews>
   <sheets>
     <sheet name="SUPPLIER PAYMENT STATUS" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="79">
   <si>
     <t>DIVISION</t>
   </si>
@@ -159,6 +159,12 @@
   </si>
   <si>
     <t>PNB</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>November</t>
   </si>
   <si>
     <t>DSP</t>
@@ -1284,10 +1290,10 @@
     <xf numFmtId="179" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2052,7 +2058,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="1:10">
+    <row r="6" spans="1:10">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
         <v>18</v>
@@ -2079,7 +2085,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" ht="15" spans="1:10">
+    <row r="7" spans="1:10">
       <c r="A7" s="17"/>
       <c r="B7" s="18" t="s">
         <v>20</v>
@@ -2106,7 +2112,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="15" spans="1:10">
+    <row r="8" spans="1:10">
       <c r="A8" s="17"/>
       <c r="B8" s="18" t="s">
         <v>22</v>
@@ -2117,8 +2123,8 @@
       <c r="D8" s="20">
         <v>8775000</v>
       </c>
-      <c r="E8" s="22" t="s">
-        <v>10</v>
+      <c r="E8" s="19" t="s">
+        <v>8</v>
       </c>
       <c r="F8" s="20">
         <v>7800000</v>
@@ -2133,20 +2139,20 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="1:8">
+    <row r="9" spans="1:8">
       <c r="A9" s="17"/>
       <c r="B9" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="22" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="20"/>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="22" t="s">
         <v>25</v>
       </c>
       <c r="F9" s="20"/>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="22" t="s">
         <v>25</v>
       </c>
       <c r="H9" s="21"/>
@@ -2156,15 +2162,15 @@
       <c r="B10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="22" t="s">
         <v>25</v>
       </c>
       <c r="D10" s="20"/>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="22" t="s">
         <v>25</v>
       </c>
       <c r="F10" s="20"/>
-      <c r="G10" s="23" t="s">
+      <c r="G10" s="22" t="s">
         <v>25</v>
       </c>
       <c r="H10" s="21"/>
@@ -2177,7 +2183,7 @@
       <c r="B11" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="22" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="20"/>
@@ -2211,8 +2217,8 @@
       <c r="F12" s="20">
         <v>924000</v>
       </c>
-      <c r="G12" s="20" t="s">
-        <v>10</v>
+      <c r="G12" s="19" t="s">
+        <v>8</v>
       </c>
       <c r="H12" s="21">
         <v>594000</v>
@@ -2230,7 +2236,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="20"/>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="23" t="s">
         <v>10</v>
       </c>
       <c r="F13" s="20">
@@ -2243,7 +2249,7 @@
         <v>995000</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" ht="15" spans="1:12">
       <c r="A14" s="17"/>
       <c r="B14" s="18" t="s">
         <v>32</v>
@@ -2280,7 +2286,7 @@
         <v>36</v>
       </c>
       <c r="D15" s="27">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>37</v>
@@ -2348,7 +2354,7 @@
       <c r="D17" s="20">
         <v>3230000</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E17" s="23" t="s">
         <v>10</v>
       </c>
       <c r="F17" s="20">
@@ -2361,7 +2367,7 @@
         <v>1800000</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:11">
       <c r="A18" s="29"/>
       <c r="B18" s="18" t="s">
         <v>43</v>
@@ -2384,11 +2390,17 @@
       <c r="H18" s="21">
         <v>7025000</v>
       </c>
+      <c r="J18" t="s">
+        <v>44</v>
+      </c>
+      <c r="K18" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="29"/>
       <c r="B19" s="18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C19" s="19" t="s">
         <v>8</v>
@@ -2413,24 +2425,24 @@
         <v>20580036</v>
       </c>
       <c r="K19" s="48">
-        <f>SUM(H2:H35)</f>
-        <v>190854034</v>
+        <f>SUM(H2:H11,H13:H35)</f>
+        <v>190260034</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="29"/>
       <c r="B20" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="22" t="s">
         <v>25</v>
       </c>
       <c r="D20" s="20"/>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="22" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="20"/>
-      <c r="G20" s="23" t="s">
+      <c r="G20" s="22" t="s">
         <v>25</v>
       </c>
       <c r="H20" s="21"/>
@@ -2438,7 +2450,7 @@
     <row r="21" ht="15" spans="1:8">
       <c r="A21" s="29"/>
       <c r="B21" s="18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>8</v>
@@ -2462,7 +2474,7 @@
     <row r="22" ht="15" spans="1:8">
       <c r="A22" s="29"/>
       <c r="B22" s="18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>8</v>
@@ -2470,7 +2482,7 @@
       <c r="D22" s="20">
         <v>2410000</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="22" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="20"/>
@@ -2484,7 +2496,7 @@
     <row r="23" ht="15" spans="1:8">
       <c r="A23" s="29"/>
       <c r="B23" s="18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C23" s="19" t="s">
         <v>8</v>
@@ -2508,19 +2520,19 @@
     <row r="24" ht="15" spans="1:8">
       <c r="A24" s="29"/>
       <c r="B24" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="22" t="s">
         <v>25</v>
       </c>
       <c r="D24" s="20"/>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="23" t="s">
         <v>10</v>
       </c>
       <c r="F24" s="20">
         <v>2280000</v>
       </c>
-      <c r="G24" s="23" t="s">
+      <c r="G24" s="22" t="s">
         <v>25</v>
       </c>
       <c r="H24" s="21"/>
@@ -2528,7 +2540,7 @@
     <row r="25" ht="15" spans="1:8">
       <c r="A25" s="29"/>
       <c r="B25" s="18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C25" s="19" t="s">
         <v>8</v>
@@ -2536,7 +2548,7 @@
       <c r="D25" s="20">
         <v>4760036</v>
       </c>
-      <c r="E25" s="22" t="s">
+      <c r="E25" s="23" t="s">
         <v>10</v>
       </c>
       <c r="F25" s="20">
@@ -2552,7 +2564,7 @@
     <row r="26" ht="15" spans="1:8">
       <c r="A26" s="29"/>
       <c r="B26" s="18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>8</v>
@@ -2576,7 +2588,7 @@
     <row r="27" ht="15" spans="1:8">
       <c r="A27" s="29"/>
       <c r="B27" s="18" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C27" s="19" t="s">
         <v>8</v>
@@ -2600,17 +2612,17 @@
     <row r="28" ht="15" spans="1:8">
       <c r="A28" s="29"/>
       <c r="B28" s="18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C28" s="34" t="s">
         <v>25</v>
       </c>
       <c r="D28" s="20"/>
-      <c r="E28" s="23" t="s">
+      <c r="E28" s="22" t="s">
         <v>25</v>
       </c>
       <c r="F28" s="20"/>
-      <c r="G28" s="23" t="s">
+      <c r="G28" s="22" t="s">
         <v>25</v>
       </c>
       <c r="H28" s="21"/>
@@ -2618,7 +2630,7 @@
     <row r="29" ht="15" spans="1:8">
       <c r="A29" s="29"/>
       <c r="B29" s="18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C29" s="19" t="s">
         <v>8</v>
@@ -2626,11 +2638,11 @@
       <c r="D29" s="20">
         <v>3948000</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="E29" s="22" t="s">
         <v>25</v>
       </c>
       <c r="F29" s="20"/>
-      <c r="G29" s="23" t="s">
+      <c r="G29" s="22" t="s">
         <v>25</v>
       </c>
       <c r="H29" s="21"/>
@@ -2638,7 +2650,7 @@
     <row r="30" ht="15" spans="1:8">
       <c r="A30" s="29"/>
       <c r="B30" s="18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C30" s="19" t="s">
         <v>8</v>
@@ -2646,29 +2658,29 @@
       <c r="D30" s="20">
         <v>250000</v>
       </c>
-      <c r="E30" s="23" t="s">
-        <v>56</v>
+      <c r="E30" s="22" t="s">
+        <v>58</v>
       </c>
       <c r="F30" s="20"/>
-      <c r="G30" s="23" t="s">
-        <v>56</v>
+      <c r="G30" s="22" t="s">
+        <v>58</v>
       </c>
       <c r="H30" s="21"/>
     </row>
     <row r="31" ht="15" spans="1:8">
       <c r="A31" s="29"/>
       <c r="B31" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C31" s="34" t="s">
         <v>25</v>
       </c>
       <c r="D31" s="20"/>
-      <c r="E31" s="23" t="s">
+      <c r="E31" s="22" t="s">
         <v>25</v>
       </c>
       <c r="F31" s="20"/>
-      <c r="G31" s="23" t="s">
+      <c r="G31" s="22" t="s">
         <v>25</v>
       </c>
       <c r="H31" s="21"/>
@@ -2676,7 +2688,7 @@
     <row r="32" spans="1:8">
       <c r="A32" s="35"/>
       <c r="B32" s="36" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C32" s="37" t="s">
         <v>8</v>
@@ -2688,17 +2700,17 @@
       <c r="F32" s="38">
         <v>915750</v>
       </c>
-      <c r="G32" s="23" t="s">
+      <c r="G32" s="22" t="s">
         <v>25</v>
       </c>
       <c r="H32" s="39"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>8</v>
@@ -2722,7 +2734,7 @@
     <row r="34" ht="15" spans="1:8">
       <c r="A34" s="17"/>
       <c r="B34" s="18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C34" s="19" t="s">
         <v>8</v>
@@ -2746,7 +2758,7 @@
     <row r="35" ht="15" spans="1:8">
       <c r="A35" s="17"/>
       <c r="B35" s="18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C35" s="19" t="s">
         <v>8</v>
@@ -2770,7 +2782,7 @@
     <row r="36" spans="1:8">
       <c r="A36" s="24"/>
       <c r="B36" s="40" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C36" s="19" t="s">
         <v>8</v>
@@ -2793,10 +2805,10 @@
     </row>
     <row r="37" ht="15" spans="1:8">
       <c r="A37" s="43" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C37" s="44"/>
       <c r="D37" s="45"/>
@@ -2812,7 +2824,7 @@
     <row r="38" ht="15" spans="1:8">
       <c r="A38" s="43"/>
       <c r="B38" s="18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C38" s="44"/>
       <c r="D38" s="45"/>
@@ -2828,7 +2840,7 @@
     <row r="39" ht="15" spans="1:8">
       <c r="A39" s="43"/>
       <c r="B39" s="18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C39" s="44"/>
       <c r="D39" s="45"/>
@@ -2844,7 +2856,7 @@
     <row r="40" ht="15" spans="1:8">
       <c r="A40" s="43"/>
       <c r="B40" s="18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C40" s="44"/>
       <c r="D40" s="45"/>
@@ -2860,7 +2872,7 @@
     <row r="41" ht="15" spans="1:8">
       <c r="A41" s="43"/>
       <c r="B41" s="18" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C41" s="44"/>
       <c r="D41" s="45"/>
@@ -2876,7 +2888,7 @@
     <row r="42" ht="15" spans="1:8">
       <c r="A42" s="43"/>
       <c r="B42" s="18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C42" s="44"/>
       <c r="D42" s="45"/>
@@ -2892,7 +2904,7 @@
     <row r="43" ht="15" spans="1:8">
       <c r="A43" s="43"/>
       <c r="B43" s="18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C43" s="44"/>
       <c r="D43" s="45"/>
@@ -2908,7 +2920,7 @@
     <row r="44" ht="15" spans="1:8">
       <c r="A44" s="43"/>
       <c r="B44" s="18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C44" s="44"/>
       <c r="D44" s="45"/>
@@ -2924,7 +2936,7 @@
     <row r="45" ht="15" spans="1:8">
       <c r="A45" s="43"/>
       <c r="B45" s="18" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C45" s="44"/>
       <c r="D45" s="45"/>
@@ -2940,11 +2952,11 @@
     <row r="46" ht="15" spans="1:8">
       <c r="A46" s="47"/>
       <c r="B46" s="18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C46" s="44"/>
       <c r="D46" s="45"/>
-      <c r="E46" s="22" t="s">
+      <c r="E46" s="23" t="s">
         <v>10</v>
       </c>
       <c r="F46" s="20">
@@ -2970,7 +2982,7 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F52" s="4"/>
     </row>
@@ -2979,7 +2991,7 @@
         <v>25</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F53" s="4"/>
     </row>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="6780"/>
+    <workbookView windowWidth="19635" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="SUPPLIER PAYMENT STATUS" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="80">
   <si>
     <t>DIVISION</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>BALI PERMATA JAYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
   <si>
     <t>BLACKLIST COFFEE ROASTERS</t>
@@ -2058,7 +2061,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" ht="15" spans="1:10">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
         <v>18</v>
@@ -2085,7 +2088,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" ht="15" spans="1:10">
       <c r="A7" s="17"/>
       <c r="B7" s="18" t="s">
         <v>20</v>
@@ -2112,7 +2115,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" ht="15" spans="1:10">
       <c r="A8" s="17"/>
       <c r="B8" s="18" t="s">
         <v>22</v>
@@ -2139,7 +2142,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" ht="15" spans="1:8">
       <c r="A9" s="17"/>
       <c r="B9" s="18" t="s">
         <v>24</v>
@@ -2367,7 +2370,7 @@
         <v>1800000</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" ht="15" spans="1:11">
       <c r="A18" s="29"/>
       <c r="B18" s="18" t="s">
         <v>43</v>
@@ -2397,7 +2400,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" ht="15" spans="1:11">
       <c r="A19" s="29"/>
       <c r="B19" s="18" t="s">
         <v>46</v>
@@ -2429,7 +2432,7 @@
         <v>190260034</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" ht="15" spans="1:8">
       <c r="A20" s="29"/>
       <c r="B20" s="18" t="s">
         <v>47</v>
@@ -2537,7 +2540,7 @@
       </c>
       <c r="H24" s="21"/>
     </row>
-    <row r="25" ht="15" spans="1:8">
+    <row r="25" spans="1:8">
       <c r="A25" s="29"/>
       <c r="B25" s="18" t="s">
         <v>52</v>
@@ -2549,7 +2552,7 @@
         <v>4760036</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F25" s="20">
         <v>4760036</v>
@@ -2564,7 +2567,7 @@
     <row r="26" ht="15" spans="1:8">
       <c r="A26" s="29"/>
       <c r="B26" s="18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>8</v>
@@ -2588,7 +2591,7 @@
     <row r="27" ht="15" spans="1:8">
       <c r="A27" s="29"/>
       <c r="B27" s="18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C27" s="19" t="s">
         <v>8</v>
@@ -2612,7 +2615,7 @@
     <row r="28" ht="15" spans="1:8">
       <c r="A28" s="29"/>
       <c r="B28" s="18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C28" s="34" t="s">
         <v>25</v>
@@ -2630,7 +2633,7 @@
     <row r="29" ht="15" spans="1:8">
       <c r="A29" s="29"/>
       <c r="B29" s="18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C29" s="19" t="s">
         <v>8</v>
@@ -2650,7 +2653,7 @@
     <row r="30" ht="15" spans="1:8">
       <c r="A30" s="29"/>
       <c r="B30" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C30" s="19" t="s">
         <v>8</v>
@@ -2659,18 +2662,18 @@
         <v>250000</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F30" s="20"/>
       <c r="G30" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H30" s="21"/>
     </row>
     <row r="31" ht="15" spans="1:8">
       <c r="A31" s="29"/>
       <c r="B31" s="18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C31" s="34" t="s">
         <v>25</v>
@@ -2688,7 +2691,7 @@
     <row r="32" spans="1:8">
       <c r="A32" s="35"/>
       <c r="B32" s="36" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C32" s="37" t="s">
         <v>8</v>
@@ -2707,10 +2710,10 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>8</v>
@@ -2734,7 +2737,7 @@
     <row r="34" ht="15" spans="1:8">
       <c r="A34" s="17"/>
       <c r="B34" s="18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C34" s="19" t="s">
         <v>8</v>
@@ -2758,7 +2761,7 @@
     <row r="35" ht="15" spans="1:8">
       <c r="A35" s="17"/>
       <c r="B35" s="18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C35" s="19" t="s">
         <v>8</v>
@@ -2782,7 +2785,7 @@
     <row r="36" spans="1:8">
       <c r="A36" s="24"/>
       <c r="B36" s="40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C36" s="19" t="s">
         <v>8</v>
@@ -2805,10 +2808,10 @@
     </row>
     <row r="37" ht="15" spans="1:8">
       <c r="A37" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C37" s="44"/>
       <c r="D37" s="45"/>
@@ -2824,7 +2827,7 @@
     <row r="38" ht="15" spans="1:8">
       <c r="A38" s="43"/>
       <c r="B38" s="18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C38" s="44"/>
       <c r="D38" s="45"/>
@@ -2840,7 +2843,7 @@
     <row r="39" ht="15" spans="1:8">
       <c r="A39" s="43"/>
       <c r="B39" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C39" s="44"/>
       <c r="D39" s="45"/>
@@ -2856,7 +2859,7 @@
     <row r="40" ht="15" spans="1:8">
       <c r="A40" s="43"/>
       <c r="B40" s="18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C40" s="44"/>
       <c r="D40" s="45"/>
@@ -2872,7 +2875,7 @@
     <row r="41" ht="15" spans="1:8">
       <c r="A41" s="43"/>
       <c r="B41" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C41" s="44"/>
       <c r="D41" s="45"/>
@@ -2888,7 +2891,7 @@
     <row r="42" ht="15" spans="1:8">
       <c r="A42" s="43"/>
       <c r="B42" s="18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C42" s="44"/>
       <c r="D42" s="45"/>
@@ -2904,7 +2907,7 @@
     <row r="43" ht="15" spans="1:8">
       <c r="A43" s="43"/>
       <c r="B43" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C43" s="44"/>
       <c r="D43" s="45"/>
@@ -2920,7 +2923,7 @@
     <row r="44" ht="15" spans="1:8">
       <c r="A44" s="43"/>
       <c r="B44" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C44" s="44"/>
       <c r="D44" s="45"/>
@@ -2936,7 +2939,7 @@
     <row r="45" ht="15" spans="1:8">
       <c r="A45" s="43"/>
       <c r="B45" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C45" s="44"/>
       <c r="D45" s="45"/>
@@ -2952,7 +2955,7 @@
     <row r="46" ht="15" spans="1:8">
       <c r="A46" s="47"/>
       <c r="B46" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C46" s="44"/>
       <c r="D46" s="45"/>
@@ -2982,7 +2985,7 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F52" s="4"/>
     </row>
@@ -2991,7 +2994,7 @@
         <v>25</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F53" s="4"/>
     </row>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="68">
   <si>
     <t>DIVISION</t>
   </si>
@@ -62,45 +62,24 @@
     <t>POSTED</t>
   </si>
   <si>
-    <t>Bu bunga</t>
-  </si>
-  <si>
     <t>SEDANA JAYA</t>
   </si>
   <si>
-    <t>Sedana</t>
-  </si>
-  <si>
     <t>RAFI SEAFOOD</t>
   </si>
   <si>
-    <t>Surbled</t>
-  </si>
-  <si>
     <t>MAMA RADA PRODUCTION</t>
   </si>
   <si>
-    <t>Bali Permata Jaya</t>
-  </si>
-  <si>
     <t>KSP</t>
   </si>
   <si>
-    <t>Bayu agni</t>
-  </si>
-  <si>
     <t>SURYA CIPTA NIAGA</t>
   </si>
   <si>
-    <t>Abdi Jaya</t>
-  </si>
-  <si>
     <t>BAYU AGNI</t>
   </si>
   <si>
-    <t>Dishy soap</t>
-  </si>
-  <si>
     <t>JOY GREEN</t>
   </si>
   <si>
@@ -110,15 +89,9 @@
     <t>CELEBRITY BAKERY</t>
   </si>
   <si>
-    <t>Dewata coconut</t>
-  </si>
-  <si>
     <t>KROP</t>
   </si>
   <si>
-    <t>Nano Dewata</t>
-  </si>
-  <si>
     <t>BOILER</t>
   </si>
   <si>
@@ -161,12 +134,6 @@
     <t>PNB</t>
   </si>
   <si>
-    <t>October</t>
-  </si>
-  <si>
-    <t>November</t>
-  </si>
-  <si>
     <t>DSP</t>
   </si>
   <si>
@@ -186,9 +153,6 @@
   </si>
   <si>
     <t>BALI PERMATA JAYA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  </t>
   </si>
   <si>
     <t>BLACKLIST COFFEE ROASTERS</t>
@@ -1951,7 +1915,7 @@
       </c>
       <c r="J1" s="48"/>
     </row>
-    <row r="2" ht="15" spans="1:10">
+    <row r="2" spans="1:8">
       <c r="A2" s="12" t="s">
         <v>6</v>
       </c>
@@ -1976,14 +1940,11 @@
       <c r="H2" s="16">
         <v>34233500</v>
       </c>
-      <c r="J2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" ht="15" spans="1:10">
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>8</v>
@@ -2003,14 +1964,11 @@
       <c r="H3" s="21">
         <v>45303890</v>
       </c>
-      <c r="J3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" ht="15" spans="1:10">
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>8</v>
@@ -2030,14 +1988,11 @@
       <c r="H4" s="21">
         <v>20728100</v>
       </c>
-      <c r="J4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" ht="15" spans="1:10">
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="17"/>
       <c r="B5" s="18" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>8</v>
@@ -2057,14 +2012,11 @@
       <c r="H5" s="21">
         <v>320000</v>
       </c>
-      <c r="J5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" ht="15" spans="1:10">
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>8</v>
@@ -2084,14 +2036,11 @@
       <c r="H6" s="21">
         <v>5069850</v>
       </c>
-      <c r="J6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" ht="15" spans="1:10">
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="17"/>
       <c r="B7" s="18" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>8</v>
@@ -2105,20 +2054,17 @@
       <c r="F7" s="20">
         <v>1983600</v>
       </c>
-      <c r="G7" s="20" t="s">
-        <v>10</v>
+      <c r="G7" s="19" t="s">
+        <v>8</v>
       </c>
       <c r="H7" s="21">
         <v>13417600</v>
       </c>
-      <c r="J7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" ht="15" spans="1:10">
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="17"/>
       <c r="B8" s="18" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>8</v>
@@ -2138,56 +2084,50 @@
       <c r="H8" s="21">
         <v>3900000</v>
       </c>
-      <c r="J8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" ht="15" spans="1:8">
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="17"/>
       <c r="B9" s="18" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F9" s="20"/>
       <c r="G9" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H9" s="21"/>
     </row>
-    <row r="10" ht="15" spans="1:10">
+    <row r="10" spans="1:8">
       <c r="A10" s="17"/>
       <c r="B10" s="18" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F10" s="20"/>
       <c r="G10" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H10" s="21"/>
-      <c r="J10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" ht="15" spans="1:12">
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="17"/>
       <c r="B11" s="18" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D11" s="20"/>
       <c r="E11" s="19" t="s">
@@ -2200,15 +2140,12 @@
       <c r="H11" s="21">
         <v>152000</v>
       </c>
-      <c r="J11" t="s">
-        <v>29</v>
-      </c>
       <c r="L11" s="48"/>
     </row>
-    <row r="12" ht="15" spans="1:10">
+    <row r="12" spans="1:8">
       <c r="A12" s="17"/>
       <c r="B12" s="18" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>8</v>
@@ -2225,15 +2162,12 @@
       </c>
       <c r="H12" s="21">
         <v>594000</v>
-      </c>
-      <c r="J12" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="13" ht="15" spans="1:8">
       <c r="A13" s="17"/>
       <c r="B13" s="18" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>8</v>
@@ -2255,7 +2189,7 @@
     <row r="14" ht="15" spans="1:12">
       <c r="A14" s="17"/>
       <c r="B14" s="18" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C14" s="19" t="s">
         <v>8</v>
@@ -2267,32 +2201,32 @@
       <c r="F14" s="20">
         <v>2320000</v>
       </c>
-      <c r="G14" s="20" t="s">
-        <v>10</v>
+      <c r="G14" s="19" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="21">
         <v>2996000</v>
       </c>
       <c r="K14" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L14" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="24"/>
       <c r="B15" s="25" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D15" s="27">
         <v>10000000</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F15" s="27">
         <v>10000000</v>
@@ -2302,7 +2236,7 @@
         <v>10000000</v>
       </c>
       <c r="J15" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K15" s="21">
         <v>65000</v>
@@ -2313,10 +2247,10 @@
     </row>
     <row r="16" ht="15" spans="1:12">
       <c r="A16" s="29" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C16" s="31" t="s">
         <v>8</v>
@@ -2337,7 +2271,7 @@
         <v>12478500</v>
       </c>
       <c r="J16" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="K16" s="21">
         <v>85000</v>
@@ -2349,7 +2283,7 @@
     <row r="17" ht="15" spans="1:8">
       <c r="A17" s="29"/>
       <c r="B17" s="18" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C17" s="19" t="s">
         <v>8</v>
@@ -2370,10 +2304,10 @@
         <v>1800000</v>
       </c>
     </row>
-    <row r="18" ht="15" spans="1:11">
+    <row r="18" spans="1:8">
       <c r="A18" s="29"/>
       <c r="B18" s="18" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C18" s="19" t="s">
         <v>8</v>
@@ -2393,17 +2327,11 @@
       <c r="H18" s="21">
         <v>7025000</v>
       </c>
-      <c r="J18" t="s">
-        <v>44</v>
-      </c>
-      <c r="K18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" ht="15" spans="1:11">
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="29"/>
       <c r="B19" s="18" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C19" s="19" t="s">
         <v>8</v>
@@ -2423,37 +2351,31 @@
       <c r="H19" s="21">
         <v>12023500</v>
       </c>
-      <c r="J19" s="48">
-        <f>SUM(F8,F13,F17,F24,F25,F46)</f>
-        <v>20580036</v>
-      </c>
-      <c r="K19" s="48">
-        <f>SUM(H2:H11,H13:H35)</f>
-        <v>190260034</v>
-      </c>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
     </row>
     <row r="20" ht="15" spans="1:8">
       <c r="A20" s="29"/>
       <c r="B20" s="18" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D20" s="20"/>
       <c r="E20" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F20" s="20"/>
       <c r="G20" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H20" s="21"/>
     </row>
     <row r="21" ht="15" spans="1:8">
       <c r="A21" s="29"/>
       <c r="B21" s="18" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>8</v>
@@ -2477,7 +2399,7 @@
     <row r="22" ht="15" spans="1:8">
       <c r="A22" s="29"/>
       <c r="B22" s="18" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>8</v>
@@ -2486,7 +2408,7 @@
         <v>2410000</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F22" s="20"/>
       <c r="G22" s="20" t="s">
@@ -2499,7 +2421,7 @@
     <row r="23" ht="15" spans="1:8">
       <c r="A23" s="29"/>
       <c r="B23" s="18" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C23" s="19" t="s">
         <v>8</v>
@@ -2523,10 +2445,10 @@
     <row r="24" ht="15" spans="1:8">
       <c r="A24" s="29"/>
       <c r="B24" s="18" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D24" s="20"/>
       <c r="E24" s="23" t="s">
@@ -2536,14 +2458,14 @@
         <v>2280000</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H24" s="21"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" ht="15" spans="1:8">
       <c r="A25" s="29"/>
       <c r="B25" s="18" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C25" s="19" t="s">
         <v>8</v>
@@ -2552,7 +2474,7 @@
         <v>4760036</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="F25" s="20">
         <v>4760036</v>
@@ -2567,7 +2489,7 @@
     <row r="26" ht="15" spans="1:8">
       <c r="A26" s="29"/>
       <c r="B26" s="18" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>8</v>
@@ -2591,7 +2513,7 @@
     <row r="27" ht="15" spans="1:8">
       <c r="A27" s="29"/>
       <c r="B27" s="18" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C27" s="19" t="s">
         <v>8</v>
@@ -2615,25 +2537,25 @@
     <row r="28" ht="15" spans="1:8">
       <c r="A28" s="29"/>
       <c r="B28" s="18" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D28" s="20"/>
       <c r="E28" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F28" s="20"/>
       <c r="G28" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H28" s="21"/>
     </row>
     <row r="29" ht="15" spans="1:8">
       <c r="A29" s="29"/>
       <c r="B29" s="18" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C29" s="19" t="s">
         <v>8</v>
@@ -2642,18 +2564,18 @@
         <v>3948000</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F29" s="20"/>
       <c r="G29" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H29" s="21"/>
     </row>
     <row r="30" ht="15" spans="1:8">
       <c r="A30" s="29"/>
       <c r="B30" s="18" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C30" s="19" t="s">
         <v>8</v>
@@ -2662,36 +2584,36 @@
         <v>250000</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F30" s="20"/>
       <c r="G30" s="22" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="H30" s="21"/>
     </row>
     <row r="31" ht="15" spans="1:8">
       <c r="A31" s="29"/>
       <c r="B31" s="18" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D31" s="20"/>
       <c r="E31" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F31" s="20"/>
       <c r="G31" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H31" s="21"/>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="35"/>
       <c r="B32" s="36" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="C32" s="37" t="s">
         <v>8</v>
@@ -2704,16 +2626,16 @@
         <v>915750</v>
       </c>
       <c r="G32" s="22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H32" s="39"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="12" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>8</v>
@@ -2737,7 +2659,7 @@
     <row r="34" ht="15" spans="1:8">
       <c r="A34" s="17"/>
       <c r="B34" s="18" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C34" s="19" t="s">
         <v>8</v>
@@ -2761,7 +2683,7 @@
     <row r="35" ht="15" spans="1:8">
       <c r="A35" s="17"/>
       <c r="B35" s="18" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C35" s="19" t="s">
         <v>8</v>
@@ -2785,7 +2707,7 @@
     <row r="36" spans="1:8">
       <c r="A36" s="24"/>
       <c r="B36" s="40" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C36" s="19" t="s">
         <v>8</v>
@@ -2808,10 +2730,10 @@
     </row>
     <row r="37" ht="15" spans="1:8">
       <c r="A37" s="43" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C37" s="44"/>
       <c r="D37" s="45"/>
@@ -2827,7 +2749,7 @@
     <row r="38" ht="15" spans="1:8">
       <c r="A38" s="43"/>
       <c r="B38" s="18" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="C38" s="44"/>
       <c r="D38" s="45"/>
@@ -2843,7 +2765,7 @@
     <row r="39" ht="15" spans="1:8">
       <c r="A39" s="43"/>
       <c r="B39" s="18" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C39" s="44"/>
       <c r="D39" s="45"/>
@@ -2859,7 +2781,7 @@
     <row r="40" ht="15" spans="1:8">
       <c r="A40" s="43"/>
       <c r="B40" s="18" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C40" s="44"/>
       <c r="D40" s="45"/>
@@ -2875,7 +2797,7 @@
     <row r="41" ht="15" spans="1:8">
       <c r="A41" s="43"/>
       <c r="B41" s="18" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C41" s="44"/>
       <c r="D41" s="45"/>
@@ -2891,7 +2813,7 @@
     <row r="42" ht="15" spans="1:8">
       <c r="A42" s="43"/>
       <c r="B42" s="18" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C42" s="44"/>
       <c r="D42" s="45"/>
@@ -2907,7 +2829,7 @@
     <row r="43" ht="15" spans="1:8">
       <c r="A43" s="43"/>
       <c r="B43" s="18" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C43" s="44"/>
       <c r="D43" s="45"/>
@@ -2923,7 +2845,7 @@
     <row r="44" ht="15" spans="1:8">
       <c r="A44" s="43"/>
       <c r="B44" s="18" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C44" s="44"/>
       <c r="D44" s="45"/>
@@ -2939,7 +2861,7 @@
     <row r="45" ht="15" spans="1:8">
       <c r="A45" s="43"/>
       <c r="B45" s="18" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C45" s="44"/>
       <c r="D45" s="45"/>
@@ -2955,7 +2877,7 @@
     <row r="46" ht="15" spans="1:8">
       <c r="A46" s="47"/>
       <c r="B46" s="18" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C46" s="44"/>
       <c r="D46" s="45"/>
@@ -2985,16 +2907,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F52" s="4"/>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="F53" s="4"/>
     </row>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7500"/>
+    <workbookView windowWidth="19635" windowHeight="6780"/>
   </bookViews>
   <sheets>
     <sheet name="SUPPLIER PAYMENT STATUS" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="70">
   <si>
     <t>DIVISION</t>
   </si>
@@ -59,12 +59,15 @@
     <t>PAID 100%</t>
   </si>
   <si>
+    <t>MAKER</t>
+  </si>
+  <si>
+    <t>SEDANA JAYA</t>
+  </si>
+  <si>
     <t>POSTED</t>
   </si>
   <si>
-    <t>SEDANA JAYA</t>
-  </si>
-  <si>
     <t>RAFI SEAFOOD</t>
   </si>
   <si>
@@ -75,6 +78,9 @@
   </si>
   <si>
     <t>SURYA CIPTA NIAGA</t>
+  </si>
+  <si>
+    <t>PAID 1/2</t>
   </si>
   <si>
     <t>BAYU AGNI</t>
@@ -419,7 +425,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -453,6 +459,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -741,6 +753,21 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -754,21 +781,6 @@
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
@@ -1066,7 +1078,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="22" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="22" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1090,16 +1102,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1108,89 +1120,89 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1239,28 +1251,31 @@
     <xf numFmtId="179" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="179" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1293,7 +1308,7 @@
     <xf numFmtId="179" fontId="0" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1913,9 +1928,9 @@
       <c r="H1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="48"/>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="J1" s="49"/>
+    </row>
+    <row r="2" ht="15" spans="1:8">
       <c r="A2" s="12" t="s">
         <v>6</v>
       </c>
@@ -1934,708 +1949,708 @@
       <c r="F2" s="15">
         <v>39738000</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="16">
+      <c r="H2" s="17">
         <v>34233500</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="17"/>
-      <c r="B3" s="18" t="s">
+    <row r="3" ht="15" spans="1:8">
+      <c r="A3" s="18"/>
+      <c r="B3" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="20">
+      <c r="C3" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="21">
         <v>45478060</v>
       </c>
-      <c r="E3" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="20">
+      <c r="E3" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="21">
         <v>39027410</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="22">
+        <v>45303890</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="1:8">
+      <c r="A4" s="18"/>
+      <c r="B4" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="21">
+        <v>29900100</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="21">
+        <v>20617200</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="22">
+        <v>20728100</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="1:8">
+      <c r="A5" s="18"/>
+      <c r="B5" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="21">
+        <v>4400000</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="21">
+        <v>5560000</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="22">
+        <v>320000</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="1:8">
+      <c r="A6" s="18"/>
+      <c r="B6" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="21">
+        <v>5610900</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="21">
+        <v>3578050</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="21">
-        <v>45303890</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="17"/>
-      <c r="B4" s="18" t="s">
+      <c r="H6" s="22">
+        <v>5069850</v>
+      </c>
+    </row>
+    <row r="7" ht="15" spans="1:8">
+      <c r="A7" s="18"/>
+      <c r="B7" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="21">
+        <v>3663300</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="21">
+        <v>1983600</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="22">
+        <v>13417600</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="1:8">
+      <c r="A8" s="18"/>
+      <c r="B8" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="21">
+        <v>8775000</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="21">
+        <v>7800000</v>
+      </c>
+      <c r="G8" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="20">
-        <v>29900100</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="20">
-        <v>20617200</v>
-      </c>
-      <c r="G4" s="20" t="s">
+      <c r="H8" s="22">
+        <v>3900000</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:8">
+      <c r="A9" s="18"/>
+      <c r="B9" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="E9" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="21"/>
+      <c r="G9" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="22"/>
+    </row>
+    <row r="10" ht="15" spans="1:8">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="21"/>
+      <c r="E10" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="21"/>
+      <c r="G10" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="22"/>
+    </row>
+    <row r="11" ht="15" spans="1:12">
+      <c r="A11" s="18"/>
+      <c r="B11" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="21"/>
+      <c r="E11" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="21">
+        <v>326000</v>
+      </c>
+      <c r="G11" s="21"/>
+      <c r="H11" s="22">
+        <v>152000</v>
+      </c>
+      <c r="L11" s="49"/>
+    </row>
+    <row r="12" ht="15" spans="1:8">
+      <c r="A12" s="18"/>
+      <c r="B12" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="21"/>
+      <c r="E12" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="21">
+        <v>924000</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="22">
+        <v>594000</v>
+      </c>
+    </row>
+    <row r="13" ht="15" spans="1:8">
+      <c r="A13" s="18"/>
+      <c r="B13" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="21"/>
+      <c r="E13" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="21">
+        <v>1525000</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="22">
+        <v>995000</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="1:12">
+      <c r="A14" s="18"/>
+      <c r="B14" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="21"/>
+      <c r="E14" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="21">
+        <v>2320000</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="22">
+        <v>2996000</v>
+      </c>
+      <c r="K14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="25"/>
+      <c r="B15" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="28">
+        <v>10000000</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="28">
+        <v>10000000</v>
+      </c>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29">
+        <v>10000000</v>
+      </c>
+      <c r="J15" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" s="22">
+        <v>65000</v>
+      </c>
+      <c r="L15" s="22">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="1:12">
+      <c r="A16" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="33">
+        <v>20669000</v>
+      </c>
+      <c r="E16" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="33">
+        <v>13909500</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="34">
+        <v>12478500</v>
+      </c>
+      <c r="J16" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="22">
+        <v>85000</v>
+      </c>
+      <c r="L16" s="22">
+        <v>115000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="30"/>
+      <c r="B17" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="21">
+        <v>3230000</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="21">
-        <v>20728100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="17"/>
-      <c r="B5" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="20">
-        <v>4400000</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="20">
-        <v>5560000</v>
-      </c>
-      <c r="G5" s="20" t="s">
+      <c r="F17" s="21">
+        <v>2415000</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="22">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="1:8">
+      <c r="A18" s="30"/>
+      <c r="B18" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="21">
+        <v>10775000</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="21">
+        <v>10000000</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="22">
+        <v>7025000</v>
+      </c>
+    </row>
+    <row r="19" ht="15" spans="1:11">
+      <c r="A19" s="30"/>
+      <c r="B19" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="21">
+        <v>10023000</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="21">
+        <v>6637500</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="22">
+        <v>12023500</v>
+      </c>
+      <c r="J19" s="49"/>
+      <c r="K19" s="49"/>
+    </row>
+    <row r="20" ht="15" spans="1:8">
+      <c r="A20" s="30"/>
+      <c r="B20" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="21"/>
+      <c r="E20" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="21"/>
+      <c r="G20" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="22"/>
+    </row>
+    <row r="21" ht="15" spans="1:8">
+      <c r="A21" s="30"/>
+      <c r="B21" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="21">
+        <v>3663000</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="21">
+        <v>1998000</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="22">
+        <v>1665000</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="1:8">
+      <c r="A22" s="30"/>
+      <c r="B22" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="21">
+        <v>2410000</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" s="22">
+        <v>2110000</v>
+      </c>
+    </row>
+    <row r="23" ht="15" spans="1:8">
+      <c r="A23" s="30"/>
+      <c r="B23" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="21">
+        <v>2447502</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="21">
+        <v>1312502</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="22">
+        <v>1750003</v>
+      </c>
+    </row>
+    <row r="24" ht="15" spans="1:8">
+      <c r="A24" s="30"/>
+      <c r="B24" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="21"/>
+      <c r="E24" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="21">
+        <v>2280000</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="22"/>
+    </row>
+    <row r="25" ht="15" spans="1:8">
+      <c r="A25" s="30"/>
+      <c r="B25" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="21">
+        <v>4760036</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="21">
+        <v>4760036</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="22">
+        <v>1190009</v>
+      </c>
+    </row>
+    <row r="26" ht="15" spans="1:8">
+      <c r="A26" s="30"/>
+      <c r="B26" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="21">
+        <v>5600000</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="21">
+        <v>5600000</v>
+      </c>
+      <c r="G26" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="21">
-        <v>320000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="17"/>
-      <c r="B6" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="20">
-        <v>5610900</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="20">
-        <v>3578050</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="21">
-        <v>5069850</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="17"/>
-      <c r="B7" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="20">
-        <v>3663300</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="20">
-        <v>1983600</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" s="21">
-        <v>13417600</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="17"/>
-      <c r="B8" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="20">
-        <v>8775000</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="20">
-        <v>7800000</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="21">
-        <v>3900000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="17"/>
-      <c r="B9" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="20"/>
-      <c r="G9" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="21"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="17"/>
-      <c r="B10" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="20"/>
-      <c r="G10" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="21"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="17"/>
-      <c r="B11" s="18" t="s">
+      <c r="H26" s="22">
+        <v>5600000</v>
+      </c>
+    </row>
+    <row r="27" ht="15" spans="1:8">
+      <c r="A27" s="30"/>
+      <c r="B27" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="21">
+        <v>1225000</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="21">
+        <v>915750</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="22">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="1:8">
+      <c r="A28" s="30"/>
+      <c r="B28" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="20">
-        <v>326000</v>
-      </c>
-      <c r="G11" s="20"/>
-      <c r="H11" s="21">
-        <v>152000</v>
-      </c>
-      <c r="L11" s="48"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="17"/>
-      <c r="B12" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="20">
-        <v>924000</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="21">
-        <v>594000</v>
-      </c>
-    </row>
-    <row r="13" ht="15" spans="1:8">
-      <c r="A13" s="17"/>
-      <c r="B13" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="20">
-        <v>1525000</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="21">
-        <v>995000</v>
-      </c>
-    </row>
-    <row r="14" ht="15" spans="1:12">
-      <c r="A14" s="17"/>
-      <c r="B14" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="20">
-        <v>2320000</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="21">
-        <v>2996000</v>
-      </c>
-      <c r="K14" t="s">
-        <v>24</v>
-      </c>
-      <c r="L14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="27">
-        <v>10000000</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="27">
-        <v>10000000</v>
-      </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="28">
-        <v>10000000</v>
-      </c>
-      <c r="J15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K15" s="21">
-        <v>65000</v>
-      </c>
-      <c r="L15" s="21">
-        <v>110000</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="1:12">
-      <c r="A16" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="32">
-        <v>20669000</v>
-      </c>
-      <c r="E16" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="32">
-        <v>13909500</v>
-      </c>
-      <c r="G16" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" s="33">
-        <v>12478500</v>
-      </c>
-      <c r="J16" t="s">
-        <v>32</v>
-      </c>
-      <c r="K16" s="21">
-        <v>85000</v>
-      </c>
-      <c r="L16" s="21">
-        <v>115000</v>
-      </c>
-    </row>
-    <row r="17" ht="15" spans="1:8">
-      <c r="A17" s="29"/>
-      <c r="B17" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="20">
-        <v>3230000</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="20">
-        <v>2415000</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H17" s="21">
-        <v>1800000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="29"/>
-      <c r="B18" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="20">
-        <v>10775000</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="20">
-        <v>10000000</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H18" s="21">
-        <v>7025000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="29"/>
-      <c r="B19" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="20">
-        <v>10023000</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="20">
-        <v>6637500</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H19" s="21">
-        <v>12023500</v>
-      </c>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-    </row>
-    <row r="20" ht="15" spans="1:8">
-      <c r="A20" s="29"/>
-      <c r="B20" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="20"/>
-      <c r="G20" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H20" s="21"/>
-    </row>
-    <row r="21" ht="15" spans="1:8">
-      <c r="A21" s="29"/>
-      <c r="B21" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="20">
-        <v>3663000</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="20">
-        <v>1998000</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H21" s="21">
-        <v>1665000</v>
-      </c>
-    </row>
-    <row r="22" ht="15" spans="1:8">
-      <c r="A22" s="29"/>
-      <c r="B22" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="20">
-        <v>2410000</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H22" s="21">
-        <v>2110000</v>
-      </c>
-    </row>
-    <row r="23" ht="15" spans="1:8">
-      <c r="A23" s="29"/>
-      <c r="B23" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="20">
-        <v>2447502</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="20">
-        <v>1312502</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H23" s="21">
-        <v>1750003</v>
-      </c>
-    </row>
-    <row r="24" ht="15" spans="1:8">
-      <c r="A24" s="29"/>
-      <c r="B24" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="20">
-        <v>2280000</v>
-      </c>
-      <c r="G24" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H24" s="21"/>
-    </row>
-    <row r="25" ht="15" spans="1:8">
-      <c r="A25" s="29"/>
-      <c r="B25" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="20">
-        <v>4760036</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="20">
-        <v>4760036</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H25" s="21">
-        <v>1190009</v>
-      </c>
-    </row>
-    <row r="26" ht="15" spans="1:8">
-      <c r="A26" s="29"/>
-      <c r="B26" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="20">
-        <v>5600000</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="20">
-        <v>5600000</v>
-      </c>
-      <c r="G26" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H26" s="21">
-        <v>5600000</v>
-      </c>
-    </row>
-    <row r="27" ht="15" spans="1:8">
-      <c r="A27" s="29"/>
-      <c r="B27" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="20">
-        <v>1225000</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="20">
+      <c r="D28" s="21"/>
+      <c r="E28" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" s="21"/>
+      <c r="G28" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="22"/>
+    </row>
+    <row r="29" ht="15" spans="1:8">
+      <c r="A29" s="30"/>
+      <c r="B29" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="21">
+        <v>3948000</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="21"/>
+      <c r="G29" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="22"/>
+    </row>
+    <row r="30" ht="15" spans="1:8">
+      <c r="A30" s="30"/>
+      <c r="B30" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="21">
+        <v>250000</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" s="21"/>
+      <c r="G30" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="H30" s="22"/>
+    </row>
+    <row r="31" ht="15" spans="1:8">
+      <c r="A31" s="30"/>
+      <c r="B31" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="21"/>
+      <c r="E31" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31" s="21"/>
+      <c r="G31" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="22"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="36"/>
+      <c r="B32" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="39"/>
+      <c r="E32" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="39">
         <v>915750</v>
       </c>
-      <c r="G27" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H27" s="21">
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="1:8">
-      <c r="A28" s="29"/>
-      <c r="B28" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F28" s="20"/>
-      <c r="G28" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H28" s="21"/>
-    </row>
-    <row r="29" ht="15" spans="1:8">
-      <c r="A29" s="29"/>
-      <c r="B29" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="20">
-        <v>3948000</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F29" s="20"/>
-      <c r="G29" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H29" s="21"/>
-    </row>
-    <row r="30" ht="15" spans="1:8">
-      <c r="A30" s="29"/>
-      <c r="B30" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="20">
-        <v>250000</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="F30" s="20"/>
-      <c r="G30" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="H30" s="21"/>
-    </row>
-    <row r="31" ht="15" spans="1:8">
-      <c r="A31" s="29"/>
-      <c r="B31" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F31" s="20"/>
-      <c r="G31" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H31" s="21"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="35"/>
-      <c r="B32" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="38"/>
-      <c r="E32" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="38">
-        <v>915750</v>
-      </c>
-      <c r="G32" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H32" s="39"/>
+      <c r="G32" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="40"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>8</v>
@@ -2650,245 +2665,245 @@
         <v>8368100</v>
       </c>
       <c r="G33" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H33" s="17">
+        <v>4047600</v>
+      </c>
+    </row>
+    <row r="34" ht="15" spans="1:8">
+      <c r="A34" s="18"/>
+      <c r="B34" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="21">
+        <v>4375000</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" s="21">
+        <v>4715000</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H34" s="22">
+        <v>2585000</v>
+      </c>
+    </row>
+    <row r="35" ht="15" spans="1:8">
+      <c r="A35" s="18"/>
+      <c r="B35" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="21">
+        <v>1007480.64</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="21">
+        <v>638483</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H35" s="21">
+        <v>269482</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="25"/>
+      <c r="B36" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="21">
+        <v>1168000</v>
+      </c>
+      <c r="E36" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="43">
+        <v>893000</v>
+      </c>
+      <c r="G36" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="H36" s="21">
+        <v>847000</v>
+      </c>
+    </row>
+    <row r="37" ht="15" spans="1:8">
+      <c r="A37" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="45"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" s="21">
+        <v>1020000</v>
+      </c>
+      <c r="G37" s="46"/>
+      <c r="H37" s="47"/>
+    </row>
+    <row r="38" ht="15" spans="1:8">
+      <c r="A38" s="44"/>
+      <c r="B38" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="45"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="21">
+        <v>1350000</v>
+      </c>
+      <c r="G38" s="46"/>
+      <c r="H38" s="47"/>
+    </row>
+    <row r="39" ht="15" spans="1:8">
+      <c r="A39" s="44"/>
+      <c r="B39" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="45"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" s="21">
+        <v>600000</v>
+      </c>
+      <c r="G39" s="46"/>
+      <c r="H39" s="47"/>
+    </row>
+    <row r="40" ht="15" spans="1:8">
+      <c r="A40" s="44"/>
+      <c r="B40" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="45"/>
+      <c r="D40" s="46"/>
+      <c r="E40" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" s="21">
+        <v>318134</v>
+      </c>
+      <c r="G40" s="46"/>
+      <c r="H40" s="47"/>
+    </row>
+    <row r="41" ht="15" spans="1:8">
+      <c r="A41" s="44"/>
+      <c r="B41" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" s="45"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="21">
+        <v>248700</v>
+      </c>
+      <c r="G41" s="46"/>
+      <c r="H41" s="47"/>
+    </row>
+    <row r="42" ht="15" spans="1:8">
+      <c r="A42" s="44"/>
+      <c r="B42" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="45"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="21">
+        <v>1029180</v>
+      </c>
+      <c r="G42" s="46"/>
+      <c r="H42" s="47"/>
+    </row>
+    <row r="43" ht="15" spans="1:8">
+      <c r="A43" s="44"/>
+      <c r="B43" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="45"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="21">
+        <v>270000</v>
+      </c>
+      <c r="G43" s="46"/>
+      <c r="H43" s="47"/>
+    </row>
+    <row r="44" ht="15" spans="1:8">
+      <c r="A44" s="44"/>
+      <c r="B44" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="45"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="21">
+        <v>1000000</v>
+      </c>
+      <c r="G44" s="46"/>
+      <c r="H44" s="47"/>
+    </row>
+    <row r="45" ht="15" spans="1:8">
+      <c r="A45" s="44"/>
+      <c r="B45" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" s="45"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="21">
+        <v>3000000</v>
+      </c>
+      <c r="G45" s="46"/>
+      <c r="H45" s="47"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="48"/>
+      <c r="B46" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" s="45"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="H33" s="16">
-        <v>4047600</v>
-      </c>
-    </row>
-    <row r="34" ht="15" spans="1:8">
-      <c r="A34" s="17"/>
-      <c r="B34" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="20">
-        <v>4375000</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" s="20">
-        <v>4715000</v>
-      </c>
-      <c r="G34" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H34" s="21">
-        <v>2585000</v>
-      </c>
-    </row>
-    <row r="35" ht="15" spans="1:8">
-      <c r="A35" s="17"/>
-      <c r="B35" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="20">
-        <v>1007480.64</v>
-      </c>
-      <c r="E35" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="20">
-        <v>638483</v>
-      </c>
-      <c r="G35" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H35" s="20">
-        <v>269482</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="24"/>
-      <c r="B36" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="20">
-        <v>1168000</v>
-      </c>
-      <c r="E36" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="42">
-        <v>893000</v>
-      </c>
-      <c r="G36" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="H36" s="20">
-        <v>847000</v>
-      </c>
-    </row>
-    <row r="37" ht="15" spans="1:8">
-      <c r="A37" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37" s="44"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="20">
-        <v>1020000</v>
-      </c>
-      <c r="G37" s="45"/>
-      <c r="H37" s="46"/>
-    </row>
-    <row r="38" ht="15" spans="1:8">
-      <c r="A38" s="43"/>
-      <c r="B38" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" s="44"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="20">
-        <v>1350000</v>
-      </c>
-      <c r="G38" s="45"/>
-      <c r="H38" s="46"/>
-    </row>
-    <row r="39" ht="15" spans="1:8">
-      <c r="A39" s="43"/>
-      <c r="B39" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C39" s="44"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="20">
-        <v>600000</v>
-      </c>
-      <c r="G39" s="45"/>
-      <c r="H39" s="46"/>
-    </row>
-    <row r="40" ht="15" spans="1:8">
-      <c r="A40" s="43"/>
-      <c r="B40" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C40" s="44"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="20">
-        <v>318134</v>
-      </c>
-      <c r="G40" s="45"/>
-      <c r="H40" s="46"/>
-    </row>
-    <row r="41" ht="15" spans="1:8">
-      <c r="A41" s="43"/>
-      <c r="B41" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="C41" s="44"/>
-      <c r="D41" s="45"/>
-      <c r="E41" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="20">
-        <v>248700</v>
-      </c>
-      <c r="G41" s="45"/>
-      <c r="H41" s="46"/>
-    </row>
-    <row r="42" ht="15" spans="1:8">
-      <c r="A42" s="43"/>
-      <c r="B42" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C42" s="44"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="20">
-        <v>1029180</v>
-      </c>
-      <c r="G42" s="45"/>
-      <c r="H42" s="46"/>
-    </row>
-    <row r="43" ht="15" spans="1:8">
-      <c r="A43" s="43"/>
-      <c r="B43" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="C43" s="44"/>
-      <c r="D43" s="45"/>
-      <c r="E43" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="20">
-        <v>270000</v>
-      </c>
-      <c r="G43" s="45"/>
-      <c r="H43" s="46"/>
-    </row>
-    <row r="44" ht="15" spans="1:8">
-      <c r="A44" s="43"/>
-      <c r="B44" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="C44" s="44"/>
-      <c r="D44" s="45"/>
-      <c r="E44" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="20">
-        <v>1000000</v>
-      </c>
-      <c r="G44" s="45"/>
-      <c r="H44" s="46"/>
-    </row>
-    <row r="45" ht="15" spans="1:8">
-      <c r="A45" s="43"/>
-      <c r="B45" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="C45" s="44"/>
-      <c r="D45" s="45"/>
-      <c r="E45" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="20">
-        <v>3000000</v>
-      </c>
-      <c r="G45" s="45"/>
-      <c r="H45" s="46"/>
-    </row>
-    <row r="46" ht="15" spans="1:8">
-      <c r="A46" s="47"/>
-      <c r="B46" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C46" s="44"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="20">
+      <c r="F46" s="21">
         <v>1800000</v>
       </c>
-      <c r="G46" s="45"/>
-      <c r="H46" s="46"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="47"/>
     </row>
     <row r="47" spans="6:6">
       <c r="F47" s="4"/>
@@ -2907,16 +2922,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F52" s="4"/>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F53" s="4"/>
     </row>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="6780"/>
+    <workbookView windowHeight="17000"/>
   </bookViews>
   <sheets>
     <sheet name="SUPPLIER PAYMENT STATUS" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="71">
   <si>
     <t>DIVISION</t>
   </si>
@@ -59,51 +59,51 @@
     <t>PAID 100%</t>
   </si>
   <si>
+    <t>PAID 1/2</t>
+  </si>
+  <si>
+    <t>SEDANA JAYA</t>
+  </si>
+  <si>
+    <t>POSTED</t>
+  </si>
+  <si>
+    <t>RAFI SEAFOOD</t>
+  </si>
+  <si>
+    <t>MAMA RADA PRODUCTION</t>
+  </si>
+  <si>
+    <t>KSP</t>
+  </si>
+  <si>
+    <t>SURYA CIPTA NIAGA</t>
+  </si>
+  <si>
+    <t>BAYU AGNI</t>
+  </si>
+  <si>
+    <t>JOY GREEN</t>
+  </si>
+  <si>
+    <t>N/O</t>
+  </si>
+  <si>
+    <t>CELEBRITY BAKERY</t>
+  </si>
+  <si>
+    <t>KROP</t>
+  </si>
+  <si>
+    <t>BOILER</t>
+  </si>
+  <si>
+    <t>DISHY SOAP</t>
+  </si>
+  <si>
     <t>MAKER</t>
   </si>
   <si>
-    <t>SEDANA JAYA</t>
-  </si>
-  <si>
-    <t>POSTED</t>
-  </si>
-  <si>
-    <t>RAFI SEAFOOD</t>
-  </si>
-  <si>
-    <t>MAMA RADA PRODUCTION</t>
-  </si>
-  <si>
-    <t>KSP</t>
-  </si>
-  <si>
-    <t>SURYA CIPTA NIAGA</t>
-  </si>
-  <si>
-    <t>PAID 1/2</t>
-  </si>
-  <si>
-    <t>BAYU AGNI</t>
-  </si>
-  <si>
-    <t>JOY GREEN</t>
-  </si>
-  <si>
-    <t>N/O</t>
-  </si>
-  <si>
-    <t>CELEBRITY BAKERY</t>
-  </si>
-  <si>
-    <t>KROP</t>
-  </si>
-  <si>
-    <t>BOILER</t>
-  </si>
-  <si>
-    <t>DISHY SOAP</t>
-  </si>
-  <si>
     <t>DAILY BAGUETTE</t>
   </si>
   <si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>BAR CHILLER MAINTENANCE</t>
+  </si>
+  <si>
+    <t>PIZZA BOX (CUSTOM)</t>
   </si>
   <si>
     <t>LEGEND:</t>
@@ -244,12 +247,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="6">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    <numFmt numFmtId="181" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -464,13 +467,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -707,19 +710,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -750,7 +740,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color auto="1"/>
       </left>
       <right style="thin">
@@ -768,10 +758,10 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -789,7 +779,7 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -798,52 +788,7 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
       <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="thin">
@@ -879,19 +824,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -909,19 +841,6 @@
         <color auto="1"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
         <color auto="1"/>
       </right>
       <top/>
@@ -952,6 +871,90 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1060,16 +1063,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1202,11 +1205,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1215,10 +1218,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1227,37 +1230,22 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1266,91 +1254,112 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1887,23 +1896,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultColWidth="9.16190476190476" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="18.8571428571429" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.3333333333333" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.3333333333333" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.3333333333333" customWidth="1"/>
-    <col min="5" max="5" width="12.5714285714286" style="3" customWidth="1"/>
-    <col min="6" max="7" width="13.6666666666667" customWidth="1"/>
-    <col min="8" max="8" width="13.6666666666667" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.3333333333333"/>
-    <col min="10" max="10" width="17.7142857142857" customWidth="1"/>
-    <col min="11" max="11" width="15.4285714285714"/>
-    <col min="12" max="12" width="22.6666666666667" customWidth="1"/>
-    <col min="13" max="13" width="11.6666666666667"/>
+    <col min="1" max="1" width="18.859375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.3359375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.3359375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.3359375" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" style="3" customWidth="1"/>
+    <col min="6" max="7" width="13.6640625" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="14.3359375"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.4296875"/>
+    <col min="12" max="12" width="22.6640625" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:10">
+    <row r="1" ht="18.35" spans="1:10">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1916,310 +1925,310 @@
       <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="36" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="49"/>
-    </row>
-    <row r="2" ht="15" spans="1:8">
-      <c r="A2" s="12" t="s">
+      <c r="J1" s="51"/>
+    </row>
+    <row r="2" ht="16.8" spans="1:8">
+      <c r="A2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="15">
+      <c r="C2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="12">
         <v>66835000</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="12">
         <v>39738000</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="17">
+      <c r="H2" s="40">
         <v>34233500</v>
       </c>
     </row>
-    <row r="3" ht="15" spans="1:8">
-      <c r="A3" s="18"/>
-      <c r="B3" s="19" t="s">
+    <row r="3" ht="16.8" spans="1:8">
+      <c r="A3" s="13"/>
+      <c r="B3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="21">
+      <c r="C3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="16">
         <v>45478060</v>
       </c>
-      <c r="E3" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="21">
+      <c r="E3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="16">
         <v>39027410</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="41">
         <v>45303890</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="1:8">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19" t="s">
+    <row r="4" ht="16.8" spans="1:8">
+      <c r="A4" s="13"/>
+      <c r="B4" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="21">
+      <c r="C4" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="16">
         <v>29900100</v>
       </c>
-      <c r="E4" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="21">
+      <c r="E4" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="16">
         <v>20617200</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="41">
         <v>20728100</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="1:8">
-      <c r="A5" s="18"/>
-      <c r="B5" s="19" t="s">
+    <row r="5" ht="16.8" spans="1:8">
+      <c r="A5" s="13"/>
+      <c r="B5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="21">
+      <c r="C5" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="16">
         <v>4400000</v>
       </c>
-      <c r="E5" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="21">
+      <c r="E5" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="16">
         <v>5560000</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="41">
         <v>320000</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="1:8">
-      <c r="A6" s="18"/>
-      <c r="B6" s="19" t="s">
+    <row r="6" ht="16.8" spans="1:8">
+      <c r="A6" s="13"/>
+      <c r="B6" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="21">
+      <c r="C6" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="16">
         <v>5610900</v>
       </c>
-      <c r="E6" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="21">
+      <c r="E6" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="16">
         <v>3578050</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="41">
+        <v>5069850</v>
+      </c>
+    </row>
+    <row r="7" ht="16.8" spans="1:8">
+      <c r="A7" s="13"/>
+      <c r="B7" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="16">
+        <v>3663300</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="16">
+        <v>1983600</v>
+      </c>
+      <c r="G7" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="22">
-        <v>5069850</v>
-      </c>
-    </row>
-    <row r="7" ht="15" spans="1:8">
-      <c r="A7" s="18"/>
-      <c r="B7" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="21">
-        <v>3663300</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="21">
-        <v>1983600</v>
-      </c>
-      <c r="G7" s="23" t="s">
+      <c r="H7" s="41">
+        <v>13417600</v>
+      </c>
+    </row>
+    <row r="8" ht="16.8" spans="1:8">
+      <c r="A8" s="13"/>
+      <c r="B8" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="22">
-        <v>13417600</v>
-      </c>
-    </row>
-    <row r="8" ht="15" spans="1:8">
-      <c r="A8" s="18"/>
-      <c r="B8" s="19" t="s">
+      <c r="C8" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="16">
+        <v>8775000</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="16">
+        <v>7800000</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="41">
+        <v>3900000</v>
+      </c>
+    </row>
+    <row r="9" ht="16.8" spans="1:8">
+      <c r="A9" s="13"/>
+      <c r="B9" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="21">
-        <v>8775000</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="21">
-        <v>7800000</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="22">
-        <v>3900000</v>
-      </c>
-    </row>
-    <row r="9" ht="15" spans="1:8">
-      <c r="A9" s="18"/>
-      <c r="B9" s="19" t="s">
+      <c r="C9" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="D9" s="16"/>
+      <c r="E9" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="16"/>
+      <c r="G9" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="41"/>
+    </row>
+    <row r="10" ht="16.8" spans="1:8">
+      <c r="A10" s="13"/>
+      <c r="B10" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="21"/>
-      <c r="G9" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="22"/>
-    </row>
-    <row r="10" ht="15" spans="1:8">
-      <c r="A10" s="18"/>
-      <c r="B10" s="19" t="s">
+      <c r="C10" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="16"/>
+      <c r="E10" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="16"/>
+      <c r="G10" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="41"/>
+    </row>
+    <row r="11" ht="16.8" spans="1:12">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="22"/>
-    </row>
-    <row r="11" ht="15" spans="1:12">
-      <c r="A11" s="18"/>
-      <c r="B11" s="19" t="s">
+      <c r="C11" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="16"/>
+      <c r="E11" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="16">
+        <v>326000</v>
+      </c>
+      <c r="G11" s="16"/>
+      <c r="H11" s="41">
+        <v>152000</v>
+      </c>
+      <c r="L11" s="51"/>
+    </row>
+    <row r="12" ht="16.8" spans="1:8">
+      <c r="A12" s="13"/>
+      <c r="B12" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="21">
-        <v>326000</v>
-      </c>
-      <c r="G11" s="21"/>
-      <c r="H11" s="22">
-        <v>152000</v>
-      </c>
-      <c r="L11" s="49"/>
-    </row>
-    <row r="12" ht="15" spans="1:8">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19" t="s">
+      <c r="C12" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="16"/>
+      <c r="E12" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="16">
+        <v>924000</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="41">
+        <v>594000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="13"/>
+      <c r="B13" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="21">
-        <v>924000</v>
-      </c>
-      <c r="G12" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="22">
-        <v>594000</v>
-      </c>
-    </row>
-    <row r="13" ht="15" spans="1:8">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19" t="s">
+      <c r="C13" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="16"/>
+      <c r="E13" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="21">
+      <c r="F13" s="16">
         <v>1525000</v>
       </c>
-      <c r="G13" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13" s="22">
+      <c r="G13" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="41">
         <v>995000</v>
       </c>
     </row>
-    <row r="14" ht="15" spans="1:12">
-      <c r="A14" s="18"/>
-      <c r="B14" s="19" t="s">
+    <row r="14" ht="16.8" spans="1:12">
+      <c r="A14" s="13"/>
+      <c r="B14" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="21">
+      <c r="C14" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="16">
         <v>2320000</v>
       </c>
-      <c r="G14" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="22">
+      <c r="G14" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="41">
         <v>2996000</v>
       </c>
       <c r="K14" t="s">
@@ -2229,684 +2238,693 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="25"/>
-      <c r="B15" s="26" t="s">
+    <row r="15" ht="17.55" spans="1:12">
+      <c r="A15" s="18"/>
+      <c r="B15" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="21">
         <v>10000000</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="21">
         <v>10000000</v>
       </c>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29">
+      <c r="G15" s="21"/>
+      <c r="H15" s="43">
         <v>10000000</v>
       </c>
       <c r="J15" t="s">
         <v>31</v>
       </c>
-      <c r="K15" s="22">
+      <c r="K15" s="41">
         <v>65000</v>
       </c>
-      <c r="L15" s="22">
+      <c r="L15" s="41">
         <v>110000</v>
       </c>
     </row>
-    <row r="16" ht="15" spans="1:12">
-      <c r="A16" s="30" t="s">
+    <row r="16" ht="16.8" spans="1:12">
+      <c r="A16" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="C16" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="25">
         <v>20669000</v>
       </c>
-      <c r="E16" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="33">
+      <c r="E16" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="25">
         <v>13909500</v>
       </c>
-      <c r="G16" s="33" t="s">
+      <c r="G16" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="44">
         <v>12478500</v>
       </c>
       <c r="J16" t="s">
         <v>34</v>
       </c>
-      <c r="K16" s="22">
+      <c r="K16" s="41">
         <v>85000</v>
       </c>
-      <c r="L16" s="22">
+      <c r="L16" s="41">
         <v>115000</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="30"/>
-      <c r="B17" s="19" t="s">
+    <row r="17" ht="16.8" spans="1:8">
+      <c r="A17" s="22"/>
+      <c r="B17" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="21">
+      <c r="C17" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="16">
         <v>3230000</v>
       </c>
-      <c r="E17" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="21">
+      <c r="E17" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="16">
         <v>2415000</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="G17" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="41">
         <v>1800000</v>
       </c>
     </row>
-    <row r="18" ht="15" spans="1:8">
-      <c r="A18" s="30"/>
-      <c r="B18" s="19" t="s">
+    <row r="18" ht="16.8" spans="1:8">
+      <c r="A18" s="22"/>
+      <c r="B18" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="21">
+      <c r="C18" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="16">
         <v>10775000</v>
       </c>
-      <c r="E18" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="21">
+      <c r="E18" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="16">
         <v>10000000</v>
       </c>
-      <c r="G18" s="21" t="s">
+      <c r="G18" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H18" s="22">
+      <c r="H18" s="41">
         <v>7025000</v>
       </c>
     </row>
-    <row r="19" ht="15" spans="1:11">
-      <c r="A19" s="30"/>
-      <c r="B19" s="19" t="s">
+    <row r="19" spans="1:11">
+      <c r="A19" s="22"/>
+      <c r="B19" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="21">
+      <c r="C19" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="16">
         <v>10023000</v>
       </c>
-      <c r="E19" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="21">
+      <c r="E19" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="16">
         <v>6637500</v>
       </c>
-      <c r="G19" s="21" t="s">
+      <c r="G19" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="41">
         <v>12023500</v>
       </c>
-      <c r="J19" s="49"/>
-      <c r="K19" s="49"/>
-    </row>
-    <row r="20" ht="15" spans="1:8">
-      <c r="A20" s="30"/>
-      <c r="B20" s="19" t="s">
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+    </row>
+    <row r="20" ht="16.8" spans="1:8">
+      <c r="A20" s="22"/>
+      <c r="B20" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="21"/>
-      <c r="E20" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="21"/>
-      <c r="G20" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="22"/>
-    </row>
-    <row r="21" ht="15" spans="1:8">
-      <c r="A21" s="30"/>
-      <c r="B21" s="19" t="s">
+      <c r="C20" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="16"/>
+      <c r="E20" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="16"/>
+      <c r="G20" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="41"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="22"/>
+      <c r="B21" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="21">
+      <c r="C21" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="16">
         <v>3663000</v>
       </c>
-      <c r="E21" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="21">
+      <c r="E21" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="16">
         <v>1998000</v>
       </c>
-      <c r="G21" s="21" t="s">
+      <c r="G21" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="41">
         <v>1665000</v>
       </c>
     </row>
-    <row r="22" ht="15" spans="1:8">
-      <c r="A22" s="30"/>
-      <c r="B22" s="19" t="s">
+    <row r="22" spans="1:8">
+      <c r="A22" s="22"/>
+      <c r="B22" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="21">
+      <c r="C22" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="16">
         <v>2410000</v>
       </c>
-      <c r="E22" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21" t="s">
+      <c r="E22" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H22" s="22">
+      <c r="H22" s="41">
         <v>2110000</v>
       </c>
     </row>
-    <row r="23" ht="15" spans="1:8">
-      <c r="A23" s="30"/>
-      <c r="B23" s="19" t="s">
+    <row r="23" spans="1:8">
+      <c r="A23" s="22"/>
+      <c r="B23" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="21">
+      <c r="C23" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="16">
         <v>2447502</v>
       </c>
-      <c r="E23" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="21">
+      <c r="E23" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="16">
         <v>1312502</v>
       </c>
-      <c r="G23" s="21" t="s">
+      <c r="G23" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H23" s="22">
+      <c r="H23" s="41">
         <v>1750003</v>
       </c>
     </row>
-    <row r="24" ht="15" spans="1:8">
-      <c r="A24" s="30"/>
-      <c r="B24" s="19" t="s">
+    <row r="24" ht="16.8" spans="1:8">
+      <c r="A24" s="22"/>
+      <c r="B24" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="21"/>
-      <c r="E24" s="16" t="s">
+      <c r="C24" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="16"/>
+      <c r="E24" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="16">
         <v>2280000</v>
       </c>
-      <c r="G24" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="22"/>
-    </row>
-    <row r="25" ht="15" spans="1:8">
-      <c r="A25" s="30"/>
-      <c r="B25" s="19" t="s">
+      <c r="G24" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="41"/>
+    </row>
+    <row r="25" ht="16.8" spans="1:8">
+      <c r="A25" s="22"/>
+      <c r="B25" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="21">
+      <c r="C25" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="16">
         <v>4760036</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E25" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="16">
+        <v>4760036</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="41">
+        <v>1190009</v>
+      </c>
+    </row>
+    <row r="26" ht="16.8" spans="1:8">
+      <c r="A26" s="22"/>
+      <c r="B26" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="16">
+        <v>5600000</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="16">
+        <v>5600000</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="41">
+        <v>5600000</v>
+      </c>
+    </row>
+    <row r="27" ht="16.8" spans="1:8">
+      <c r="A27" s="22"/>
+      <c r="B27" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="16">
+        <v>1225000</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="16">
+        <v>915750</v>
+      </c>
+      <c r="G27" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="21">
-        <v>4760036</v>
-      </c>
-      <c r="G25" s="21" t="s">
+      <c r="H27" s="41">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="28" ht="16.8" spans="1:8">
+      <c r="A28" s="22"/>
+      <c r="B28" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="16"/>
+      <c r="E28" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" s="41"/>
+    </row>
+    <row r="29" ht="16.8" spans="1:8">
+      <c r="A29" s="22"/>
+      <c r="B29" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="16">
+        <v>3948000</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" s="41"/>
+    </row>
+    <row r="30" ht="16.8" spans="1:8">
+      <c r="A30" s="22"/>
+      <c r="B30" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="16">
+        <v>250000</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" s="16"/>
+      <c r="G30" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="H30" s="41"/>
+    </row>
+    <row r="31" ht="16.8" spans="1:8">
+      <c r="A31" s="22"/>
+      <c r="B31" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="16"/>
+      <c r="E31" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" s="16"/>
+      <c r="G31" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" s="41"/>
+    </row>
+    <row r="32" ht="17.55" spans="1:8">
+      <c r="A32" s="27"/>
+      <c r="B32" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="30"/>
+      <c r="E32" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="30">
+        <v>915750</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" s="45"/>
+    </row>
+    <row r="33" ht="17.55" spans="1:8">
+      <c r="A33" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="12">
+        <v>4897000</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="12">
+        <v>8368100</v>
+      </c>
+      <c r="G33" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H25" s="22">
-        <v>1190009</v>
-      </c>
-    </row>
-    <row r="26" ht="15" spans="1:8">
-      <c r="A26" s="30"/>
-      <c r="B26" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="21">
-        <v>5600000</v>
-      </c>
-      <c r="E26" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="21">
-        <v>5600000</v>
-      </c>
-      <c r="G26" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="H26" s="22">
-        <v>5600000</v>
-      </c>
-    </row>
-    <row r="27" ht="15" spans="1:8">
-      <c r="A27" s="30"/>
-      <c r="B27" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="21">
-        <v>1225000</v>
-      </c>
-      <c r="E27" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="21">
-        <v>915750</v>
-      </c>
-      <c r="G27" s="21" t="s">
+      <c r="H33" s="40">
+        <v>4047600</v>
+      </c>
+    </row>
+    <row r="34" ht="16.8" spans="1:8">
+      <c r="A34" s="13"/>
+      <c r="B34" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="16">
+        <v>4375000</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" s="16">
+        <v>4715000</v>
+      </c>
+      <c r="G34" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H27" s="22">
+      <c r="H34" s="41">
+        <v>2585000</v>
+      </c>
+    </row>
+    <row r="35" ht="16.8" spans="1:8">
+      <c r="A35" s="13"/>
+      <c r="B35" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="16">
+        <v>1007480.64</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="16">
+        <v>638483</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H35" s="16">
+        <v>269482</v>
+      </c>
+    </row>
+    <row r="36" ht="17.55" spans="1:8">
+      <c r="A36" s="18"/>
+      <c r="B36" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="16">
+        <v>1168000</v>
+      </c>
+      <c r="E36" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="47">
+        <v>893000</v>
+      </c>
+      <c r="G36" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="H36" s="16">
+        <v>847000</v>
+      </c>
+    </row>
+    <row r="37" ht="16.8" spans="1:8">
+      <c r="A37" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="33"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" s="16">
+        <v>1020000</v>
+      </c>
+      <c r="G37" s="34"/>
+      <c r="H37" s="48"/>
+    </row>
+    <row r="38" ht="16.8" spans="1:8">
+      <c r="A38" s="32"/>
+      <c r="B38" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="33"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="16">
+        <v>1350000</v>
+      </c>
+      <c r="G38" s="34"/>
+      <c r="H38" s="48"/>
+    </row>
+    <row r="39" ht="16.8" spans="1:8">
+      <c r="A39" s="32"/>
+      <c r="B39" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="33"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" s="16">
         <v>600000</v>
       </c>
-    </row>
-    <row r="28" ht="15" spans="1:8">
-      <c r="A28" s="30"/>
-      <c r="B28" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="21"/>
-      <c r="E28" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="F28" s="21"/>
-      <c r="G28" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="22"/>
-    </row>
-    <row r="29" ht="15" spans="1:8">
-      <c r="A29" s="30"/>
-      <c r="B29" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="21">
-        <v>3948000</v>
-      </c>
-      <c r="E29" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="F29" s="21"/>
-      <c r="G29" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="22"/>
-    </row>
-    <row r="30" ht="15" spans="1:8">
-      <c r="A30" s="30"/>
-      <c r="B30" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="21">
-        <v>250000</v>
-      </c>
-      <c r="E30" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="F30" s="21"/>
-      <c r="G30" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="H30" s="22"/>
-    </row>
-    <row r="31" ht="15" spans="1:8">
-      <c r="A31" s="30"/>
-      <c r="B31" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="21"/>
-      <c r="E31" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="F31" s="21"/>
-      <c r="G31" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="22"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="36"/>
-      <c r="B32" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="39"/>
-      <c r="E32" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="39">
-        <v>915750</v>
-      </c>
-      <c r="G32" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32" s="40"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="15">
-        <v>4897000</v>
-      </c>
-      <c r="E33" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="15">
-        <v>8368100</v>
-      </c>
-      <c r="G33" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="H33" s="17">
-        <v>4047600</v>
-      </c>
-    </row>
-    <row r="34" ht="15" spans="1:8">
-      <c r="A34" s="18"/>
-      <c r="B34" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="21">
-        <v>4375000</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" s="21">
-        <v>4715000</v>
-      </c>
-      <c r="G34" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="H34" s="22">
-        <v>2585000</v>
-      </c>
-    </row>
-    <row r="35" ht="15" spans="1:8">
-      <c r="A35" s="18"/>
-      <c r="B35" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="21">
-        <v>1007480.64</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="21">
-        <v>638483</v>
-      </c>
-      <c r="G35" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="H35" s="21">
-        <v>269482</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="25"/>
-      <c r="B36" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="21">
-        <v>1168000</v>
-      </c>
-      <c r="E36" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="43">
-        <v>893000</v>
-      </c>
-      <c r="G36" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="H36" s="21">
-        <v>847000</v>
-      </c>
-    </row>
-    <row r="37" ht="15" spans="1:8">
-      <c r="A37" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="C37" s="45"/>
-      <c r="D37" s="46"/>
-      <c r="E37" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="21">
-        <v>1020000</v>
-      </c>
-      <c r="G37" s="46"/>
-      <c r="H37" s="47"/>
-    </row>
-    <row r="38" ht="15" spans="1:8">
-      <c r="A38" s="44"/>
-      <c r="B38" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C38" s="45"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="21">
-        <v>1350000</v>
-      </c>
-      <c r="G38" s="46"/>
-      <c r="H38" s="47"/>
-    </row>
-    <row r="39" ht="15" spans="1:8">
-      <c r="A39" s="44"/>
-      <c r="B39" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C39" s="45"/>
-      <c r="D39" s="46"/>
-      <c r="E39" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="21">
-        <v>600000</v>
-      </c>
-      <c r="G39" s="46"/>
-      <c r="H39" s="47"/>
-    </row>
-    <row r="40" ht="15" spans="1:8">
-      <c r="A40" s="44"/>
-      <c r="B40" s="19" t="s">
+      <c r="G39" s="34"/>
+      <c r="H39" s="48"/>
+    </row>
+    <row r="40" ht="16.8" spans="1:8">
+      <c r="A40" s="32"/>
+      <c r="B40" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="45"/>
-      <c r="D40" s="46"/>
-      <c r="E40" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="21">
+      <c r="C40" s="33"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" s="16">
         <v>318134</v>
       </c>
-      <c r="G40" s="46"/>
-      <c r="H40" s="47"/>
-    </row>
-    <row r="41" ht="15" spans="1:8">
-      <c r="A41" s="44"/>
-      <c r="B41" s="19" t="s">
+      <c r="G40" s="34"/>
+      <c r="H40" s="48"/>
+    </row>
+    <row r="41" ht="16.8" spans="1:8">
+      <c r="A41" s="32"/>
+      <c r="B41" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C41" s="45"/>
-      <c r="D41" s="46"/>
-      <c r="E41" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="21">
+      <c r="C41" s="33"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="16">
         <v>248700</v>
       </c>
-      <c r="G41" s="46"/>
-      <c r="H41" s="47"/>
-    </row>
-    <row r="42" ht="15" spans="1:8">
-      <c r="A42" s="44"/>
-      <c r="B42" s="19" t="s">
+      <c r="G41" s="34"/>
+      <c r="H41" s="48"/>
+    </row>
+    <row r="42" ht="16.8" spans="1:8">
+      <c r="A42" s="32"/>
+      <c r="B42" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C42" s="45"/>
-      <c r="D42" s="46"/>
-      <c r="E42" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="21">
+      <c r="C42" s="33"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="16">
         <v>1029180</v>
       </c>
-      <c r="G42" s="46"/>
-      <c r="H42" s="47"/>
-    </row>
-    <row r="43" ht="15" spans="1:8">
-      <c r="A43" s="44"/>
-      <c r="B43" s="19" t="s">
+      <c r="G42" s="34"/>
+      <c r="H42" s="48"/>
+    </row>
+    <row r="43" ht="16.8" spans="1:8">
+      <c r="A43" s="32"/>
+      <c r="B43" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C43" s="45"/>
-      <c r="D43" s="46"/>
-      <c r="E43" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="21">
+      <c r="C43" s="33"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="16">
         <v>270000</v>
       </c>
-      <c r="G43" s="46"/>
-      <c r="H43" s="47"/>
-    </row>
-    <row r="44" ht="15" spans="1:8">
-      <c r="A44" s="44"/>
-      <c r="B44" s="19" t="s">
+      <c r="G43" s="34"/>
+      <c r="H43" s="48"/>
+    </row>
+    <row r="44" ht="16.8" spans="1:8">
+      <c r="A44" s="32"/>
+      <c r="B44" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="45"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="21">
+      <c r="C44" s="33"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="16">
         <v>1000000</v>
       </c>
-      <c r="G44" s="46"/>
-      <c r="H44" s="47"/>
-    </row>
-    <row r="45" ht="15" spans="1:8">
-      <c r="A45" s="44"/>
-      <c r="B45" s="19" t="s">
+      <c r="G44" s="34"/>
+      <c r="H44" s="48"/>
+    </row>
+    <row r="45" ht="16.8" spans="1:8">
+      <c r="A45" s="32"/>
+      <c r="B45" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="45"/>
-      <c r="D45" s="46"/>
-      <c r="E45" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="21">
+      <c r="C45" s="33"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="16">
         <v>3000000</v>
       </c>
-      <c r="G45" s="46"/>
-      <c r="H45" s="47"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="48"/>
-      <c r="B46" s="19" t="s">
+      <c r="G45" s="34"/>
+      <c r="H45" s="48"/>
+    </row>
+    <row r="46" ht="16.8" spans="1:8">
+      <c r="A46" s="35"/>
+      <c r="B46" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C46" s="45"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="21">
+      <c r="C46" s="33"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" s="16">
         <v>1800000</v>
       </c>
-      <c r="G46" s="46"/>
-      <c r="H46" s="47"/>
-    </row>
-    <row r="47" spans="6:6">
+      <c r="G46" s="34"/>
+      <c r="H46" s="48"/>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="B47" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="F47" s="4"/>
+      <c r="G47" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="50">
+        <v>2450000</v>
+      </c>
     </row>
     <row r="48" spans="6:6">
       <c r="F48" s="4"/>
@@ -2922,16 +2940,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F52" s="4"/>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F53" s="4"/>
     </row>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="71">
   <si>
     <t>DIVISION</t>
   </si>
@@ -2109,7 +2109,7 @@
         <v>3900000</v>
       </c>
     </row>
-    <row r="9" ht="16.8" spans="1:8">
+    <row r="9" spans="1:8">
       <c r="A9" s="13"/>
       <c r="B9" s="14" t="s">
         <v>18</v>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="H9" s="41"/>
     </row>
-    <row r="10" ht="16.8" spans="1:8">
+    <row r="10" spans="1:8">
       <c r="A10" s="13"/>
       <c r="B10" s="14" t="s">
         <v>20</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="H10" s="41"/>
     </row>
-    <row r="11" ht="16.8" spans="1:12">
+    <row r="11" spans="1:12">
       <c r="A11" s="13"/>
       <c r="B11" s="14" t="s">
         <v>21</v>
@@ -2160,13 +2160,13 @@
       <c r="F11" s="16">
         <v>326000</v>
       </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="41">
-        <v>152000</v>
-      </c>
+      <c r="G11" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="41"/>
       <c r="L11" s="51"/>
     </row>
-    <row r="12" ht="16.8" spans="1:8">
+    <row r="12" spans="1:8">
       <c r="A12" s="13"/>
       <c r="B12" s="14" t="s">
         <v>22</v>
@@ -2188,7 +2188,7 @@
         <v>594000</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" ht="16.8" spans="1:8">
       <c r="A13" s="13"/>
       <c r="B13" s="14" t="s">
         <v>23</v>
@@ -2352,7 +2352,7 @@
         <v>7025000</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" ht="16.8" spans="1:11">
       <c r="A19" s="22"/>
       <c r="B19" s="14" t="s">
         <v>37</v>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="H20" s="41"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" ht="16.8" spans="1:8">
       <c r="A21" s="22"/>
       <c r="B21" s="14" t="s">
         <v>39</v>
@@ -2442,7 +2442,7 @@
         <v>2110000</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:10">
       <c r="A23" s="22"/>
       <c r="B23" s="14" t="s">
         <v>41</v>
@@ -2465,8 +2465,9 @@
       <c r="H23" s="41">
         <v>1750003</v>
       </c>
-    </row>
-    <row r="24" ht="16.8" spans="1:8">
+      <c r="J23" s="51"/>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="22"/>
       <c r="B24" s="14" t="s">
         <v>42</v>
@@ -2486,7 +2487,7 @@
       </c>
       <c r="H24" s="41"/>
     </row>
-    <row r="25" ht="16.8" spans="1:8">
+    <row r="25" spans="1:10">
       <c r="A25" s="22"/>
       <c r="B25" s="14" t="s">
         <v>43</v>
@@ -2509,8 +2510,9 @@
       <c r="H25" s="41">
         <v>1190009</v>
       </c>
-    </row>
-    <row r="26" ht="16.8" spans="1:8">
+      <c r="J25" s="51"/>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="22"/>
       <c r="B26" s="14" t="s">
         <v>44</v>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17000"/>
+    <workbookView windowHeight="17020"/>
   </bookViews>
   <sheets>
     <sheet name="SUPPLIER PAYMENT STATUS" sheetId="1" r:id="rId1"/>
@@ -664,7 +664,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -847,6 +847,19 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1081,7 +1094,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="22" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="23" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1093,34 +1106,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1205,7 +1218,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1299,7 +1312,10 @@
     <xf numFmtId="181" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="1" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1311,50 +1327,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="180" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="181" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="181" fontId="0" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="0" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1925,19 +1944,19 @@
       <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="39" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="G1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="51"/>
+      <c r="J1" s="53"/>
     </row>
     <row r="2" ht="16.8" spans="1:8">
       <c r="A2" s="9" t="s">
@@ -1958,10 +1977,10 @@
       <c r="F2" s="12">
         <v>39738000</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="40">
+      <c r="H2" s="43">
         <v>34233500</v>
       </c>
     </row>
@@ -1985,7 +2004,7 @@
       <c r="G3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="41">
+      <c r="H3" s="44">
         <v>45303890</v>
       </c>
     </row>
@@ -2009,11 +2028,11 @@
       <c r="G4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="41">
+      <c r="H4" s="44">
         <v>20728100</v>
       </c>
     </row>
-    <row r="5" ht="16.8" spans="1:8">
+    <row r="5" spans="1:8">
       <c r="A5" s="13"/>
       <c r="B5" s="14" t="s">
         <v>14</v>
@@ -2033,11 +2052,11 @@
       <c r="G5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="44">
         <v>320000</v>
       </c>
     </row>
-    <row r="6" ht="16.8" spans="1:8">
+    <row r="6" spans="1:8">
       <c r="A6" s="13"/>
       <c r="B6" s="14" t="s">
         <v>15</v>
@@ -2057,11 +2076,11 @@
       <c r="G6" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="41">
+      <c r="H6" s="44">
         <v>5069850</v>
       </c>
     </row>
-    <row r="7" ht="16.8" spans="1:8">
+    <row r="7" spans="1:8">
       <c r="A7" s="13"/>
       <c r="B7" s="14" t="s">
         <v>16</v>
@@ -2078,14 +2097,14 @@
       <c r="F7" s="16">
         <v>1983600</v>
       </c>
-      <c r="G7" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="41">
+      <c r="G7" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="44">
         <v>13417600</v>
       </c>
     </row>
-    <row r="8" ht="16.8" spans="1:8">
+    <row r="8" spans="1:8">
       <c r="A8" s="13"/>
       <c r="B8" s="14" t="s">
         <v>17</v>
@@ -2105,11 +2124,11 @@
       <c r="G8" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="44">
         <v>3900000</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" ht="16.8" spans="1:8">
       <c r="A9" s="13"/>
       <c r="B9" s="14" t="s">
         <v>18</v>
@@ -2125,9 +2144,9 @@
       <c r="G9" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="41"/>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="H9" s="44"/>
+    </row>
+    <row r="10" ht="16.8" spans="1:8">
       <c r="A10" s="13"/>
       <c r="B10" s="14" t="s">
         <v>20</v>
@@ -2143,7 +2162,7 @@
       <c r="G10" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="41"/>
+      <c r="H10" s="44"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="13"/>
@@ -2163,8 +2182,8 @@
       <c r="G11" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="41"/>
-      <c r="L11" s="51"/>
+      <c r="H11" s="44"/>
+      <c r="L11" s="53"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="13"/>
@@ -2184,11 +2203,11 @@
       <c r="G12" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="44">
         <v>594000</v>
       </c>
     </row>
-    <row r="13" ht="16.8" spans="1:8">
+    <row r="13" spans="1:8">
       <c r="A13" s="13"/>
       <c r="B13" s="14" t="s">
         <v>23</v>
@@ -2197,20 +2216,20 @@
         <v>8</v>
       </c>
       <c r="D13" s="16"/>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="45" t="s">
         <v>24</v>
       </c>
       <c r="F13" s="16">
         <v>1525000</v>
       </c>
-      <c r="G13" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="41">
+      <c r="G13" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="44">
         <v>995000</v>
       </c>
     </row>
-    <row r="14" ht="16.8" spans="1:12">
+    <row r="14" spans="1:12">
       <c r="A14" s="13"/>
       <c r="B14" s="14" t="s">
         <v>25</v>
@@ -2228,7 +2247,7 @@
       <c r="G14" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="44">
         <v>2996000</v>
       </c>
       <c r="K14" t="s">
@@ -2256,16 +2275,16 @@
         <v>10000000</v>
       </c>
       <c r="G15" s="21"/>
-      <c r="H15" s="43">
+      <c r="H15" s="46">
         <v>10000000</v>
       </c>
       <c r="J15" t="s">
         <v>31</v>
       </c>
-      <c r="K15" s="41">
+      <c r="K15" s="44">
         <v>65000</v>
       </c>
-      <c r="L15" s="41">
+      <c r="L15" s="44">
         <v>110000</v>
       </c>
     </row>
@@ -2291,16 +2310,16 @@
       <c r="G16" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="44">
+      <c r="H16" s="47">
         <v>12478500</v>
       </c>
       <c r="J16" t="s">
         <v>34</v>
       </c>
-      <c r="K16" s="41">
+      <c r="K16" s="44">
         <v>85000</v>
       </c>
-      <c r="L16" s="41">
+      <c r="L16" s="44">
         <v>115000</v>
       </c>
     </row>
@@ -2324,7 +2343,7 @@
       <c r="G17" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="44">
         <v>1800000</v>
       </c>
     </row>
@@ -2348,7 +2367,7 @@
       <c r="G18" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H18" s="41">
+      <c r="H18" s="44">
         <v>7025000</v>
       </c>
     </row>
@@ -2372,11 +2391,11 @@
       <c r="G19" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H19" s="41">
+      <c r="H19" s="44">
         <v>12023500</v>
       </c>
-      <c r="J19" s="51"/>
-      <c r="K19" s="51"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
     </row>
     <row r="20" ht="16.8" spans="1:8">
       <c r="A20" s="22"/>
@@ -2394,7 +2413,7 @@
       <c r="G20" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="H20" s="41"/>
+      <c r="H20" s="44"/>
     </row>
     <row r="21" ht="16.8" spans="1:8">
       <c r="A21" s="22"/>
@@ -2416,11 +2435,11 @@
       <c r="G21" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H21" s="41">
+      <c r="H21" s="44">
         <v>1665000</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" ht="16.8" spans="1:8">
       <c r="A22" s="22"/>
       <c r="B22" s="14" t="s">
         <v>40</v>
@@ -2438,11 +2457,11 @@
       <c r="G22" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H22" s="41">
+      <c r="H22" s="44">
         <v>2110000</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" ht="16.8" spans="1:10">
       <c r="A23" s="22"/>
       <c r="B23" s="14" t="s">
         <v>41</v>
@@ -2462,10 +2481,10 @@
       <c r="G23" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H23" s="41">
+      <c r="H23" s="44">
         <v>1750003</v>
       </c>
-      <c r="J23" s="51"/>
+      <c r="J23" s="53"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="22"/>
@@ -2476,7 +2495,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="16"/>
-      <c r="E24" s="42" t="s">
+      <c r="E24" s="45" t="s">
         <v>12</v>
       </c>
       <c r="F24" s="16">
@@ -2485,7 +2504,7 @@
       <c r="G24" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="H24" s="41"/>
+      <c r="H24" s="44"/>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="22"/>
@@ -2498,19 +2517,19 @@
       <c r="D25" s="16">
         <v>4760036</v>
       </c>
-      <c r="E25" s="42" t="s">
-        <v>24</v>
+      <c r="E25" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="F25" s="16">
         <v>4760036</v>
       </c>
-      <c r="G25" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="H25" s="41">
+      <c r="G25" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="44">
         <v>1190009</v>
       </c>
-      <c r="J25" s="51"/>
+      <c r="J25" s="53"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="22"/>
@@ -2532,11 +2551,11 @@
       <c r="G26" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="H26" s="41">
+      <c r="H26" s="44">
         <v>5600000</v>
       </c>
     </row>
-    <row r="27" ht="16.8" spans="1:8">
+    <row r="27" spans="1:8">
       <c r="A27" s="22"/>
       <c r="B27" s="14" t="s">
         <v>45</v>
@@ -2556,7 +2575,7 @@
       <c r="G27" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H27" s="41">
+      <c r="H27" s="44">
         <v>600000</v>
       </c>
     </row>
@@ -2576,7 +2595,7 @@
       <c r="G28" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="H28" s="41"/>
+      <c r="H28" s="44"/>
     </row>
     <row r="29" ht="16.8" spans="1:8">
       <c r="A29" s="22"/>
@@ -2596,7 +2615,7 @@
       <c r="G29" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="H29" s="41"/>
+      <c r="H29" s="44"/>
     </row>
     <row r="30" ht="16.8" spans="1:8">
       <c r="A30" s="22"/>
@@ -2616,7 +2635,7 @@
       <c r="G30" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="H30" s="41"/>
+      <c r="H30" s="44"/>
     </row>
     <row r="31" ht="16.8" spans="1:8">
       <c r="A31" s="22"/>
@@ -2634,7 +2653,7 @@
       <c r="G31" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="H31" s="41"/>
+      <c r="H31" s="44"/>
     </row>
     <row r="32" ht="17.55" spans="1:8">
       <c r="A32" s="27"/>
@@ -2654,7 +2673,7 @@
       <c r="G32" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="H32" s="45"/>
+      <c r="H32" s="48"/>
     </row>
     <row r="33" ht="17.55" spans="1:8">
       <c r="A33" s="9" t="s">
@@ -2678,7 +2697,7 @@
       <c r="G33" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H33" s="40">
+      <c r="H33" s="43">
         <v>4047600</v>
       </c>
     </row>
@@ -2702,11 +2721,11 @@
       <c r="G34" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H34" s="41">
+      <c r="H34" s="44">
         <v>2585000</v>
       </c>
     </row>
-    <row r="35" ht="16.8" spans="1:8">
+    <row r="35" spans="1:8">
       <c r="A35" s="13"/>
       <c r="B35" s="14" t="s">
         <v>55</v>
@@ -2730,9 +2749,9 @@
         <v>269482</v>
       </c>
     </row>
-    <row r="36" ht="17.55" spans="1:8">
-      <c r="A36" s="18"/>
-      <c r="B36" s="31" t="s">
+    <row r="36" spans="1:8">
+      <c r="A36" s="31"/>
+      <c r="B36" s="32" t="s">
         <v>56</v>
       </c>
       <c r="C36" s="15" t="s">
@@ -2741,190 +2760,191 @@
       <c r="D36" s="16">
         <v>1168000</v>
       </c>
-      <c r="E36" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="47">
+      <c r="E36" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="50">
         <v>893000</v>
       </c>
-      <c r="G36" s="46" t="s">
+      <c r="G36" s="49" t="s">
         <v>8</v>
       </c>
       <c r="H36" s="16">
         <v>847000</v>
       </c>
     </row>
-    <row r="37" ht="16.8" spans="1:8">
-      <c r="A37" s="32" t="s">
+    <row r="37" spans="1:8">
+      <c r="A37" s="33" t="s">
         <v>57</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C37" s="33"/>
-      <c r="D37" s="34"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="35"/>
       <c r="E37" s="15" t="s">
         <v>8</v>
       </c>
       <c r="F37" s="16">
         <v>1020000</v>
       </c>
-      <c r="G37" s="34"/>
-      <c r="H37" s="48"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="51"/>
     </row>
     <row r="38" ht="16.8" spans="1:8">
-      <c r="A38" s="32"/>
+      <c r="A38" s="36"/>
       <c r="B38" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C38" s="33"/>
-      <c r="D38" s="34"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="35"/>
       <c r="E38" s="15" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="16">
         <v>1350000</v>
       </c>
-      <c r="G38" s="34"/>
-      <c r="H38" s="48"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="51"/>
     </row>
     <row r="39" ht="16.8" spans="1:8">
-      <c r="A39" s="32"/>
+      <c r="A39" s="36"/>
       <c r="B39" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="33"/>
-      <c r="D39" s="34"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="35"/>
       <c r="E39" s="15" t="s">
         <v>8</v>
       </c>
       <c r="F39" s="16">
         <v>600000</v>
       </c>
-      <c r="G39" s="34"/>
-      <c r="H39" s="48"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="51"/>
     </row>
     <row r="40" ht="16.8" spans="1:8">
-      <c r="A40" s="32"/>
+      <c r="A40" s="36"/>
       <c r="B40" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="33"/>
-      <c r="D40" s="34"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="35"/>
       <c r="E40" s="15" t="s">
         <v>8</v>
       </c>
       <c r="F40" s="16">
         <v>318134</v>
       </c>
-      <c r="G40" s="34"/>
-      <c r="H40" s="48"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="51"/>
     </row>
     <row r="41" ht="16.8" spans="1:8">
-      <c r="A41" s="32"/>
+      <c r="A41" s="36"/>
       <c r="B41" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C41" s="33"/>
-      <c r="D41" s="34"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="35"/>
       <c r="E41" s="15" t="s">
         <v>8</v>
       </c>
       <c r="F41" s="16">
         <v>248700</v>
       </c>
-      <c r="G41" s="34"/>
-      <c r="H41" s="48"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="51"/>
     </row>
     <row r="42" ht="16.8" spans="1:8">
-      <c r="A42" s="32"/>
+      <c r="A42" s="36"/>
       <c r="B42" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C42" s="33"/>
-      <c r="D42" s="34"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="35"/>
       <c r="E42" s="15" t="s">
         <v>8</v>
       </c>
       <c r="F42" s="16">
         <v>1029180</v>
       </c>
-      <c r="G42" s="34"/>
-      <c r="H42" s="48"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="51"/>
     </row>
     <row r="43" ht="16.8" spans="1:8">
-      <c r="A43" s="32"/>
+      <c r="A43" s="36"/>
       <c r="B43" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C43" s="33"/>
-      <c r="D43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="35"/>
       <c r="E43" s="15" t="s">
         <v>8</v>
       </c>
       <c r="F43" s="16">
         <v>270000</v>
       </c>
-      <c r="G43" s="34"/>
-      <c r="H43" s="48"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="51"/>
     </row>
     <row r="44" ht="16.8" spans="1:8">
-      <c r="A44" s="32"/>
+      <c r="A44" s="36"/>
       <c r="B44" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="33"/>
-      <c r="D44" s="34"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="35"/>
       <c r="E44" s="15" t="s">
         <v>8</v>
       </c>
       <c r="F44" s="16">
         <v>1000000</v>
       </c>
-      <c r="G44" s="34"/>
-      <c r="H44" s="48"/>
+      <c r="G44" s="35"/>
+      <c r="H44" s="51"/>
     </row>
     <row r="45" ht="16.8" spans="1:8">
-      <c r="A45" s="32"/>
+      <c r="A45" s="36"/>
       <c r="B45" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="33"/>
-      <c r="D45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="35"/>
       <c r="E45" s="15" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="16">
         <v>3000000</v>
       </c>
-      <c r="G45" s="34"/>
-      <c r="H45" s="48"/>
+      <c r="G45" s="35"/>
+      <c r="H45" s="51"/>
     </row>
     <row r="46" ht="16.8" spans="1:8">
-      <c r="A46" s="35"/>
+      <c r="A46" s="36"/>
       <c r="B46" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C46" s="33"/>
-      <c r="D46" s="34"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="35"/>
       <c r="E46" s="15" t="s">
         <v>8</v>
       </c>
       <c r="F46" s="16">
         <v>1800000</v>
       </c>
-      <c r="G46" s="34"/>
-      <c r="H46" s="48"/>
-    </row>
-    <row r="47" spans="2:8">
-      <c r="B47" s="2" t="s">
+      <c r="G46" s="35"/>
+      <c r="H46" s="51"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="37"/>
+      <c r="B47" s="38" t="s">
         <v>68</v>
       </c>
       <c r="F47" s="4"/>
-      <c r="G47" s="49" t="s">
-        <v>24</v>
-      </c>
-      <c r="H47" s="50">
+      <c r="G47" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="52">
         <v>2450000</v>
       </c>
     </row>
@@ -2960,7 +2980,7 @@
     <mergeCell ref="A2:A15"/>
     <mergeCell ref="A16:A32"/>
     <mergeCell ref="A33:A36"/>
-    <mergeCell ref="A37:A46"/>
+    <mergeCell ref="A37:A47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="68">
   <si>
     <t>DIVISION</t>
   </si>
@@ -65,97 +65,88 @@
     <t>SEDANA JAYA</t>
   </si>
   <si>
+    <t>RAFI SEAFOOD</t>
+  </si>
+  <si>
+    <t>MAMA RADA PRODUCTION</t>
+  </si>
+  <si>
+    <t>KSP</t>
+  </si>
+  <si>
+    <t>SURYA CIPTA NIAGA</t>
+  </si>
+  <si>
+    <t>BAYU AGNI</t>
+  </si>
+  <si>
+    <t>JOY GREEN</t>
+  </si>
+  <si>
+    <t>N/O</t>
+  </si>
+  <si>
+    <t>CELEBRITY BAKERY</t>
+  </si>
+  <si>
+    <t>KROP</t>
+  </si>
+  <si>
+    <t>MAKER</t>
+  </si>
+  <si>
+    <t>BOILER</t>
+  </si>
+  <si>
+    <t>Total account payable</t>
+  </si>
+  <si>
+    <t>DISHY SOAP</t>
+  </si>
+  <si>
+    <t>DAILY BAGUETTE</t>
+  </si>
+  <si>
+    <t>SURBLED</t>
+  </si>
+  <si>
+    <t>PAID 1ST</t>
+  </si>
+  <si>
+    <t>PAID 2ND</t>
+  </si>
+  <si>
+    <t>BAR</t>
+  </si>
+  <si>
+    <t>WARUNG EKA</t>
+  </si>
+  <si>
+    <t>DEWATA COCONUT</t>
+  </si>
+  <si>
+    <t>PNB</t>
+  </si>
+  <si>
+    <t>DSP</t>
+  </si>
+  <si>
+    <t>DSP (ARYA BIMA)</t>
+  </si>
+  <si>
+    <t>SELERA (STIR UP SYRUP)</t>
+  </si>
+  <si>
+    <t>DW BALI</t>
+  </si>
+  <si>
+    <t>DDB</t>
+  </si>
+  <si>
+    <t>NANO DEWATA</t>
+  </si>
+  <si>
     <t>POSTED</t>
-  </si>
-  <si>
-    <t>RAFI SEAFOOD</t>
-  </si>
-  <si>
-    <t>MAMA RADA PRODUCTION</t>
-  </si>
-  <si>
-    <t>KSP</t>
-  </si>
-  <si>
-    <t>SURYA CIPTA NIAGA</t>
-  </si>
-  <si>
-    <t>BAYU AGNI</t>
-  </si>
-  <si>
-    <t>JOY GREEN</t>
-  </si>
-  <si>
-    <t>N/O</t>
-  </si>
-  <si>
-    <t>CELEBRITY BAKERY</t>
-  </si>
-  <si>
-    <t>KROP</t>
-  </si>
-  <si>
-    <t>BOILER</t>
-  </si>
-  <si>
-    <t>DISHY SOAP</t>
-  </si>
-  <si>
-    <t>MAKER</t>
-  </si>
-  <si>
-    <t>DAILY BAGUETTE</t>
-  </si>
-  <si>
-    <t>abdi</t>
-  </si>
-  <si>
-    <t>anugrah</t>
-  </si>
-  <si>
-    <t>SURBLED</t>
-  </si>
-  <si>
-    <t>PAID 1ST</t>
-  </si>
-  <si>
-    <t>PAID 2ND</t>
-  </si>
-  <si>
-    <t>16x25</t>
-  </si>
-  <si>
-    <t>BAR</t>
-  </si>
-  <si>
-    <t>WARUNG EKA</t>
-  </si>
-  <si>
-    <t>20x30</t>
-  </si>
-  <si>
-    <t>DEWATA COCONUT</t>
-  </si>
-  <si>
-    <t>PNB</t>
-  </si>
-  <si>
-    <t>DSP</t>
-  </si>
-  <si>
-    <t>DSP (ARYA BIMA)</t>
-  </si>
-  <si>
-    <t>SELERA (STIR UP SYRUP)</t>
-  </si>
-  <si>
-    <t>DW BALI</t>
-  </si>
-  <si>
-    <t>DDB</t>
-  </si>
-  <si>
-    <t>NANO DEWATA</t>
   </si>
   <si>
     <t>BALI PERMATA JAYA</t>
@@ -1218,7 +1209,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1333,9 +1324,6 @@
     <xf numFmtId="180" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1351,24 +1339,24 @@
     <xf numFmtId="181" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="181" fontId="0" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="181" fontId="0" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="181" fontId="0" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1380,6 +1368,12 @@
     </xf>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1944,19 +1938,19 @@
       <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="38" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="41" t="s">
+      <c r="H1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="53"/>
+      <c r="J1" s="52"/>
     </row>
     <row r="2" ht="16.8" spans="1:8">
       <c r="A2" s="9" t="s">
@@ -1977,10 +1971,10 @@
       <c r="F2" s="12">
         <v>39738000</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="43">
+      <c r="H2" s="42">
         <v>34233500</v>
       </c>
     </row>
@@ -2001,8 +1995,8 @@
       <c r="F3" s="16">
         <v>39027410</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>12</v>
+      <c r="G3" s="43" t="s">
+        <v>8</v>
       </c>
       <c r="H3" s="44">
         <v>45303890</v>
@@ -2011,7 +2005,7 @@
     <row r="4" ht="16.8" spans="1:8">
       <c r="A4" s="13"/>
       <c r="B4" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>8</v>
@@ -2025,17 +2019,17 @@
       <c r="F4" s="16">
         <v>20617200</v>
       </c>
-      <c r="G4" s="16" t="s">
-        <v>12</v>
+      <c r="G4" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="H4" s="44">
-        <v>20728100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>21943450</v>
+      </c>
+    </row>
+    <row r="5" ht="16.8" spans="1:8">
       <c r="A5" s="13"/>
       <c r="B5" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>8</v>
@@ -2049,17 +2043,17 @@
       <c r="F5" s="16">
         <v>5560000</v>
       </c>
-      <c r="G5" s="16" t="s">
-        <v>12</v>
+      <c r="G5" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="H5" s="44">
         <v>320000</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" ht="16.8" spans="1:8">
       <c r="A6" s="13"/>
       <c r="B6" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>8</v>
@@ -2080,10 +2074,10 @@
         <v>5069850</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" ht="16.8" spans="1:8">
       <c r="A7" s="13"/>
       <c r="B7" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>8</v>
@@ -2104,10 +2098,10 @@
         <v>13417600</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" ht="16.8" spans="1:8">
       <c r="A8" s="13"/>
       <c r="B8" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>8</v>
@@ -2121,56 +2115,56 @@
       <c r="F8" s="16">
         <v>7800000</v>
       </c>
-      <c r="G8" s="16" t="s">
-        <v>12</v>
+      <c r="G8" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="H8" s="44">
-        <v>3900000</v>
+        <v>5850000</v>
       </c>
     </row>
     <row r="9" ht="16.8" spans="1:8">
       <c r="A9" s="13"/>
       <c r="B9" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>18</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>19</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H9" s="44"/>
     </row>
     <row r="10" ht="16.8" spans="1:8">
       <c r="A10" s="13"/>
       <c r="B10" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" s="16"/>
       <c r="E10" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H10" s="44"/>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" ht="16.8" spans="1:12">
       <c r="A11" s="13"/>
       <c r="B11" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" s="16"/>
       <c r="E11" s="15" t="s">
@@ -2179,13 +2173,15 @@
       <c r="F11" s="16">
         <v>326000</v>
       </c>
-      <c r="G11" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="44"/>
-      <c r="L11" s="53"/>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="G11" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="44">
+        <v>152000</v>
+      </c>
+      <c r="L11" s="52"/>
+    </row>
+    <row r="12" ht="16.8" spans="1:10">
       <c r="A12" s="13"/>
       <c r="B12" s="14" t="s">
         <v>22</v>
@@ -2206,18 +2202,21 @@
       <c r="H12" s="44">
         <v>594000</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="J12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" ht="16.8" spans="1:10">
       <c r="A13" s="13"/>
       <c r="B13" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="16"/>
-      <c r="E13" s="45" t="s">
-        <v>24</v>
+      <c r="E13" s="43" t="s">
+        <v>8</v>
       </c>
       <c r="F13" s="16">
         <v>1525000</v>
@@ -2228,8 +2227,12 @@
       <c r="H13" s="44">
         <v>995000</v>
       </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="J13" s="52">
+        <f>H4+H5+H8+H16+H17+H18+H19+H21+H22+H23+H27+H33+H34+F24</f>
+        <v>76478053</v>
+      </c>
+    </row>
+    <row r="14" ht="16.8" spans="1:12">
       <c r="A14" s="13"/>
       <c r="B14" s="14" t="s">
         <v>25</v>
@@ -2250,50 +2253,41 @@
       <c r="H14" s="44">
         <v>2996000</v>
       </c>
-      <c r="K14" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" t="s">
-        <v>27</v>
-      </c>
+      <c r="J14" s="53"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="53"/>
     </row>
     <row r="15" ht="17.55" spans="1:12">
       <c r="A15" s="18"/>
       <c r="B15" s="19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D15" s="21">
         <v>10000000</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F15" s="21">
         <v>10000000</v>
       </c>
       <c r="G15" s="21"/>
-      <c r="H15" s="46">
+      <c r="H15" s="45">
         <v>10000000</v>
       </c>
-      <c r="J15" t="s">
-        <v>31</v>
-      </c>
-      <c r="K15" s="44">
-        <v>65000</v>
-      </c>
-      <c r="L15" s="44">
-        <v>110000</v>
-      </c>
+      <c r="J15" s="53"/>
+      <c r="K15" s="54"/>
+      <c r="L15" s="54"/>
     </row>
     <row r="16" ht="16.8" spans="1:12">
       <c r="A16" s="22" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C16" s="24" t="s">
         <v>8</v>
@@ -2307,26 +2301,20 @@
       <c r="F16" s="25">
         <v>13909500</v>
       </c>
-      <c r="G16" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="47">
+      <c r="G16" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="46">
         <v>12478500</v>
       </c>
-      <c r="J16" t="s">
-        <v>34</v>
-      </c>
-      <c r="K16" s="44">
-        <v>85000</v>
-      </c>
-      <c r="L16" s="44">
-        <v>115000</v>
-      </c>
+      <c r="J16" s="53"/>
+      <c r="K16" s="54"/>
+      <c r="L16" s="54"/>
     </row>
     <row r="17" ht="16.8" spans="1:8">
       <c r="A17" s="22"/>
       <c r="B17" s="14" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>8</v>
@@ -2340,8 +2328,8 @@
       <c r="F17" s="16">
         <v>2415000</v>
       </c>
-      <c r="G17" s="16" t="s">
-        <v>12</v>
+      <c r="G17" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="H17" s="44">
         <v>1800000</v>
@@ -2350,7 +2338,7 @@
     <row r="18" ht="16.8" spans="1:8">
       <c r="A18" s="22"/>
       <c r="B18" s="14" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>8</v>
@@ -2364,8 +2352,8 @@
       <c r="F18" s="16">
         <v>10000000</v>
       </c>
-      <c r="G18" s="16" t="s">
-        <v>12</v>
+      <c r="G18" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="H18" s="44">
         <v>7025000</v>
@@ -2374,7 +2362,7 @@
     <row r="19" ht="16.8" spans="1:11">
       <c r="A19" s="22"/>
       <c r="B19" s="14" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>8</v>
@@ -2388,37 +2376,37 @@
       <c r="F19" s="16">
         <v>6637500</v>
       </c>
-      <c r="G19" s="16" t="s">
-        <v>12</v>
+      <c r="G19" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="H19" s="44">
         <v>12023500</v>
       </c>
-      <c r="J19" s="53"/>
-      <c r="K19" s="53"/>
+      <c r="J19" s="52"/>
+      <c r="K19" s="52"/>
     </row>
     <row r="20" ht="16.8" spans="1:8">
       <c r="A20" s="22"/>
       <c r="B20" s="14" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D20" s="16"/>
       <c r="E20" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F20" s="16"/>
       <c r="G20" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H20" s="44"/>
     </row>
     <row r="21" ht="16.8" spans="1:8">
       <c r="A21" s="22"/>
       <c r="B21" s="14" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>8</v>
@@ -2432,8 +2420,8 @@
       <c r="F21" s="16">
         <v>1998000</v>
       </c>
-      <c r="G21" s="16" t="s">
-        <v>12</v>
+      <c r="G21" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="H21" s="44">
         <v>1665000</v>
@@ -2442,7 +2430,7 @@
     <row r="22" ht="16.8" spans="1:8">
       <c r="A22" s="22"/>
       <c r="B22" s="14" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>8</v>
@@ -2451,11 +2439,11 @@
         <v>2410000</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F22" s="16"/>
-      <c r="G22" s="16" t="s">
-        <v>12</v>
+      <c r="G22" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="H22" s="44">
         <v>2110000</v>
@@ -2464,7 +2452,7 @@
     <row r="23" ht="16.8" spans="1:10">
       <c r="A23" s="22"/>
       <c r="B23" s="14" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>8</v>
@@ -2479,37 +2467,37 @@
         <v>1312502</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H23" s="44">
         <v>1750003</v>
       </c>
-      <c r="J23" s="53"/>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="J23" s="52"/>
+    </row>
+    <row r="24" ht="16.8" spans="1:8">
       <c r="A24" s="22"/>
       <c r="B24" s="14" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D24" s="16"/>
-      <c r="E24" s="45" t="s">
-        <v>12</v>
+      <c r="E24" s="47" t="s">
+        <v>39</v>
       </c>
       <c r="F24" s="16">
         <v>2280000</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H24" s="44"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" ht="16.8" spans="1:10">
       <c r="A25" s="22"/>
       <c r="B25" s="14" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>8</v>
@@ -2529,12 +2517,12 @@
       <c r="H25" s="44">
         <v>1190009</v>
       </c>
-      <c r="J25" s="53"/>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="J25" s="52"/>
+    </row>
+    <row r="26" ht="16.8" spans="1:8">
       <c r="A26" s="22"/>
       <c r="B26" s="14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>8</v>
@@ -2555,10 +2543,10 @@
         <v>5600000</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" ht="16.8" spans="1:8">
       <c r="A27" s="22"/>
       <c r="B27" s="14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>8</v>
@@ -2572,8 +2560,8 @@
       <c r="F27" s="16">
         <v>915750</v>
       </c>
-      <c r="G27" s="16" t="s">
-        <v>12</v>
+      <c r="G27" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="H27" s="44">
         <v>600000</v>
@@ -2582,25 +2570,25 @@
     <row r="28" ht="16.8" spans="1:8">
       <c r="A28" s="22"/>
       <c r="B28" s="14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F28" s="16"/>
       <c r="G28" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H28" s="44"/>
     </row>
     <row r="29" ht="16.8" spans="1:8">
       <c r="A29" s="22"/>
       <c r="B29" s="14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>8</v>
@@ -2609,18 +2597,18 @@
         <v>3948000</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F29" s="16"/>
       <c r="G29" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H29" s="44"/>
     </row>
     <row r="30" ht="16.8" spans="1:8">
       <c r="A30" s="22"/>
       <c r="B30" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>8</v>
@@ -2629,36 +2617,36 @@
         <v>250000</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F30" s="16"/>
       <c r="G30" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H30" s="44"/>
     </row>
     <row r="31" ht="16.8" spans="1:8">
       <c r="A31" s="22"/>
       <c r="B31" s="14" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D31" s="16"/>
       <c r="E31" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F31" s="16"/>
       <c r="G31" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H31" s="44"/>
     </row>
     <row r="32" ht="17.55" spans="1:8">
       <c r="A32" s="27"/>
       <c r="B32" s="28" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C32" s="29" t="s">
         <v>8</v>
@@ -2671,16 +2659,16 @@
         <v>915750</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H32" s="48"/>
     </row>
     <row r="33" ht="17.55" spans="1:8">
       <c r="A33" s="9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>8</v>
@@ -2694,17 +2682,17 @@
       <c r="F33" s="12">
         <v>8368100</v>
       </c>
-      <c r="G33" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="H33" s="43">
+      <c r="G33" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="42">
         <v>4047600</v>
       </c>
     </row>
     <row r="34" ht="16.8" spans="1:8">
       <c r="A34" s="13"/>
       <c r="B34" s="14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>8</v>
@@ -2718,17 +2706,17 @@
       <c r="F34" s="16">
         <v>4715000</v>
       </c>
-      <c r="G34" s="16" t="s">
-        <v>12</v>
+      <c r="G34" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="H34" s="44">
         <v>2585000</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" ht="16.8" spans="1:8">
       <c r="A35" s="13"/>
       <c r="B35" s="14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>8</v>
@@ -2742,17 +2730,17 @@
       <c r="F35" s="16">
         <v>638483</v>
       </c>
-      <c r="G35" s="16" t="s">
-        <v>12</v>
+      <c r="G35" s="43" t="s">
+        <v>8</v>
       </c>
       <c r="H35" s="16">
         <v>269482</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" ht="16.8" spans="1:8">
       <c r="A36" s="31"/>
       <c r="B36" s="32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>8</v>
@@ -2760,25 +2748,25 @@
       <c r="D36" s="16">
         <v>1168000</v>
       </c>
-      <c r="E36" s="49" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="50">
+      <c r="E36" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="49">
         <v>893000</v>
       </c>
-      <c r="G36" s="49" t="s">
+      <c r="G36" s="43" t="s">
         <v>8</v>
       </c>
       <c r="H36" s="16">
         <v>847000</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" ht="16.8" spans="1:8">
       <c r="A37" s="33" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C37" s="34"/>
       <c r="D37" s="35"/>
@@ -2789,12 +2777,12 @@
         <v>1020000</v>
       </c>
       <c r="G37" s="35"/>
-      <c r="H37" s="51"/>
+      <c r="H37" s="50"/>
     </row>
     <row r="38" ht="16.8" spans="1:8">
       <c r="A38" s="36"/>
       <c r="B38" s="14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C38" s="34"/>
       <c r="D38" s="35"/>
@@ -2805,12 +2793,12 @@
         <v>1350000</v>
       </c>
       <c r="G38" s="35"/>
-      <c r="H38" s="51"/>
+      <c r="H38" s="50"/>
     </row>
     <row r="39" ht="16.8" spans="1:8">
       <c r="A39" s="36"/>
       <c r="B39" s="14" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C39" s="34"/>
       <c r="D39" s="35"/>
@@ -2821,12 +2809,12 @@
         <v>600000</v>
       </c>
       <c r="G39" s="35"/>
-      <c r="H39" s="51"/>
+      <c r="H39" s="50"/>
     </row>
     <row r="40" ht="16.8" spans="1:8">
       <c r="A40" s="36"/>
       <c r="B40" s="14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C40" s="34"/>
       <c r="D40" s="35"/>
@@ -2837,12 +2825,12 @@
         <v>318134</v>
       </c>
       <c r="G40" s="35"/>
-      <c r="H40" s="51"/>
+      <c r="H40" s="50"/>
     </row>
     <row r="41" ht="16.8" spans="1:8">
       <c r="A41" s="36"/>
       <c r="B41" s="14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C41" s="34"/>
       <c r="D41" s="35"/>
@@ -2853,12 +2841,12 @@
         <v>248700</v>
       </c>
       <c r="G41" s="35"/>
-      <c r="H41" s="51"/>
+      <c r="H41" s="50"/>
     </row>
     <row r="42" ht="16.8" spans="1:8">
       <c r="A42" s="36"/>
       <c r="B42" s="14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C42" s="34"/>
       <c r="D42" s="35"/>
@@ -2869,12 +2857,12 @@
         <v>1029180</v>
       </c>
       <c r="G42" s="35"/>
-      <c r="H42" s="51"/>
+      <c r="H42" s="50"/>
     </row>
     <row r="43" ht="16.8" spans="1:8">
       <c r="A43" s="36"/>
       <c r="B43" s="14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C43" s="34"/>
       <c r="D43" s="35"/>
@@ -2885,12 +2873,12 @@
         <v>270000</v>
       </c>
       <c r="G43" s="35"/>
-      <c r="H43" s="51"/>
+      <c r="H43" s="50"/>
     </row>
     <row r="44" ht="16.8" spans="1:8">
       <c r="A44" s="36"/>
       <c r="B44" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C44" s="34"/>
       <c r="D44" s="35"/>
@@ -2901,12 +2889,12 @@
         <v>1000000</v>
       </c>
       <c r="G44" s="35"/>
-      <c r="H44" s="51"/>
+      <c r="H44" s="50"/>
     </row>
     <row r="45" ht="16.8" spans="1:8">
       <c r="A45" s="36"/>
       <c r="B45" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C45" s="34"/>
       <c r="D45" s="35"/>
@@ -2917,12 +2905,12 @@
         <v>3000000</v>
       </c>
       <c r="G45" s="35"/>
-      <c r="H45" s="51"/>
+      <c r="H45" s="50"/>
     </row>
     <row r="46" ht="16.8" spans="1:8">
       <c r="A46" s="36"/>
       <c r="B46" s="14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C46" s="34"/>
       <c r="D46" s="35"/>
@@ -2933,18 +2921,18 @@
         <v>1800000</v>
       </c>
       <c r="G46" s="35"/>
-      <c r="H46" s="51"/>
-    </row>
-    <row r="47" spans="1:8">
+      <c r="H46" s="50"/>
+    </row>
+    <row r="47" ht="16.8" spans="1:8">
       <c r="A47" s="37"/>
-      <c r="B47" s="38" t="s">
-        <v>68</v>
+      <c r="B47" s="14" t="s">
+        <v>65</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="52">
+      <c r="H47" s="51">
         <v>2450000</v>
       </c>
     </row>
@@ -2962,16 +2950,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F52" s="4"/>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F53" s="4"/>
     </row>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -59,7 +59,7 @@
     <t>PAID 100%</t>
   </si>
   <si>
-    <t>PAID 1/2</t>
+    <t>PAID 2/2</t>
   </si>
   <si>
     <t>SEDANA JAYA</t>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="J1" s="52"/>
     </row>
-    <row r="2" ht="16.8" spans="1:8">
+    <row r="2" spans="1:8">
       <c r="A2" s="9" t="s">
         <v>6</v>
       </c>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="L11" s="52"/>
     </row>
-    <row r="12" ht="16.8" spans="1:10">
+    <row r="12" spans="1:10">
       <c r="A12" s="13"/>
       <c r="B12" s="14" t="s">
         <v>22</v>
@@ -2206,7 +2206,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" ht="16.8" spans="1:10">
+    <row r="13" spans="1:10">
       <c r="A13" s="13"/>
       <c r="B13" s="14" t="s">
         <v>24</v>
@@ -2228,11 +2228,11 @@
         <v>995000</v>
       </c>
       <c r="J13" s="52">
-        <f>H4+H5+H8+H16+H17+H18+H19+H21+H22+H23+H27+H33+H34+F24</f>
-        <v>76478053</v>
-      </c>
-    </row>
-    <row r="14" ht="16.8" spans="1:12">
+        <f>H23+F24+H11</f>
+        <v>4182003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="13"/>
       <c r="B14" s="14" t="s">
         <v>25</v>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="73">
   <si>
     <t>DIVISION</t>
   </si>
@@ -47,6 +47,9 @@
     <t>NOVEMBER</t>
   </si>
   <si>
+    <t>DECEMBER</t>
+  </si>
+  <si>
     <t>KITCHEN</t>
   </si>
   <si>
@@ -62,6 +65,9 @@
     <t>PAID 2/2</t>
   </si>
   <si>
+    <t>LAUNCHED</t>
+  </si>
+  <si>
     <t>SEDANA JAYA</t>
   </si>
   <si>
@@ -71,6 +77,9 @@
     <t>MAMA RADA PRODUCTION</t>
   </si>
   <si>
+    <t>N/O</t>
+  </si>
+  <si>
     <t>KSP</t>
   </si>
   <si>
@@ -80,12 +89,12 @@
     <t>BAYU AGNI</t>
   </si>
   <si>
+    <t>NO OUTSTANDING YET</t>
+  </si>
+  <si>
     <t>JOY GREEN</t>
   </si>
   <si>
-    <t>N/O</t>
-  </si>
-  <si>
     <t>CELEBRITY BAKERY</t>
   </si>
   <si>
@@ -98,9 +107,6 @@
     <t>BOILER</t>
   </si>
   <si>
-    <t>Total account payable</t>
-  </si>
-  <si>
     <t>DISHY SOAP</t>
   </si>
   <si>
@@ -171,6 +177,15 @@
   </si>
   <si>
     <t>DEWATA KENCANA DISTRIBUSI</t>
+  </si>
+  <si>
+    <t>YET</t>
+  </si>
+  <si>
+    <t>INDOBEV MENTARI SEJAHTERA</t>
+  </si>
+  <si>
+    <t>DINETA JAYA</t>
   </si>
   <si>
     <t>ISOLA WINE</t>
@@ -655,7 +670,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -802,19 +817,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -870,17 +872,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -939,10 +930,10 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -952,6 +943,41 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -959,6 +985,19 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1085,7 +1124,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="23" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="25" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1097,34 +1136,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1209,7 +1248,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1276,53 +1315,56 @@
     <xf numFmtId="181" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="180" fontId="1" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1330,40 +1372,49 @@
     <xf numFmtId="181" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="181" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="181" fontId="0" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="0" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="181" fontId="0" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="181" fontId="0" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -1372,8 +1423,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="181" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1908,7 +2010,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="18.859375" style="1" customWidth="1"/>
@@ -1918,11 +2020,11 @@
     <col min="5" max="5" width="12.5703125" style="3" customWidth="1"/>
     <col min="6" max="7" width="13.6640625" customWidth="1"/>
     <col min="8" max="8" width="13.6640625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.3359375"/>
+    <col min="9" max="9" width="14.3359375" style="3"/>
     <col min="10" max="10" width="17.7109375" customWidth="1"/>
     <col min="11" max="11" width="15.4296875"/>
     <col min="12" max="12" width="22.6640625" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625"/>
+    <col min="13" max="13" width="15.25"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.35" spans="1:10">
@@ -1938,338 +2040,418 @@
       <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="39" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="52"/>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="41" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="12">
         <v>66835000</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="12">
         <v>39738000</v>
       </c>
-      <c r="G2" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="42">
+      <c r="G2" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="43">
         <v>34233500</v>
       </c>
-    </row>
-    <row r="3" ht="16.8" spans="1:8">
+      <c r="I2" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="43">
+        <v>42310500</v>
+      </c>
+      <c r="M2" s="56">
+        <f>SUM(J2:J40)</f>
+        <v>251673016</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="13"/>
       <c r="B3" s="14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="16">
         <v>45478060</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="16">
         <v>39027410</v>
       </c>
-      <c r="G3" s="43" t="s">
-        <v>8</v>
+      <c r="G3" s="31" t="s">
+        <v>9</v>
       </c>
       <c r="H3" s="44">
         <v>45303890</v>
       </c>
-    </row>
-    <row r="4" ht="16.8" spans="1:8">
+      <c r="I3" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="44">
+        <v>48169400</v>
+      </c>
+    </row>
+    <row r="4" ht="16.8" spans="1:10">
       <c r="A4" s="13"/>
       <c r="B4" s="14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="16">
         <v>29900100</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="16">
         <v>20617200</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="44">
         <v>21943450</v>
       </c>
-    </row>
-    <row r="5" ht="16.8" spans="1:8">
+      <c r="I4" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="44">
+        <v>36138000</v>
+      </c>
+    </row>
+    <row r="5" ht="16.8" spans="1:10">
       <c r="A5" s="13"/>
       <c r="B5" s="14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="16">
         <v>4400000</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="16">
         <v>5560000</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="44">
         <v>320000</v>
       </c>
-    </row>
-    <row r="6" ht="16.8" spans="1:8">
+      <c r="I5" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="44"/>
+    </row>
+    <row r="6" ht="16.8" spans="1:10">
       <c r="A6" s="13"/>
       <c r="B6" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="16">
         <v>5610900</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="16">
         <v>3578050</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="44">
         <v>5069850</v>
       </c>
-    </row>
-    <row r="7" ht="16.8" spans="1:8">
+      <c r="I6" s="35"/>
+      <c r="J6" s="44"/>
+    </row>
+    <row r="7" ht="16.8" spans="1:10">
       <c r="A7" s="13"/>
       <c r="B7" s="14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="16">
         <v>3663300</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="16">
         <v>1983600</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="44">
         <v>13417600</v>
       </c>
-    </row>
-    <row r="8" ht="16.8" spans="1:8">
+      <c r="I7" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="44">
+        <v>9006800</v>
+      </c>
+    </row>
+    <row r="8" ht="16.8" spans="1:12">
       <c r="A8" s="13"/>
       <c r="B8" s="14" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="16">
         <v>8775000</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="16">
         <v>7800000</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H8" s="44">
         <v>5850000</v>
       </c>
-    </row>
-    <row r="9" ht="16.8" spans="1:8">
+      <c r="I8" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="44">
+        <v>8775000</v>
+      </c>
+      <c r="L8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" ht="16.8" spans="1:10">
       <c r="A9" s="13"/>
       <c r="B9" s="14" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H9" s="44"/>
-    </row>
-    <row r="10" ht="16.8" spans="1:8">
+      <c r="I9" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="44"/>
+    </row>
+    <row r="10" ht="16.8" spans="1:12">
       <c r="A10" s="13"/>
       <c r="B10" s="14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D10" s="16"/>
       <c r="E10" s="17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H10" s="44"/>
+      <c r="I10" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="44">
+        <v>160000</v>
+      </c>
+      <c r="L10" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="11" ht="16.8" spans="1:12">
       <c r="A11" s="13"/>
       <c r="B11" s="14" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D11" s="16"/>
       <c r="E11" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" s="16">
         <v>326000</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H11" s="44">
         <v>152000</v>
       </c>
-      <c r="L11" s="52"/>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="I11" s="53" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="44">
+        <v>329000</v>
+      </c>
+      <c r="L11" s="56" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" ht="16.8" spans="1:12">
       <c r="A12" s="13"/>
       <c r="B12" s="14" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="16"/>
       <c r="E12" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="16">
         <v>924000</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" s="44">
         <v>594000</v>
       </c>
-      <c r="J12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="I12" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="44">
+        <v>319000</v>
+      </c>
+      <c r="L12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" ht="16.8" spans="1:12">
       <c r="A13" s="13"/>
       <c r="B13" s="14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="16"/>
-      <c r="E13" s="43" t="s">
-        <v>8</v>
+      <c r="E13" s="31" t="s">
+        <v>9</v>
       </c>
       <c r="F13" s="16">
         <v>1525000</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13" s="44">
         <v>995000</v>
       </c>
-      <c r="J13" s="52">
-        <f>H23+F24+H11</f>
-        <v>4182003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="I13" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="44">
+        <v>2855000</v>
+      </c>
+      <c r="K13" s="57"/>
+      <c r="L13" s="57"/>
+    </row>
+    <row r="14" ht="16.8" spans="1:12">
       <c r="A14" s="13"/>
       <c r="B14" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="16"/>
       <c r="E14" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="16">
         <v>2320000</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="44">
         <v>2996000</v>
       </c>
-      <c r="J14" s="53"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
     </row>
     <row r="15" ht="17.55" spans="1:12">
       <c r="A15" s="18"/>
       <c r="B15" s="19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D15" s="21">
         <v>10000000</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F15" s="21">
         <v>10000000</v>
@@ -2278,669 +2460,897 @@
       <c r="H15" s="45">
         <v>10000000</v>
       </c>
-      <c r="J15" s="53"/>
-      <c r="K15" s="54"/>
-      <c r="L15" s="54"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="59"/>
+      <c r="L15" s="59"/>
     </row>
     <row r="16" ht="16.8" spans="1:12">
       <c r="A16" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="25">
+        <v>31</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="12">
         <v>20669000</v>
       </c>
-      <c r="E16" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="25">
+      <c r="E16" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="12">
         <v>13909500</v>
       </c>
-      <c r="G16" s="15" t="s">
-        <v>8</v>
+      <c r="G16" s="11" t="s">
+        <v>9</v>
       </c>
       <c r="H16" s="46">
         <v>12478500</v>
       </c>
-      <c r="J16" s="53"/>
-      <c r="K16" s="54"/>
-      <c r="L16" s="54"/>
-    </row>
-    <row r="17" ht="16.8" spans="1:8">
-      <c r="A17" s="22"/>
+      <c r="I16" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="43">
+        <v>14051500</v>
+      </c>
+      <c r="K16" s="59"/>
+      <c r="L16" s="59"/>
+    </row>
+    <row r="17" ht="16.8" spans="1:12">
+      <c r="A17" s="23"/>
       <c r="B17" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="16">
         <v>3230000</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" s="16">
         <v>2415000</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H17" s="44">
+        <v>9</v>
+      </c>
+      <c r="H17" s="47">
         <v>1800000</v>
       </c>
-    </row>
-    <row r="18" ht="16.8" spans="1:8">
-      <c r="A18" s="22"/>
+      <c r="I17" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="44">
+        <v>2860000</v>
+      </c>
+      <c r="K17" s="57"/>
+      <c r="L17" s="57" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="23"/>
       <c r="B18" s="14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="16">
         <v>10775000</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" s="16">
         <v>10000000</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H18" s="44">
+        <v>9</v>
+      </c>
+      <c r="H18" s="47">
         <v>7025000</v>
       </c>
-    </row>
-    <row r="19" ht="16.8" spans="1:11">
-      <c r="A19" s="22"/>
+      <c r="I18" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="J18" s="44">
+        <v>4175000</v>
+      </c>
+      <c r="K18" s="57"/>
+      <c r="L18" s="57" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" ht="16.8" spans="1:12">
+      <c r="A19" s="23"/>
       <c r="B19" s="14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="16">
         <v>10023000</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" s="16">
         <v>6637500</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H19" s="44">
+        <v>9</v>
+      </c>
+      <c r="H19" s="47">
         <v>12023500</v>
       </c>
-      <c r="J19" s="52"/>
-      <c r="K19" s="52"/>
-    </row>
-    <row r="20" ht="16.8" spans="1:8">
-      <c r="A20" s="22"/>
+      <c r="I19" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19" s="44">
+        <v>18173500</v>
+      </c>
+      <c r="K19" s="62"/>
+      <c r="L19" s="57" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" ht="16.8" spans="1:12">
+      <c r="A20" s="23"/>
       <c r="B20" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D20" s="16"/>
       <c r="E20" s="17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F20" s="16"/>
       <c r="G20" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H20" s="44"/>
-    </row>
-    <row r="21" ht="16.8" spans="1:8">
-      <c r="A21" s="22"/>
+        <v>16</v>
+      </c>
+      <c r="H20" s="47"/>
+      <c r="I20" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="44">
+        <v>3633750</v>
+      </c>
+      <c r="L20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="23"/>
       <c r="B21" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="16">
         <v>3663000</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" s="16">
         <v>1998000</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H21" s="44">
+        <v>9</v>
+      </c>
+      <c r="H21" s="47">
         <v>1665000</v>
       </c>
-    </row>
-    <row r="22" ht="16.8" spans="1:8">
-      <c r="A22" s="22"/>
+      <c r="I21" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="44">
+        <v>3552000</v>
+      </c>
+      <c r="L21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" ht="16.8" spans="1:12">
+      <c r="A22" s="23"/>
       <c r="B22" s="14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="16">
         <v>2410000</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F22" s="16"/>
       <c r="G22" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="44">
+        <v>9</v>
+      </c>
+      <c r="H22" s="47">
         <v>2110000</v>
       </c>
-    </row>
-    <row r="23" ht="16.8" spans="1:10">
-      <c r="A23" s="22"/>
+      <c r="I22" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="J22" s="44">
+        <v>12065000</v>
+      </c>
+      <c r="L22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" ht="16.8" spans="1:12">
+      <c r="A23" s="23"/>
       <c r="B23" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="16">
         <v>2447502</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" s="16">
         <v>1312502</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" s="44">
+        <v>24</v>
+      </c>
+      <c r="H23" s="47">
         <v>1750003</v>
       </c>
-      <c r="J23" s="52"/>
-    </row>
-    <row r="24" ht="16.8" spans="1:8">
-      <c r="A24" s="22"/>
+      <c r="I23" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="J23" s="44">
+        <v>1837503</v>
+      </c>
+      <c r="L23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" ht="16.8" spans="1:10">
+      <c r="A24" s="23"/>
       <c r="B24" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D24" s="16"/>
-      <c r="E24" s="47" t="s">
-        <v>39</v>
+      <c r="E24" s="48" t="s">
+        <v>41</v>
       </c>
       <c r="F24" s="16">
         <v>2280000</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H24" s="44"/>
-    </row>
-    <row r="25" ht="16.8" spans="1:10">
-      <c r="A25" s="22"/>
+        <v>16</v>
+      </c>
+      <c r="H24" s="47"/>
+      <c r="I24" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="44"/>
+    </row>
+    <row r="25" ht="16.8" spans="1:12">
+      <c r="A25" s="23"/>
       <c r="B25" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="16">
         <v>4760036</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F25" s="16">
         <v>4760036</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H25" s="44">
+        <v>9</v>
+      </c>
+      <c r="H25" s="47">
         <v>1190009</v>
       </c>
-      <c r="J25" s="52"/>
-    </row>
-    <row r="26" ht="16.8" spans="1:8">
-      <c r="A26" s="22"/>
+      <c r="I25" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="J25" s="44">
+        <v>2380013</v>
+      </c>
+      <c r="L25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" ht="16.8" spans="1:12">
+      <c r="A26" s="23"/>
       <c r="B26" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="16">
         <v>5600000</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" s="16">
         <v>5600000</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H26" s="44">
+        <v>9</v>
+      </c>
+      <c r="H26" s="47">
         <v>5600000</v>
       </c>
-    </row>
-    <row r="27" ht="16.8" spans="1:8">
-      <c r="A27" s="22"/>
+      <c r="I26" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="J26" s="44">
+        <v>5600000</v>
+      </c>
+      <c r="L26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" ht="16.8" spans="1:12">
+      <c r="A27" s="23"/>
       <c r="B27" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="16">
         <v>1225000</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" s="16">
         <v>915750</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H27" s="44">
+        <v>9</v>
+      </c>
+      <c r="H27" s="47">
         <v>600000</v>
       </c>
-    </row>
-    <row r="28" ht="16.8" spans="1:8">
-      <c r="A28" s="22"/>
+      <c r="I27" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="J27" s="44">
+        <v>915750</v>
+      </c>
+      <c r="L27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" ht="16.8" spans="1:10">
+      <c r="A28" s="23"/>
       <c r="B28" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="26" t="s">
-        <v>18</v>
+        <v>45</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>16</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F28" s="16"/>
       <c r="G28" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H28" s="44"/>
-    </row>
-    <row r="29" ht="16.8" spans="1:8">
-      <c r="A29" s="22"/>
+        <v>16</v>
+      </c>
+      <c r="H28" s="47"/>
+      <c r="I28" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="44"/>
+    </row>
+    <row r="29" ht="16.8" spans="1:10">
+      <c r="A29" s="23"/>
       <c r="B29" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" s="16">
         <v>3948000</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F29" s="16"/>
       <c r="G29" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H29" s="44"/>
-    </row>
-    <row r="30" ht="16.8" spans="1:8">
-      <c r="A30" s="22"/>
+        <v>16</v>
+      </c>
+      <c r="H29" s="47"/>
+      <c r="I29" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="44"/>
+    </row>
+    <row r="30" ht="16.8" spans="1:10">
+      <c r="A30" s="23"/>
       <c r="B30" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" s="16">
         <v>250000</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="F30" s="16"/>
+        <v>48</v>
+      </c>
+      <c r="F30" s="16">
+        <v>300000</v>
+      </c>
       <c r="G30" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="H30" s="44"/>
-    </row>
-    <row r="31" ht="16.8" spans="1:8">
-      <c r="A31" s="22"/>
+        <v>48</v>
+      </c>
+      <c r="H30" s="47">
+        <v>300000</v>
+      </c>
+      <c r="I30" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="44"/>
+    </row>
+    <row r="31" ht="16.8" spans="1:12">
+      <c r="A31" s="23"/>
       <c r="B31" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="26" t="s">
-        <v>18</v>
+        <v>49</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>16</v>
       </c>
       <c r="D31" s="16"/>
       <c r="E31" s="17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F31" s="16"/>
       <c r="G31" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H31" s="44"/>
-    </row>
-    <row r="32" ht="17.55" spans="1:8">
-      <c r="A32" s="27"/>
-      <c r="B32" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="30"/>
-      <c r="E32" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="30">
+        <v>16</v>
+      </c>
+      <c r="H31" s="47"/>
+      <c r="I31" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="J31" s="44">
+        <v>975300</v>
+      </c>
+      <c r="L31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="23"/>
+      <c r="B32" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="16"/>
+      <c r="E32" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="16"/>
+      <c r="G32" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="47"/>
+      <c r="I32" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="J32" s="44">
+        <v>1600000</v>
+      </c>
+      <c r="L32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="23"/>
+      <c r="B33" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="16"/>
+      <c r="E33" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="16"/>
+      <c r="G33" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="47"/>
+      <c r="I33" s="61"/>
+      <c r="J33" s="44"/>
+    </row>
+    <row r="34" ht="17.55" spans="1:10">
+      <c r="A34" s="25"/>
+      <c r="B34" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="28"/>
+      <c r="E34" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="28">
         <v>915750</v>
       </c>
-      <c r="G32" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H32" s="48"/>
-    </row>
-    <row r="33" ht="17.55" spans="1:8">
-      <c r="A33" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="12">
+      <c r="G34" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="50"/>
+      <c r="I34" s="65"/>
+      <c r="J34" s="66"/>
+    </row>
+    <row r="35" ht="17.55" spans="1:12">
+      <c r="A35" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="12">
         <v>4897000</v>
       </c>
-      <c r="E33" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="12">
+      <c r="E35" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="12">
         <v>8368100</v>
       </c>
-      <c r="G33" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H33" s="42">
+      <c r="G35" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" s="46">
         <v>4047600</v>
       </c>
-    </row>
-    <row r="34" ht="16.8" spans="1:8">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="16">
+      <c r="I35" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="J35" s="43">
+        <v>1897000</v>
+      </c>
+      <c r="L35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" ht="16.8" spans="1:10">
+      <c r="A36" s="13"/>
+      <c r="B36" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="16">
         <v>4375000</v>
       </c>
-      <c r="E34" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" s="16">
+      <c r="E36" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="16">
         <v>4715000</v>
       </c>
-      <c r="G34" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H34" s="44">
+      <c r="G36" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" s="47">
         <v>2585000</v>
       </c>
-    </row>
-    <row r="35" ht="16.8" spans="1:8">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="16">
+      <c r="I36" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="J36" s="44">
+        <v>27100000</v>
+      </c>
+    </row>
+    <row r="37" ht="17.55" spans="1:10">
+      <c r="A37" s="13"/>
+      <c r="B37" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="16">
         <v>1007480.64</v>
       </c>
-      <c r="E35" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="16">
+      <c r="E37" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="16">
         <v>638483</v>
       </c>
-      <c r="G35" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="H35" s="16">
+      <c r="G37" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="H37" s="47">
         <v>269482</v>
       </c>
-    </row>
-    <row r="36" ht="16.8" spans="1:8">
-      <c r="A36" s="31"/>
-      <c r="B36" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="16">
+      <c r="I37" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" s="44"/>
+    </row>
+    <row r="38" ht="17.55" spans="1:12">
+      <c r="A38" s="29"/>
+      <c r="B38" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="32">
         <v>1168000</v>
       </c>
-      <c r="E36" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="49">
+      <c r="E38" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="32">
         <v>893000</v>
       </c>
-      <c r="G36" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="H36" s="16">
+      <c r="G38" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" s="51">
         <v>847000</v>
       </c>
-    </row>
-    <row r="37" ht="16.8" spans="1:8">
-      <c r="A37" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" s="34"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="16">
+      <c r="I38" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="J38" s="69">
+        <v>944000</v>
+      </c>
+      <c r="L38" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" ht="16.8" spans="1:10">
+      <c r="A39" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="33"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="12">
         <v>1020000</v>
       </c>
-      <c r="G37" s="35"/>
-      <c r="H37" s="50"/>
-    </row>
-    <row r="38" ht="16.8" spans="1:8">
-      <c r="A38" s="36"/>
-      <c r="B38" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" s="34"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="16">
+      <c r="G39" s="34"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="71"/>
+    </row>
+    <row r="40" ht="16.8" spans="1:10">
+      <c r="A40" s="23"/>
+      <c r="B40" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="35"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="16">
         <v>1350000</v>
       </c>
-      <c r="G38" s="35"/>
-      <c r="H38" s="50"/>
-    </row>
-    <row r="39" ht="16.8" spans="1:8">
-      <c r="A39" s="36"/>
-      <c r="B39" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" s="34"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="16">
+      <c r="G40" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" s="53">
+        <v>1800000</v>
+      </c>
+      <c r="I40" s="72" t="s">
+        <v>24</v>
+      </c>
+      <c r="J40" s="73">
+        <v>1850000</v>
+      </c>
+    </row>
+    <row r="41" ht="16.8" spans="1:10">
+      <c r="A41" s="23"/>
+      <c r="B41" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" s="35"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="16">
         <v>600000</v>
       </c>
-      <c r="G39" s="35"/>
-      <c r="H39" s="50"/>
-    </row>
-    <row r="40" ht="16.8" spans="1:8">
-      <c r="A40" s="36"/>
-      <c r="B40" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C40" s="34"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="16">
+      <c r="G41" s="36"/>
+      <c r="H41" s="53"/>
+      <c r="I41" s="72"/>
+      <c r="J41" s="74"/>
+    </row>
+    <row r="42" ht="16.8" spans="1:10">
+      <c r="A42" s="23"/>
+      <c r="B42" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="35"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="16">
         <v>318134</v>
       </c>
-      <c r="G40" s="35"/>
-      <c r="H40" s="50"/>
-    </row>
-    <row r="41" ht="16.8" spans="1:8">
-      <c r="A41" s="36"/>
-      <c r="B41" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C41" s="34"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="16">
+      <c r="G42" s="36"/>
+      <c r="H42" s="53"/>
+      <c r="I42" s="72"/>
+      <c r="J42" s="74"/>
+    </row>
+    <row r="43" ht="16.8" spans="1:10">
+      <c r="A43" s="23"/>
+      <c r="B43" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="35"/>
+      <c r="D43" s="36"/>
+      <c r="E43" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" s="16">
         <v>248700</v>
       </c>
-      <c r="G41" s="35"/>
-      <c r="H41" s="50"/>
-    </row>
-    <row r="42" ht="16.8" spans="1:8">
-      <c r="A42" s="36"/>
-      <c r="B42" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="16">
+      <c r="G43" s="36"/>
+      <c r="H43" s="53"/>
+      <c r="I43" s="72"/>
+      <c r="J43" s="74"/>
+    </row>
+    <row r="44" ht="16.8" spans="1:10">
+      <c r="A44" s="23"/>
+      <c r="B44" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="35"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="16">
         <v>1029180</v>
       </c>
-      <c r="G42" s="35"/>
-      <c r="H42" s="50"/>
-    </row>
-    <row r="43" ht="16.8" spans="1:8">
-      <c r="A43" s="36"/>
-      <c r="B43" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" s="34"/>
-      <c r="D43" s="35"/>
-      <c r="E43" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="16">
+      <c r="G44" s="36"/>
+      <c r="H44" s="53"/>
+      <c r="I44" s="72"/>
+      <c r="J44" s="74"/>
+    </row>
+    <row r="45" ht="16.8" spans="1:10">
+      <c r="A45" s="23"/>
+      <c r="B45" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" s="35"/>
+      <c r="D45" s="36"/>
+      <c r="E45" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" s="16">
         <v>270000</v>
       </c>
-      <c r="G43" s="35"/>
-      <c r="H43" s="50"/>
-    </row>
-    <row r="44" ht="16.8" spans="1:8">
-      <c r="A44" s="36"/>
-      <c r="B44" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" s="34"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="16">
+      <c r="G45" s="36"/>
+      <c r="H45" s="53"/>
+      <c r="I45" s="72"/>
+      <c r="J45" s="74"/>
+    </row>
+    <row r="46" ht="16.8" spans="1:10">
+      <c r="A46" s="23"/>
+      <c r="B46" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" s="35"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" s="16">
         <v>1000000</v>
       </c>
-      <c r="G44" s="35"/>
-      <c r="H44" s="50"/>
-    </row>
-    <row r="45" ht="16.8" spans="1:8">
-      <c r="A45" s="36"/>
-      <c r="B45" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C45" s="34"/>
-      <c r="D45" s="35"/>
-      <c r="E45" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="16">
+      <c r="G46" s="36"/>
+      <c r="H46" s="53"/>
+      <c r="I46" s="72"/>
+      <c r="J46" s="74"/>
+    </row>
+    <row r="47" ht="16.8" spans="1:10">
+      <c r="A47" s="23"/>
+      <c r="B47" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" s="35"/>
+      <c r="D47" s="36"/>
+      <c r="E47" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" s="16">
         <v>3000000</v>
       </c>
-      <c r="G45" s="35"/>
-      <c r="H45" s="50"/>
-    </row>
-    <row r="46" ht="16.8" spans="1:8">
-      <c r="A46" s="36"/>
-      <c r="B46" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C46" s="34"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" s="16">
+      <c r="G47" s="36"/>
+      <c r="H47" s="53"/>
+      <c r="I47" s="72"/>
+      <c r="J47" s="74"/>
+    </row>
+    <row r="48" ht="16.8" spans="1:10">
+      <c r="A48" s="23"/>
+      <c r="B48" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="35"/>
+      <c r="D48" s="36"/>
+      <c r="E48" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" s="16">
         <v>1800000</v>
       </c>
-      <c r="G46" s="35"/>
-      <c r="H46" s="50"/>
-    </row>
-    <row r="47" ht="16.8" spans="1:8">
-      <c r="A47" s="37"/>
-      <c r="B47" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="F47" s="4"/>
-      <c r="G47" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H47" s="51">
+      <c r="G48" s="36"/>
+      <c r="H48" s="53"/>
+      <c r="I48" s="72"/>
+      <c r="J48" s="74"/>
+    </row>
+    <row r="49" ht="17.55" spans="1:10">
+      <c r="A49" s="25"/>
+      <c r="B49" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="37"/>
+      <c r="D49" s="38"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H49" s="54">
         <v>2450000</v>
       </c>
-    </row>
-    <row r="48" spans="6:6">
-      <c r="F48" s="4"/>
-    </row>
-    <row r="49" spans="6:6">
-      <c r="F49" s="4"/>
+      <c r="I49" s="37"/>
+      <c r="J49" s="75"/>
     </row>
     <row r="50" spans="6:6">
       <c r="F50" s="4"/>
@@ -2948,27 +3358,33 @@
     <row r="51" spans="6:6">
       <c r="F51" s="4"/>
     </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="1" t="s">
-        <v>66</v>
-      </c>
+    <row r="52" spans="6:6">
       <c r="F52" s="4"/>
     </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>67</v>
-      </c>
+    <row r="53" spans="6:6">
       <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F55" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:A15"/>
-    <mergeCell ref="A16:A32"/>
-    <mergeCell ref="A33:A36"/>
-    <mergeCell ref="A37:A47"/>
+    <mergeCell ref="A16:A34"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A39:A49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
+++ b/SUPPLIER RELATED/SUPPLIER PAYMENT STATUS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17020"/>
+    <workbookView windowWidth="27080" windowHeight="17020"/>
   </bookViews>
   <sheets>
     <sheet name="SUPPLIER PAYMENT STATUS" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="81">
   <si>
     <t>DIVISION</t>
   </si>
@@ -74,7 +74,7 @@
     <t>PAID 1/2</t>
   </si>
   <si>
-    <t>5 &amp; 25 JAN</t>
+    <t>15 &amp; 25 JAN</t>
   </si>
   <si>
     <t>OUTSTANDING CONFIRMED</t>
@@ -89,21 +89,36 @@
     <t>RAFI SEAFOOD (SEAFOOD)</t>
   </si>
   <si>
+    <t>MAMA RADA PRODUCTION</t>
+  </si>
+  <si>
+    <t>N/O</t>
+  </si>
+  <si>
+    <t>KSP (CHICKEN)</t>
+  </si>
+  <si>
     <t>MAKER</t>
   </si>
   <si>
-    <t>MAMA RADA PRODUCTION</t>
-  </si>
-  <si>
-    <t>N/O</t>
-  </si>
-  <si>
-    <t>KSP (CHICKEN)</t>
-  </si>
-  <si>
     <t>SURYA CIPTA NIAGA (STEAK MEAT)</t>
   </si>
   <si>
+    <r>
+      <t>NOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: BU BUNGA Bill's shown on status is only half of the total bill and MulIa Jaya has been removed from the lists since it's paid by petty cash. There's also small revision on BU BUNGA 1st payment due date which is supposed to be 15th instead of 5th of each month.</t>
+    </r>
+  </si>
+  <si>
     <t>BAYU AGNI (LPG GAS)</t>
   </si>
   <si>
@@ -119,7 +134,7 @@
     <t>BOILER (DUMPLINGS)</t>
   </si>
   <si>
-    <t>DISHY SOAP CHEMICALS)</t>
+    <t>DISHY SOAP (CHEMICALS)</t>
   </si>
   <si>
     <t>DAILY BAGUETTE (BREAD)</t>
@@ -134,6 +149,9 @@
     <t>PAID 2ND</t>
   </si>
   <si>
+    <t>PAID 3ND</t>
+  </si>
+  <si>
     <t>BAR</t>
   </si>
   <si>
@@ -149,18 +167,24 @@
     <t>PNB (ALCOHOL)</t>
   </si>
   <si>
-    <t>TOTAL DECEMBER BILL (TENTATIVE)</t>
+    <t>TOTAL DECEMBER'S BILL</t>
   </si>
   <si>
     <t>DSP (ALCOHOL)</t>
   </si>
   <si>
+    <t>INITIAL</t>
+  </si>
+  <si>
     <t>DSP ARYA BIMA (ALCOHOL)</t>
   </si>
   <si>
     <t>SELERA (STIR UP SYRUP)</t>
   </si>
   <si>
+    <t>UNPAID</t>
+  </si>
+  <si>
     <t>DW BALI (ALCOHOL)</t>
   </si>
   <si>
@@ -185,12 +209,6 @@
     <t>CHAI CHITAI (TEA)</t>
   </si>
   <si>
-    <t>MULIA JAYA (PASSION FRUIT)</t>
-  </si>
-  <si>
-    <t>BY CASH</t>
-  </si>
-  <si>
     <t>DEWATA KENCANA DISTRIBUSI (ICELAND)</t>
   </si>
   <si>
@@ -230,13 +248,7 @@
     <t>COFFEE MACHINE MAINTENANCE</t>
   </si>
   <si>
-    <t>cling</t>
-  </si>
-  <si>
     <t>TWIN PACK MINI &amp; ANT KILLER (TKP)</t>
-  </si>
-  <si>
-    <t>plastic vacuum</t>
   </si>
   <si>
     <t>GLASS TISSUE BOX (TKP)</t>
@@ -276,7 +288,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
@@ -284,6 +296,7 @@
     <numFmt numFmtId="180" formatCode="[$-409]d\-mmm\-yyyy;@"/>
     <numFmt numFmtId="181" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="182" formatCode="[$-809]dd\ mmmm\ yyyy;@"/>
+    <numFmt numFmtId="183" formatCode="[$Rp-421]#,##0.00;[Red][$Rp-421]#,##0.00"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -461,7 +474,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -518,6 +531,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -703,7 +728,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -1025,6 +1050,37 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1151,7 +1207,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1163,119 +1219,119 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1408,9 +1464,6 @@
     <xf numFmtId="180" fontId="2" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1504,7 +1557,40 @@
     <xf numFmtId="181" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -2043,7 +2129,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="18.4375" style="2" customWidth="1"/>
@@ -2056,9 +2142,11 @@
     <col min="9" max="9" width="14.3359375" style="4"/>
     <col min="10" max="10" width="17.7109375" customWidth="1"/>
     <col min="11" max="11" width="17.3125" style="6"/>
-    <col min="12" max="12" width="22.6640625" style="4" customWidth="1"/>
-    <col min="13" max="13" width="15.25"/>
-    <col min="14" max="14" width="19.140625" customWidth="1"/>
+    <col min="12" max="12" width="26.125" style="4" customWidth="1"/>
+    <col min="13" max="13" width="5.8671875" customWidth="1"/>
+    <col min="14" max="14" width="16.9375" customWidth="1"/>
+    <col min="15" max="15" width="7.9375" customWidth="1"/>
+    <col min="17" max="17" width="15.25"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="18.35" spans="1:12">
@@ -2074,32 +2162,32 @@
       <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="46" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="48" t="s">
+      <c r="G1" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="49" t="s">
+      <c r="H1" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="48" t="s">
+      <c r="I1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="57" t="s">
+      <c r="J1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="58" t="s">
+      <c r="K1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="59" t="s">
+      <c r="L1" s="58" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" ht="16.8" spans="1:12">
       <c r="A2" s="11" t="s">
         <v>9</v>
       </c>
@@ -2118,26 +2206,26 @@
       <c r="F2" s="14">
         <v>39738000</v>
       </c>
-      <c r="G2" s="50" t="s">
+      <c r="G2" s="49" t="s">
         <v>13</v>
       </c>
       <c r="H2" s="18">
         <v>34233500</v>
       </c>
-      <c r="I2" s="50" t="s">
+      <c r="I2" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="60">
+      <c r="J2" s="59">
         <v>42310500</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="61" t="s">
+      <c r="L2" s="60" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" ht="16.8" spans="1:12">
       <c r="A3" s="15"/>
       <c r="B3" s="16" t="s">
         <v>17</v>
@@ -2163,17 +2251,17 @@
       <c r="I3" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="62">
+      <c r="J3" s="61">
         <v>48169400</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="61" t="s">
+      <c r="L3" s="60" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" ht="16.8" spans="1:12">
       <c r="A4" s="15"/>
       <c r="B4" s="16" t="s">
         <v>19</v>
@@ -2196,23 +2284,23 @@
       <c r="H4" s="18">
         <v>21943450</v>
       </c>
-      <c r="I4" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="62">
+      <c r="I4" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="61">
         <v>36138000</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="61" t="s">
+      <c r="L4" s="60" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" ht="16.8" spans="1:10">
       <c r="A5" s="15"/>
       <c r="B5" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>11</v>
@@ -2233,14 +2321,14 @@
         <v>320000</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="62"/>
+        <v>21</v>
+      </c>
+      <c r="J5" s="61"/>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="15"/>
       <c r="B6" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>11</v>
@@ -2261,16 +2349,16 @@
         <v>5069850</v>
       </c>
       <c r="I6" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="62">
+        <v>23</v>
+      </c>
+      <c r="J6" s="61">
         <v>6026050</v>
       </c>
-      <c r="L6" s="61" t="s">
+      <c r="L6" s="60" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:15">
       <c r="A7" s="15"/>
       <c r="B7" s="16" t="s">
         <v>24</v>
@@ -2293,23 +2381,27 @@
       <c r="H7" s="18">
         <v>13417600</v>
       </c>
-      <c r="I7" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="62">
+      <c r="I7" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="61">
         <v>9006800</v>
       </c>
       <c r="K7" s="6">
         <v>46027</v>
       </c>
-      <c r="L7" s="61" t="s">
+      <c r="L7" s="60" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="N7" s="75" t="s">
+        <v>25</v>
+      </c>
+      <c r="O7" s="76"/>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="15"/>
       <c r="B8" s="16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>11</v>
@@ -2330,77 +2422,83 @@
         <v>5850000</v>
       </c>
       <c r="I8" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="62">
+        <v>23</v>
+      </c>
+      <c r="J8" s="61">
         <v>8775000</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="61" t="s">
+      <c r="L8" s="60" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="N8" s="77"/>
+      <c r="O8" s="78"/>
+    </row>
+    <row r="9" ht="16.8" spans="1:15">
       <c r="A9" s="15"/>
       <c r="B9" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F9" s="18"/>
       <c r="G9" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H9" s="18"/>
       <c r="I9" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="62"/>
-    </row>
-    <row r="10" spans="1:12">
+        <v>21</v>
+      </c>
+      <c r="J9" s="61"/>
+      <c r="N9" s="77"/>
+      <c r="O9" s="78"/>
+    </row>
+    <row r="10" ht="16.8" spans="1:15">
       <c r="A10" s="15"/>
       <c r="B10" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10" s="18"/>
       <c r="E10" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F10" s="18"/>
       <c r="G10" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H10" s="18"/>
       <c r="I10" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="62">
+      <c r="J10" s="61">
         <v>160000</v>
       </c>
       <c r="K10" s="6">
-        <v>46021</v>
-      </c>
-      <c r="L10" s="61" t="s">
+        <v>46386</v>
+      </c>
+      <c r="L10" s="60" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="N10" s="77"/>
+      <c r="O10" s="78"/>
+    </row>
+    <row r="11" ht="16.8" spans="1:15">
       <c r="A11" s="15"/>
       <c r="B11" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="18"/>
       <c r="E11" s="17" t="s">
@@ -2415,23 +2513,25 @@
       <c r="H11" s="18">
         <v>152000</v>
       </c>
-      <c r="I11" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="62">
+      <c r="I11" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="61">
         <v>329000</v>
       </c>
       <c r="K11" s="6">
-        <v>46017</v>
-      </c>
-      <c r="L11" s="61" t="s">
+        <v>46382</v>
+      </c>
+      <c r="L11" s="60" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="N11" s="77"/>
+      <c r="O11" s="78"/>
+    </row>
+    <row r="12" ht="16.8" spans="1:15">
       <c r="A12" s="15"/>
       <c r="B12" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>11</v>
@@ -2452,20 +2552,22 @@
       <c r="I12" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="62">
+      <c r="J12" s="61">
         <v>319000</v>
       </c>
       <c r="K12" s="6">
-        <v>46015</v>
-      </c>
-      <c r="L12" s="61" t="s">
+        <v>46380</v>
+      </c>
+      <c r="L12" s="60" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="N12" s="77"/>
+      <c r="O12" s="78"/>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="15"/>
       <c r="B13" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>11</v>
@@ -2483,19 +2585,21 @@
       <c r="H13" s="18">
         <v>995000</v>
       </c>
-      <c r="I13" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" s="62">
+      <c r="I13" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J13" s="61">
         <v>2855000</v>
       </c>
-      <c r="K13" s="63"/>
-      <c r="L13" s="64"/>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="K13" s="62"/>
+      <c r="L13" s="63"/>
+      <c r="N13" s="77"/>
+      <c r="O13" s="78"/>
+    </row>
+    <row r="14" ht="16.8" spans="1:15">
       <c r="A14" s="15"/>
       <c r="B14" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>11</v>
@@ -2513,49 +2617,53 @@
       <c r="H14" s="18">
         <v>2996000</v>
       </c>
-      <c r="I14" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" s="62">
+      <c r="I14" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J14" s="61">
         <v>1044000</v>
       </c>
-      <c r="K14" s="63"/>
-      <c r="L14" s="64"/>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="K14" s="62"/>
+      <c r="L14" s="63"/>
+      <c r="N14" s="77"/>
+      <c r="O14" s="78"/>
+    </row>
+    <row r="15" ht="17.55" spans="1:15">
       <c r="A15" s="20"/>
       <c r="B15" s="21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="23"/>
-      <c r="E15" s="51" t="s">
-        <v>33</v>
+      <c r="E15" s="50" t="s">
+        <v>34</v>
       </c>
       <c r="F15" s="23">
         <v>10000000</v>
       </c>
-      <c r="G15" s="51" t="s">
-        <v>34</v>
+      <c r="G15" s="50" t="s">
+        <v>35</v>
       </c>
       <c r="H15" s="18">
         <v>10000000</v>
       </c>
-      <c r="I15" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" s="65">
+      <c r="I15" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" s="64">
         <v>10000000</v>
       </c>
-      <c r="K15" s="66"/>
-      <c r="L15" s="67"/>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="K15" s="65"/>
+      <c r="L15" s="66"/>
+      <c r="N15" s="77"/>
+      <c r="O15" s="78"/>
+    </row>
+    <row r="16" ht="17.55" spans="1:15">
       <c r="A16" s="24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>11</v>
@@ -2576,22 +2684,24 @@
         <v>12478500</v>
       </c>
       <c r="I16" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="60">
+        <v>23</v>
+      </c>
+      <c r="J16" s="59">
         <v>14051500</v>
       </c>
-      <c r="K16" s="66" t="s">
+      <c r="K16" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="L16" s="68" t="s">
+      <c r="L16" s="67" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="N16" s="79"/>
+      <c r="O16" s="80"/>
+    </row>
+    <row r="17" ht="16.8" spans="1:12">
       <c r="A17" s="25"/>
       <c r="B17" s="16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>11</v>
@@ -2611,23 +2721,23 @@
       <c r="H17" s="18">
         <v>1800000</v>
       </c>
-      <c r="I17" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="62">
+      <c r="I17" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J17" s="61">
         <v>2860000</v>
       </c>
-      <c r="K17" s="66" t="s">
+      <c r="K17" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="L17" s="69" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="L17" s="68" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" ht="16.8" spans="1:15">
       <c r="A18" s="25"/>
       <c r="B18" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>11</v>
@@ -2647,26 +2757,27 @@
       <c r="H18" s="18">
         <v>7025000</v>
       </c>
-      <c r="I18" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="62">
+      <c r="I18" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J18" s="61">
         <v>4175000</v>
       </c>
       <c r="K18" s="6">
         <v>46052</v>
       </c>
-      <c r="L18" s="68" t="s">
+      <c r="L18" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="N18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="N18" s="81" t="s">
+        <v>42</v>
+      </c>
+      <c r="O18" s="81"/>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="25"/>
       <c r="B19" s="16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>11</v>
@@ -2687,56 +2798,66 @@
         <v>12023500</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="62">
+        <v>23</v>
+      </c>
+      <c r="J19" s="61">
         <v>18173500</v>
       </c>
       <c r="K19" s="6">
         <v>46051</v>
       </c>
-      <c r="L19" s="68" t="s">
+      <c r="L19" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="N19" s="76">
+      <c r="N19" s="82">
         <f>SUM(J2:J50)+42310500</f>
-        <v>312314366</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+        <v>312960866</v>
+      </c>
+      <c r="O19" s="42" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" ht="16.8" spans="1:15">
       <c r="A20" s="25"/>
       <c r="B20" s="16" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D20" s="18"/>
       <c r="E20" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F20" s="18"/>
       <c r="G20" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H20" s="18"/>
-      <c r="I20" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="62">
+      <c r="I20" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J20" s="61">
         <v>3633750</v>
       </c>
       <c r="K20" s="6">
         <v>46035</v>
       </c>
-      <c r="L20" s="61" t="s">
+      <c r="L20" s="60" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="N20" s="82">
+        <f>SUMIFS(J2:J50,I2:I50,"*PAID*")</f>
+        <v>211559316</v>
+      </c>
+      <c r="O20" s="83" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" ht="16.8" spans="1:17">
       <c r="A21" s="25"/>
       <c r="B21" s="16" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>11</v>
@@ -2756,24 +2877,31 @@
       <c r="H21" s="18">
         <v>1665000</v>
       </c>
-      <c r="I21" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" s="62">
+      <c r="I21" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J21" s="61">
         <v>3552000</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L21" s="61" t="s">
+      <c r="L21" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="N21" s="77"/>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="N21" s="84">
+        <f>N19-N20</f>
+        <v>101401550</v>
+      </c>
+      <c r="O21" s="85" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q21" s="87"/>
+    </row>
+    <row r="22" ht="16.8" spans="1:17">
       <c r="A22" s="25"/>
       <c r="B22" s="16" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>11</v>
@@ -2782,7 +2910,7 @@
         <v>2410000</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F22" s="18"/>
       <c r="G22" s="17" t="s">
@@ -2792,22 +2920,24 @@
         <v>2110000</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="62">
+        <v>23</v>
+      </c>
+      <c r="J22" s="61">
         <v>12065000</v>
       </c>
       <c r="K22" s="6">
         <v>46036</v>
       </c>
-      <c r="L22" s="61" t="s">
+      <c r="L22" s="60" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="N22" s="86"/>
+      <c r="Q22" s="87"/>
+    </row>
+    <row r="23" ht="16.8" spans="1:14">
       <c r="A23" s="25"/>
       <c r="B23" s="16" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>11</v>
@@ -2827,26 +2957,27 @@
       <c r="H23" s="18">
         <v>1750003</v>
       </c>
-      <c r="I23" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="62">
+      <c r="I23" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J23" s="61">
         <v>1837503</v>
       </c>
       <c r="K23" s="6">
         <v>46036</v>
       </c>
-      <c r="L23" s="61" t="s">
+      <c r="L23" s="60" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="N23" s="87"/>
+    </row>
+    <row r="24" ht="16.8" spans="1:10">
       <c r="A24" s="25"/>
       <c r="B24" s="16" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D24" s="18"/>
       <c r="E24" s="17" t="s">
@@ -2856,18 +2987,18 @@
         <v>2280000</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H24" s="18"/>
       <c r="I24" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" s="62"/>
-    </row>
-    <row r="25" spans="1:12">
+        <v>21</v>
+      </c>
+      <c r="J24" s="61"/>
+    </row>
+    <row r="25" ht="16.8" spans="1:14">
       <c r="A25" s="25"/>
       <c r="B25" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>11</v>
@@ -2887,23 +3018,24 @@
       <c r="H25" s="18">
         <v>1190009</v>
       </c>
-      <c r="I25" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" s="62">
+      <c r="I25" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J25" s="61">
         <v>2380013</v>
       </c>
       <c r="K25" s="6">
         <v>46044</v>
       </c>
-      <c r="L25" s="61" t="s">
+      <c r="L25" s="60" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="N25" s="87"/>
+    </row>
+    <row r="26" ht="16.8" spans="1:14">
       <c r="A26" s="25"/>
       <c r="B26" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>11</v>
@@ -2926,20 +3058,21 @@
       <c r="I26" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="J26" s="62">
+      <c r="J26" s="61">
         <v>5600000</v>
       </c>
       <c r="K26" s="6">
         <v>46023</v>
       </c>
-      <c r="L26" s="61" t="s">
+      <c r="L26" s="60" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="N26" s="87"/>
+    </row>
+    <row r="27" ht="16.8" spans="1:12">
       <c r="A27" s="25"/>
       <c r="B27" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>11</v>
@@ -2959,45 +3092,45 @@
       <c r="H27" s="18">
         <v>600000</v>
       </c>
-      <c r="I27" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J27" s="62">
+      <c r="I27" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J27" s="61">
         <v>915750</v>
       </c>
       <c r="K27" s="6">
-        <v>46013</v>
-      </c>
-      <c r="L27" s="61" t="s">
+        <v>46378</v>
+      </c>
+      <c r="L27" s="60" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" ht="16.8" spans="1:10">
       <c r="A28" s="25"/>
       <c r="B28" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D28" s="18"/>
       <c r="E28" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F28" s="18"/>
       <c r="G28" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H28" s="18"/>
       <c r="I28" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="J28" s="62"/>
-    </row>
-    <row r="29" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="J28" s="61"/>
+    </row>
+    <row r="29" ht="16.8" spans="1:10">
       <c r="A29" s="25"/>
       <c r="B29" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>11</v>
@@ -3006,306 +3139,302 @@
         <v>3948000</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F29" s="18"/>
       <c r="G29" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H29" s="18"/>
       <c r="I29" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" s="62"/>
-    </row>
-    <row r="30" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="J29" s="61"/>
+    </row>
+    <row r="30" ht="16.8" spans="1:12">
       <c r="A30" s="25"/>
       <c r="B30" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D30" s="18">
-        <v>250000</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="18"/>
       <c r="E30" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="F30" s="18">
-        <v>300000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="F30" s="18"/>
       <c r="G30" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="H30" s="18">
-        <v>300000</v>
-      </c>
-      <c r="I30" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="J30" s="62">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
+        <v>21</v>
+      </c>
+      <c r="H30" s="18"/>
+      <c r="I30" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J30" s="61">
+        <v>975300</v>
+      </c>
+      <c r="K30" s="6">
+        <v>46031</v>
+      </c>
+      <c r="L30" s="60" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" ht="16.8" spans="1:12">
       <c r="A31" s="25"/>
       <c r="B31" s="16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D31" s="18"/>
       <c r="E31" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" s="18"/>
       <c r="G31" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H31" s="18"/>
       <c r="I31" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="J31" s="62">
-        <v>975300</v>
+      <c r="J31" s="61">
+        <v>1600000</v>
       </c>
       <c r="K31" s="6">
-        <v>46031</v>
-      </c>
-      <c r="L31" s="61" t="s">
+        <v>46383</v>
+      </c>
+      <c r="L31" s="60" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" ht="16.8" spans="1:10">
       <c r="A32" s="25"/>
       <c r="B32" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D32" s="18"/>
-      <c r="E32" s="19" t="s">
-        <v>22</v>
+      <c r="E32" s="26" t="s">
+        <v>21</v>
       </c>
       <c r="F32" s="18"/>
-      <c r="G32" s="19" t="s">
-        <v>22</v>
+      <c r="G32" s="26" t="s">
+        <v>21</v>
       </c>
       <c r="H32" s="18"/>
-      <c r="I32" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="J32" s="62">
-        <v>1600000</v>
-      </c>
-      <c r="K32" s="6">
-        <v>46018</v>
-      </c>
-      <c r="L32" s="61" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="25"/>
-      <c r="B33" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" s="18"/>
-      <c r="E33" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="18"/>
-      <c r="G33" s="26" t="s">
-        <v>22</v>
+      <c r="I32" s="39"/>
+      <c r="J32" s="61"/>
+    </row>
+    <row r="33" ht="17.55" spans="1:10">
+      <c r="A33" s="27"/>
+      <c r="B33" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="30"/>
+      <c r="E33" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="30">
+        <v>915750</v>
+      </c>
+      <c r="G33" s="51" t="s">
+        <v>21</v>
       </c>
       <c r="H33" s="18"/>
       <c r="I33" s="39"/>
-      <c r="J33" s="62"/>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="27"/>
-      <c r="B34" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="D34" s="30"/>
-      <c r="E34" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="30">
-        <v>915750</v>
-      </c>
-      <c r="G34" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="18"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="70"/>
-    </row>
-    <row r="35" spans="1:12">
-      <c r="A35" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" s="14">
+      <c r="J33" s="69"/>
+    </row>
+    <row r="34" ht="17.55" spans="1:12">
+      <c r="A34" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="14">
         <v>4897000</v>
       </c>
+      <c r="E34" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="14">
+        <v>8368100</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="18">
+        <v>4047600</v>
+      </c>
+      <c r="I34" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J34" s="59">
+        <v>1897000</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L34" s="60" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" ht="16.8" spans="1:10">
+      <c r="A35" s="15"/>
+      <c r="B35" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="18">
+        <v>4375000</v>
+      </c>
       <c r="E35" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F35" s="14">
-        <v>8368100</v>
-      </c>
-      <c r="G35" s="13" t="s">
+      <c r="F35" s="18">
+        <v>4715000</v>
+      </c>
+      <c r="G35" s="17" t="s">
         <v>11</v>
       </c>
       <c r="H35" s="18">
-        <v>4047600</v>
-      </c>
-      <c r="I35" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J35" s="60">
-        <v>1897000</v>
-      </c>
-      <c r="K35" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="L35" s="61" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>2585000</v>
+      </c>
+      <c r="I35" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J35" s="61">
+        <v>27100000</v>
+      </c>
+    </row>
+    <row r="36" ht="16.8" spans="1:10">
       <c r="A36" s="15"/>
       <c r="B36" s="16" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>11</v>
       </c>
       <c r="D36" s="18">
-        <v>4375000</v>
-      </c>
-      <c r="E36" s="13" t="s">
+        <v>1007480.64</v>
+      </c>
+      <c r="E36" s="17" t="s">
         <v>11</v>
       </c>
       <c r="F36" s="18">
-        <v>4715000</v>
-      </c>
-      <c r="G36" s="17" t="s">
+        <v>638483</v>
+      </c>
+      <c r="G36" s="33" t="s">
         <v>11</v>
       </c>
       <c r="H36" s="18">
-        <v>2585000</v>
-      </c>
-      <c r="I36" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J36" s="62">
-        <v>27100000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="15"/>
-      <c r="B37" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D37" s="18">
-        <v>1007480.64</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="18">
-        <v>638483</v>
+        <v>269482</v>
+      </c>
+      <c r="I36" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" s="61"/>
+    </row>
+    <row r="37" ht="17.55" spans="1:12">
+      <c r="A37" s="31"/>
+      <c r="B37" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="34">
+        <v>1168000</v>
+      </c>
+      <c r="E37" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="34">
+        <v>893000</v>
       </c>
       <c r="G37" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="H37" s="18">
-        <v>269482</v>
-      </c>
-      <c r="I37" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="J37" s="62"/>
-    </row>
-    <row r="38" spans="1:12">
-      <c r="A38" s="31"/>
-      <c r="B38" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="C38" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" s="34">
-        <v>1168000</v>
-      </c>
-      <c r="E38" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="34">
-        <v>893000</v>
-      </c>
-      <c r="G38" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="H38" s="34">
+      <c r="H37" s="34">
         <v>847000</v>
       </c>
-      <c r="I38" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="J38" s="71">
+      <c r="I37" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J37" s="70">
         <v>944000</v>
       </c>
-      <c r="K38" s="6">
+      <c r="K37" s="6">
         <v>46027</v>
       </c>
-      <c r="L38" s="61" t="s">
+      <c r="L37" s="60" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39" s="36"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="14">
+    <row r="38" ht="16.8" spans="1:10">
+      <c r="A38" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C38" s="36"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="14">
         <v>1020000</v>
       </c>
-      <c r="G39" s="37"/>
-      <c r="H39" s="53"/>
-      <c r="I39" s="72"/>
-      <c r="J39" s="73"/>
-    </row>
-    <row r="40" spans="1:10">
+      <c r="G38" s="37"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="72"/>
+    </row>
+    <row r="39" ht="16.8" spans="1:10">
+      <c r="A39" s="38"/>
+      <c r="B39" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" s="39"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="18">
+        <v>1350000</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" s="53">
+        <v>1800000</v>
+      </c>
+      <c r="I39" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J39" s="73">
+        <v>1850000</v>
+      </c>
+    </row>
+    <row r="40" ht="16.8" spans="1:10">
       <c r="A40" s="38"/>
       <c r="B40" s="16" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C40" s="39"/>
       <c r="D40" s="40"/>
@@ -3313,25 +3442,17 @@
         <v>11</v>
       </c>
       <c r="F40" s="18">
-        <v>1350000</v>
-      </c>
-      <c r="G40" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="H40" s="54">
-        <v>1800000</v>
-      </c>
-      <c r="I40" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="J40" s="74">
-        <v>1850000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12">
+        <v>600000</v>
+      </c>
+      <c r="G40" s="40"/>
+      <c r="H40" s="53"/>
+      <c r="I40" s="41"/>
+      <c r="J40" s="73"/>
+    </row>
+    <row r="41" ht="16.8" spans="1:10">
       <c r="A41" s="38"/>
       <c r="B41" s="16" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C41" s="39"/>
       <c r="D41" s="40"/>
@@ -3339,20 +3460,17 @@
         <v>11</v>
       </c>
       <c r="F41" s="18">
-        <v>600000</v>
+        <v>318134</v>
       </c>
       <c r="G41" s="40"/>
-      <c r="H41" s="54"/>
+      <c r="H41" s="53"/>
       <c r="I41" s="41"/>
-      <c r="J41" s="74"/>
-      <c r="L41" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12">
+      <c r="J41" s="73"/>
+    </row>
+    <row r="42" ht="16.8" spans="1:10">
       <c r="A42" s="38"/>
       <c r="B42" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C42" s="39"/>
       <c r="D42" s="40"/>
@@ -3360,20 +3478,17 @@
         <v>11</v>
       </c>
       <c r="F42" s="18">
-        <v>318134</v>
+        <v>248700</v>
       </c>
       <c r="G42" s="40"/>
-      <c r="H42" s="54"/>
+      <c r="H42" s="53"/>
       <c r="I42" s="41"/>
-      <c r="J42" s="74"/>
-      <c r="L42" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+      <c r="J42" s="73"/>
+    </row>
+    <row r="43" ht="16.8" spans="1:10">
       <c r="A43" s="38"/>
       <c r="B43" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C43" s="39"/>
       <c r="D43" s="40"/>
@@ -3381,17 +3496,17 @@
         <v>11</v>
       </c>
       <c r="F43" s="18">
-        <v>248700</v>
+        <v>1029180</v>
       </c>
       <c r="G43" s="40"/>
-      <c r="H43" s="54"/>
+      <c r="H43" s="53"/>
       <c r="I43" s="41"/>
-      <c r="J43" s="74"/>
-    </row>
-    <row r="44" spans="1:10">
+      <c r="J43" s="73"/>
+    </row>
+    <row r="44" ht="16.8" spans="1:10">
       <c r="A44" s="38"/>
       <c r="B44" s="16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C44" s="39"/>
       <c r="D44" s="40"/>
@@ -3399,17 +3514,17 @@
         <v>11</v>
       </c>
       <c r="F44" s="18">
-        <v>1029180</v>
+        <v>270000</v>
       </c>
       <c r="G44" s="40"/>
-      <c r="H44" s="54"/>
+      <c r="H44" s="53"/>
       <c r="I44" s="41"/>
-      <c r="J44" s="74"/>
-    </row>
-    <row r="45" spans="1:10">
+      <c r="J44" s="73"/>
+    </row>
+    <row r="45" ht="16.8" spans="1:10">
       <c r="A45" s="38"/>
       <c r="B45" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C45" s="39"/>
       <c r="D45" s="40"/>
@@ -3417,17 +3532,17 @@
         <v>11</v>
       </c>
       <c r="F45" s="18">
-        <v>270000</v>
+        <v>1000000</v>
       </c>
       <c r="G45" s="40"/>
-      <c r="H45" s="54"/>
+      <c r="H45" s="53"/>
       <c r="I45" s="41"/>
-      <c r="J45" s="74"/>
-    </row>
-    <row r="46" spans="1:10">
+      <c r="J45" s="73"/>
+    </row>
+    <row r="46" ht="16.8" spans="1:10">
       <c r="A46" s="38"/>
       <c r="B46" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C46" s="39"/>
       <c r="D46" s="40"/>
@@ -3435,17 +3550,17 @@
         <v>11</v>
       </c>
       <c r="F46" s="18">
-        <v>1000000</v>
+        <v>3000000</v>
       </c>
       <c r="G46" s="40"/>
-      <c r="H46" s="54"/>
+      <c r="H46" s="53"/>
       <c r="I46" s="41"/>
-      <c r="J46" s="74"/>
-    </row>
-    <row r="47" spans="1:10">
+      <c r="J46" s="73"/>
+    </row>
+    <row r="47" ht="16.8" spans="1:10">
       <c r="A47" s="38"/>
       <c r="B47" s="16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C47" s="39"/>
       <c r="D47" s="40"/>
@@ -3453,112 +3568,96 @@
         <v>11</v>
       </c>
       <c r="F47" s="18">
-        <v>3000000</v>
+        <v>1800000</v>
       </c>
       <c r="G47" s="40"/>
-      <c r="H47" s="54"/>
+      <c r="H47" s="53"/>
       <c r="I47" s="41"/>
-      <c r="J47" s="74"/>
-    </row>
-    <row r="48" spans="1:10">
+      <c r="J47" s="73"/>
+    </row>
+    <row r="48" ht="16.8" spans="1:10">
       <c r="A48" s="38"/>
       <c r="B48" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C48" s="39"/>
-      <c r="D48" s="40"/>
-      <c r="E48" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="18">
-        <v>1800000</v>
-      </c>
-      <c r="G48" s="40"/>
-      <c r="H48" s="54"/>
+        <v>76</v>
+      </c>
+      <c r="C48" s="41"/>
+      <c r="D48" s="42"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" s="54">
+        <v>2450000</v>
+      </c>
       <c r="I48" s="41"/>
-      <c r="J48" s="74"/>
-    </row>
-    <row r="49" spans="1:10">
+      <c r="J48" s="73"/>
+    </row>
+    <row r="49" ht="16.8" spans="1:10">
       <c r="A49" s="38"/>
       <c r="B49" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C49" s="41"/>
       <c r="D49" s="42"/>
       <c r="E49" s="41"/>
-      <c r="F49" s="55"/>
-      <c r="G49" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="H49" s="55">
-        <v>2450000</v>
-      </c>
-      <c r="I49" s="41"/>
-      <c r="J49" s="74"/>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="38"/>
-      <c r="B50" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C50" s="41"/>
-      <c r="D50" s="42"/>
-      <c r="E50" s="41"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J49" s="73">
+        <v>860800</v>
+      </c>
+    </row>
+    <row r="50" ht="17.55" spans="1:10">
+      <c r="A50" s="43"/>
+      <c r="B50" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C50" s="44"/>
+      <c r="D50" s="45"/>
+      <c r="E50" s="44"/>
       <c r="F50" s="55"/>
-      <c r="G50" s="42"/>
+      <c r="G50" s="45"/>
       <c r="H50" s="55"/>
       <c r="I50" s="17" t="s">
         <v>11</v>
       </c>
       <c r="J50" s="74">
-        <v>860800</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" s="43"/>
-      <c r="B51" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="C51" s="45"/>
-      <c r="D51" s="46"/>
-      <c r="E51" s="45"/>
-      <c r="F51" s="56"/>
-      <c r="G51" s="46"/>
-      <c r="H51" s="56"/>
-      <c r="I51" s="45" t="s">
-        <v>20</v>
-      </c>
-      <c r="J51" s="75">
         <v>1046500</v>
       </c>
+    </row>
+    <row r="51" spans="6:6">
+      <c r="F51" s="5"/>
     </row>
     <row r="52" spans="6:6">
       <c r="F52" s="5"/>
     </row>
-    <row r="53" spans="6:6">
+    <row r="53" spans="1:6">
+      <c r="A53" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="F53" s="5"/>
     </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="2" t="s">
-        <v>79</v>
+    <row r="54" ht="16.8" spans="1:6">
+      <c r="A54" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="F54" s="5"/>
     </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F55" s="5"/>
-    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
+    <mergeCell ref="N18:O18"/>
     <mergeCell ref="A2:A15"/>
-    <mergeCell ref="A16:A34"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A39:A51"/>
+    <mergeCell ref="A16:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A50"/>
+    <mergeCell ref="N7:O16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
